--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -5,23 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\actualizar tarifario\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0344EE8-046B-4096-B6A1-D6A87F94C499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C94063-557E-4C2D-9274-D89899604713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REDES" sheetId="1" r:id="rId1"/>
     <sheet name="INFO_PLAN" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="226">
   <si>
     <t>Aseguradora</t>
   </si>
@@ -119,9 +119,6 @@
     <t>Red 6</t>
   </si>
   <si>
-    <t>Angloamericana</t>
-  </si>
-  <si>
     <t>Red 7</t>
   </si>
   <si>
@@ -179,27 +176,15 @@
     <t>1 día de cuarto al 95%</t>
   </si>
   <si>
-    <t>San Judas Tadeo, Santa Martha Del Sur, San Juan Bautista</t>
-  </si>
-  <si>
     <t>S/55 al 65%</t>
   </si>
   <si>
-    <t>Bellavista, Limatambo, Good Hope, Montefiori, Cm Jockey Salud, Providencia, Stella Maris, Vesalio</t>
-  </si>
-  <si>
     <t>S/65 al 60%</t>
   </si>
   <si>
-    <t>Centenario Peruano Japonesa, Tezza, San Gabriel, Especialidades Médicas, Javier Prado</t>
-  </si>
-  <si>
     <t>S/80 al 55%</t>
   </si>
   <si>
-    <t>Jesús Del Norte</t>
-  </si>
-  <si>
     <t>S/95 al 55%</t>
   </si>
   <si>
@@ -227,18 +212,9 @@
     <t>S/35 al 85%</t>
   </si>
   <si>
-    <t>Maisón De Santé, San Juan Bautista, Santa Martha Del Sur</t>
-  </si>
-  <si>
     <t>S/45 al 75%</t>
   </si>
   <si>
-    <t>Sanna Miraflores, Sanna Chacarilla, Sanna La Molina, Sanna Los Olivos, Stella Maris, Vesalio, Limatambo, Cayetano Heredia, Providencia, Aviva</t>
-  </si>
-  <si>
-    <t>Montefiori, Good Hope, Centenario Peruano Japonesa, San Gabriel</t>
-  </si>
-  <si>
     <t>Esencial Plus</t>
   </si>
   <si>
@@ -248,15 +224,9 @@
     <t>S/45 al 80%</t>
   </si>
   <si>
-    <t>Sanna Miraflores, Sanna Chacarilla, Sanna La Molina, Sanna Los Olivos, Stella Maris, Vesalio, Limatambo, Cayetano Heredia, Providencia, Aviva, Centenario Peruano Japonesa, Montefiori</t>
-  </si>
-  <si>
     <t>S/55 al 70%</t>
   </si>
   <si>
-    <t>Good Hope, San Gabriel</t>
-  </si>
-  <si>
     <t>Multisalud Base</t>
   </si>
   <si>
@@ -266,108 +236,51 @@
     <t>S/40 al 80%</t>
   </si>
   <si>
-    <t>Good Hope, San Gabriel, Jesús Del Norte, Javier Prado</t>
-  </si>
-  <si>
     <t>S/85 al 60%</t>
   </si>
   <si>
-    <t>Sanna San Borja, El Golf, Tezza</t>
-  </si>
-  <si>
     <t>1 día de cuarto al 60%</t>
   </si>
   <si>
-    <t>Red Sanna - Centros Clínicos</t>
-  </si>
-  <si>
     <t>S/55 al 100%</t>
   </si>
   <si>
     <t>No aplica</t>
   </si>
   <si>
-    <t>Sanna Miraflores, Sanna Chacarilla, Sanna La Molina, Sanna Los Olivos</t>
-  </si>
-  <si>
     <t>S/50 al 75%</t>
   </si>
   <si>
-    <t>S/400 al 85%</t>
-  </si>
-  <si>
-    <t>Versalles, Montefiori, Providencia, San Juan Bautista, Santa Martha Del Sur</t>
-  </si>
-  <si>
-    <t>S/500 al 80%</t>
-  </si>
-  <si>
-    <t>Bellavista, Medavan, Stella Maris, Vesalio, Limatambo, Cayetano Heredia, San Judas Tadeo, Jockey Salud</t>
-  </si>
-  <si>
     <t>S/70 al 65%</t>
   </si>
   <si>
-    <t>S/600 al 75%</t>
-  </si>
-  <si>
-    <t>Good Hope, Javier Prado, Aviva, San Gabriel</t>
-  </si>
-  <si>
     <t>S/800 al70%</t>
   </si>
   <si>
-    <t>Sanna San Borja, Centenario Peruano Japonesa</t>
-  </si>
-  <si>
     <t>Multisalud</t>
   </si>
   <si>
-    <t>Versalles, Montefiori, Providencia, San Juan Bautista, Santa Martha Del Sur, Providencia, Stella Maris, Vesalio, Limatambo, Cayetano Heredia, Cm Jockey Salud</t>
-  </si>
-  <si>
-    <t>Javier Prado, Centenario Peruano Japonesa, Aviva, Good Hope, Jesús Del Norte, San Gabriel</t>
-  </si>
-  <si>
     <t>S/80 al 70%</t>
   </si>
   <si>
     <t>S/110 al 60%</t>
   </si>
   <si>
-    <t>San Felipe</t>
-  </si>
-  <si>
     <t>S/120 al 60%</t>
   </si>
   <si>
     <t>Red 8</t>
   </si>
   <si>
-    <t>S/140 al 60%</t>
-  </si>
-  <si>
-    <t>Delgado</t>
-  </si>
-  <si>
     <t>Medicvida Nacional</t>
   </si>
   <si>
     <t>S/45 al 100%</t>
   </si>
   <si>
-    <t>Versalles, Montefiori, Providencia, San Juan Bautista, Santa Martha Del Sur, Providencia, Stella Maris, Vesalio, Limatambo, Cayetano Heredia, Cm Jockey Salud, Centenario Peruano Japonesa, Javier Prado</t>
-  </si>
-  <si>
-    <t>Good Hope, Jesús Del Norte, San Gabriel, Tezza</t>
-  </si>
-  <si>
     <t>Angloamericana, San Felipe</t>
   </si>
   <si>
-    <t>Montesur</t>
-  </si>
-  <si>
     <t>S/125 al 60%</t>
   </si>
   <si>
@@ -383,9 +296,6 @@
     <t>Red La Positiva</t>
   </si>
   <si>
-    <t>La Positiva Salud</t>
-  </si>
-  <si>
     <t>S/60 al 80%</t>
   </si>
   <si>
@@ -443,110 +353,359 @@
     <t>S/110 al 65%</t>
   </si>
   <si>
-    <t>Santa Martha Del Sur, San Judas Tadeo, Bellavista, Aviva</t>
-  </si>
-  <si>
-    <t>Limatambo, Providencia, Medavan, Stella Maris, Montefiori, Vesalio, Cm Jockey Salud, San Gabriel, Especialidades Médicas, Jesús Del Norte</t>
-  </si>
-  <si>
-    <t>Internacional Lima, Tezza, San Pablo</t>
-  </si>
-  <si>
     <t>S/130 al 60%</t>
   </si>
   <si>
-    <t>Internacional Lima, Tezza, San Pablo, Ricardo Palma, El Golf, Santa Isabel, Hogar  San Juan De Dios</t>
-  </si>
-  <si>
-    <t>Angloamericana, San Felipe, Miraflores</t>
-  </si>
-  <si>
-    <t>San Juan Bautista, Centro Médico Medex, Integramédica</t>
-  </si>
-  <si>
-    <t>Centenario Peruano Japonesa, Javier Prado, Cayetano Heredia, Good Hope</t>
-  </si>
-  <si>
     <t>Montefiori, Providencia, Medavan, Cayetano Heredia, San Judas Tadeo, Santa Martha Del Sur, Especialidades Médicas, Jesús Del Norte, Hogar  San Juan De Dios, San Juan Bautista</t>
   </si>
   <si>
     <t>Cubierto al 90%</t>
   </si>
   <si>
-    <t>Montefiori, Cayetano Heredia</t>
-  </si>
-  <si>
-    <t>Stella Maris, San Judas Tadeo, Bellavista,  San Juan Bautista, Santa Martha Del Sur, Versalles, Hogar  San Juan De Dios, La Luz</t>
-  </si>
-  <si>
-    <t>Tezza, Jesús Del Norte, San Gabriel, Maisón De Santé, Javier Prado</t>
-  </si>
-  <si>
-    <t>San Pablo, Ricardo Palma, Urozen</t>
-  </si>
-  <si>
-    <t>San Juan Bautista, Santa Martha Del Sur, Versalles, Hogar  San Juan De Dios, La Luz, Montefiori</t>
-  </si>
-  <si>
-    <t>Limatambo, Centenario Peruano Japonesa, Good Hope, Providencia, Cm Jockey Salud, Vesalio</t>
-  </si>
-  <si>
-    <t>Good Hope, Centenario Peruano Japonesa, Providencia, Limatambo, Cm Jockey Salud, Vesalio, Medavan</t>
-  </si>
-  <si>
-    <t>Medex, Bellavista, San Judas Tadeo, Stella Maris</t>
-  </si>
-  <si>
     <t>S/60 al 70%</t>
   </si>
   <si>
-    <t>Medex, Bellavista, San Judas Tadeo, Stella Maris, Medavan</t>
-  </si>
-  <si>
-    <t>Good Hope, Centenario Peruano Japonesa, Providencia, Limatambo, Cm Jockey Salud, Vesalio</t>
-  </si>
-  <si>
     <t>S/105 al 65%</t>
   </si>
   <si>
-    <t>El Golf, Santa Isabel, Alvarez, Auna Guardia Cvil</t>
-  </si>
-  <si>
-    <t>Sanna San Borja, Montesur</t>
-  </si>
-  <si>
-    <t>Santa Isabel, Ricardo Palma, Internacional San Borja</t>
-  </si>
-  <si>
-    <t>Sanna San Borja, Bellavista, Especialidades Médicas, El Golf, Maisón De Santé, Tezza, Internacional Lima, San Pablo</t>
-  </si>
-  <si>
-    <t>Angloamericana, San Felipe, Delgado, Internacional San Borja, Internacional Lima</t>
-  </si>
-  <si>
-    <t>Internacional San Borja</t>
-  </si>
-  <si>
-    <t>Montesur, Sanna San Borja, Internacional San Borja</t>
-  </si>
-  <si>
-    <t>Santa Isabel, Internacional San Borja</t>
-  </si>
-  <si>
-    <t>Santa Isabel, Internacional San Borja, El Golf</t>
-  </si>
-  <si>
-    <t>Ricardo Palma, San Pablo, Internacional San Borja</t>
-  </si>
-  <si>
     <t>Ricardo Palma, Sanna San Borja, Maisón De Santé, El Golf, Santa Isabel, Internacional San Borja, Internacional Lima</t>
+  </si>
+  <si>
+    <t>Plan Vital</t>
+  </si>
+  <si>
+    <t>S/60 al 60%</t>
+  </si>
+  <si>
+    <t>Clínicas</t>
+  </si>
+  <si>
+    <t>Centro médico</t>
+  </si>
+  <si>
+    <t>Sede</t>
+  </si>
+  <si>
+    <t>Callao</t>
+  </si>
+  <si>
+    <t>Limatambo</t>
+  </si>
+  <si>
+    <t>Suiza Lab</t>
+  </si>
+  <si>
+    <t>Miraflores</t>
+  </si>
+  <si>
+    <t>Surquillo</t>
+  </si>
+  <si>
+    <t>Integramédica</t>
+  </si>
+  <si>
+    <t>Medex</t>
+  </si>
+  <si>
+    <t>Independencia</t>
+  </si>
+  <si>
+    <t>San Juan Bautista</t>
+  </si>
+  <si>
+    <t>SJL</t>
+  </si>
+  <si>
+    <t>Aviva</t>
+  </si>
+  <si>
+    <t>Los Olivos</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>San Isidro</t>
+  </si>
+  <si>
+    <t>Lima</t>
+  </si>
+  <si>
+    <t>Santa Maria del Sur</t>
+  </si>
+  <si>
+    <t>SJM</t>
+  </si>
+  <si>
+    <t>Maisón de Sante</t>
+  </si>
+  <si>
+    <t>Chorrillos</t>
+  </si>
+  <si>
+    <t>Surco</t>
+  </si>
+  <si>
+    <t>San Judas Tadeo</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Vesalio</t>
+  </si>
+  <si>
+    <t>San Borja</t>
+  </si>
+  <si>
+    <t>Stella Maris</t>
+  </si>
+  <si>
+    <t>Pueblo Libre</t>
+  </si>
+  <si>
+    <t>Montefiori</t>
+  </si>
+  <si>
+    <t>La Molina</t>
+  </si>
+  <si>
+    <t>Jesús del Norte</t>
+  </si>
+  <si>
+    <t>San Gabriel</t>
+  </si>
+  <si>
+    <t>Jockey Salud</t>
+  </si>
+  <si>
+    <t>Cayetano Heredia</t>
+  </si>
+  <si>
+    <t>SMP</t>
+  </si>
+  <si>
+    <t>Centenario Peruano Japonesa</t>
+  </si>
+  <si>
+    <t>Good Hope</t>
+  </si>
+  <si>
+    <t>Centro Médico Limatambo - Callao, Centro Médico Suiza Lab - Miraflores, Centro Médico Integramédica - Independencia, Clínica San Juan Bautista - SJL, Clínica Aviva - Los Olivos</t>
+  </si>
+  <si>
+    <t>Clínica Limatambo - SJL, Clínica Limatambo - San Isidro, Clínica Internacional - Lima, Clínica Santa Martha del Sur - SJM, Clínica Maisón de Sante - Chorrillos, Centro Médico Internacional - Surco, Clínica San Judas Tadeo - San Miguel, Clínica Vesalio - San Borja</t>
+  </si>
+  <si>
+    <t>Clínica Stella Maris - Pueblo Libre, Clínica Montefiori - La Molina, Clínica Jesús del Norte - Independencia, Clínica San Gabriel - San Miguel, Centro Médico Jockey Salud - Surco, Clínica Cayetano Heredia - SMP, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Good Hope - Miraflores, Clínica Limatambo - San Isidro</t>
+  </si>
+  <si>
+    <t>Clínica Limatambo - SJL, Clínica San Judas Tadeo - San Miguel, Clínica Santa Martha del Sur - SJM, Centro Médico Avendaño - Miraflores, Clínica Aviva - Los Olivos, Clínica Aviva - Lima, Clínica Maisón de Sante - Chorrillos</t>
+  </si>
+  <si>
+    <t>Centro Médico Limatambo - Callao, Clínica Bellavista - Callao, Centro Médico Suiza Lab - Miraflores, Clínica San Juan Bautista - SJL, Clínica Integramédica - San Isidro, Centro Médico Integramédica - Independencia, Clínica Cayetano Heredia - Lince, Centro Médico Ricardo Palma - Chorrillos, Centro Médico Medex - Surquillo</t>
+  </si>
+  <si>
+    <t>Clínica Good Hope - Miraflores, Clínica Cayetano Heredia - SMP, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Javier Prado - San Isidro</t>
+  </si>
+  <si>
+    <t>Clínica Tezza - Surco, Clínica Internacional - Lima, Clínica San Pablo - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Internacional - San Borja</t>
+  </si>
+  <si>
+    <t>Centro Médico Avendaño - Miraflores, Clínica Limatambo - SJL, Clínica San Judas Tadeo - San Miguel, Clínica Santa Martha del Sur - SJM, Clínica Aviva - Los Olivos, Clínica Aviva - Lima, Clínica Maisón de Sante - Chorrillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clínica Tezza - Surco, Clínica Internacional - Lima, Clínica Ricardo Palma - San Isidro, Clínica San Pablo - Surco, Clínica Santa Isabel - San Borja, Clínica San Juan De Dios - San Luis, Centro Médico Sanna - La Molina, Clínica El Golf - San Isidro, Centro Médico Sanna - Surco, Centro Médico Sanna - Miraflores  </t>
+  </si>
+  <si>
+    <t>Clínica Internacional - San Borja, Clínica Sanna  - San Borja, Clínica Montesur - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Angloamericana - La Molina, Clínica Angloamericana - San Isidro, Centro Médico San Felipe - La Molina, Clínica San Felipe - Jesús María, Clínica Miraflores - Miraflores</t>
+  </si>
+  <si>
+    <t>Clínica Delgado - Miraflores</t>
+  </si>
+  <si>
+    <t>Centro Médico Jockey Salud - Surco, Clínica Limatambo - San Isidro, Clínica Montefiori - La Molina, Clínica Providencia - San Miguel, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Clínica Medavan - Magdalena, Clínica Especialidades Médicas - San Borja, Centro Médico Internacional - San Isidro, Clínica San Gabriel - San Miguel, Centro Médico Internacional - Surco, Centro Médico Internacional - La Molina,  Clínica Jesús del Norte - Independencia</t>
+  </si>
+  <si>
+    <t>Clínica San Judas Tadeo - San Miguel, Centro Médico Suiza Lab - Miraflores, Clínica Santa Martha del Sur - SJM, Centro Médico Limatambo - Callao, Clínica Limatambo - SJL, Centro Médico Integramédica - Independencia, Clínica Integramédica - San Isidro, Clínica San Bernardo - Pueblo Libre, Clínica San Juan Bautista - SJL, Clínica MegaSalud Universal - Lima</t>
+  </si>
+  <si>
+    <t>Clínica Bellavista - Callao, Clínica Limatambo - San Isidro, Clínica Good Hope - Miraflores, Clínica Montefiori - La Molina, Centro Médico Jockey Salud - Surco, Clínica Medavan - Magdalena, Clínica Providencia - San Miguel, Clínica Versalles - Comas, Centro Médico Medex - Surquillo, Clínica Maisón de Sante - Chorrillos, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Clínica Cayetano Heredia - SMP</t>
+  </si>
+  <si>
+    <t>Centro Médico Internacional - San Isidro, Centro Médico Internacional - La Molina, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Tezza - Surco, Clínica San Gabriel - San Miguel, Clínica Javier Prado - San Isidro, Clínica Especialidades Médicas - San Borja</t>
+  </si>
+  <si>
+    <t>Clínica Internacional - Lima, Centro Médico Internacional - Surco, Clínica Jesús del Norte - Independencia</t>
+  </si>
+  <si>
+    <t>Clínica San Pablo - Surco, Clínica Ricardo Palma - San Isidro, Clínica Santa Isabel - San Borja, Clínica El Golf - San Isidro, Clínica Internacional - San Borja, Clínica Sanna  - San Borja, Clínica San Juan De Dios - San Luis, Centro Médico Sanna - La Molina</t>
+  </si>
+  <si>
+    <t>Clínica Angloamericana - La Molina, Clínica Angloamericana - San Isidro</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Clínica Santa Isabel - San Borja, Clínica Internacional - San Borja,</t>
+  </si>
+  <si>
+    <t>Centro Médico Limatambo - Callao, Clínica Maisón de Sante - Lima, Clínica Maisón de Sante - Chorrillos, Clínica Versalles - Comas, Clínica Mundo Salud - Los Olivos, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM</t>
+  </si>
+  <si>
+    <t>Centro Médico Jockey Salud - Surco, Centro Médico Sanna - La Molina, Centro Médico Sanna - Miraflores, Centro Médico Sanna - Surco, Centro Médico Sanna - Los Olivos, Centro Médico Sanna - San Miguel, Centro Médico Sanna - San Juan de Lurigancho, Centro Médico Ricardo Palma - Chorrillos, Centro Médico Integramédica - Independencia, Clínica Medavan - Magdalena, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Clínica Limatambo - San Isidro, Clínica Limatambo - SJL, Clínica Cayetano Heredia - SMP, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Clínica Aviva - Los Olivos, Clínica Aviva - Lima</t>
+  </si>
+  <si>
+    <t>Clínica Montefiori - La Molina, Clínica Good Hope - Miraflores, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica San Gabriel - San Miguel</t>
+  </si>
+  <si>
+    <t>Centro Médico Limatambo - Callao, Clínica Maisón de Sante - Lima, Clínica Maisón de Sante - Chorrillos, Clínica Versalles - Comas, Centro Médico Cayetano Heredia - Lince,  Clínica Mundo Salud - Los Olivos, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM</t>
+  </si>
+  <si>
+    <t>Centro Médico Ricardo Palma - Chorrillos, Centro Médico Integramédica - Independencia, Sanna Miraflores, Sanna La Molina, Centro Médico Sanna - San Miguel, Sanna Los Olivos, Centro Médico Sanna - San Juan de Lurigancho, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Centro Médico Sanna - Surco, Clínica Limatambo - San Isidro, Clínica Limatambo - SJL, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Aviva - Los Olivos, Clínica Aviva - Lima, Centro Médico Jockey Salud - Surco, Clínica Cayetano Heredia - SMP</t>
+  </si>
+  <si>
+    <t>Clínica Montefiori - La Molina, Clínica Good Hope - Miraflores, Clínica San Gabriel - San Miguel</t>
+  </si>
+  <si>
+    <t>Clínica Montefiori - La Molina, Clínica Good Hope - Miraflores, Clínica San Gabriel - San Miguel, Clínica Jesús del Norte - Independencia, Clínica Javier Prado - San Isidro</t>
+  </si>
+  <si>
+    <t>Clínica Internacional - Lima, Clínica Sanna  - San Borja, Clínica El Golf - San Isidro, Clínica Tezza - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Ricardo Palma - San Isidro, Clínica San Pablo - Surco, Clínica Internacional - San Borja</t>
+  </si>
+  <si>
+    <t>Centro Médico Integramédica - Independencia, Clínica Versalles - Comas, Clínica Mundo Salud - Los Olivos, Clínica Virgen del Rosario - Magdalena, Clínica Montefiori - La Molina, Clínica Providencia - San Miguel, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM</t>
+  </si>
+  <si>
+    <t>Centro Médico Sanna - Miraflores, Centro Médico Sanna - Surco, Centro Médico Sanna - La Molina, Centro Médico Sanna - Los Olivos, Centro Médico Sanna - San Miguel, Centro Médico Sanna - San Juan de Lurigancho, Centro Médico Ricardo Palma - Chorrillos, Clínica Bellavista - Callao, Clínica Medavan - Magdalena, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Centro Médico Limatambo - Callao, Centro Médico Los Álamos - Surquillo, Clínica Limatambo - San Isidro, Clínica Limatambo - SJL, Clínica Cayetano Heredia - SMP, Clínica San Judas Tadeo - San Miguel, Centro Médico Jockey Salud - Surco, Clínica Aviva - Lima</t>
+  </si>
+  <si>
+    <t>Clínica Good Hope - Miraflores, Clínica Javier Prado - San Isidro, Clínica Maisón de Sante - Chorrillos, Clínica Aviva - Los Olivos, Clínica San Gabriel - San Miguel</t>
+  </si>
+  <si>
+    <t>Clínica Sanna  - San Borja, Clínica Centenario Peruano Japonesa - Pueblo Libre</t>
+  </si>
+  <si>
+    <t>S/160 al 60%</t>
+  </si>
+  <si>
+    <t>Centro Médico Sanna - Miraflores, Centro Médico Sanna - Surco, Centro Médico Sanna - La Molina, Centro Médico Sanna - Los Olivos, Centro Médico Sanna - San Miguel, Centro Médico Sanna - San Juan de Lurigancho</t>
+  </si>
+  <si>
+    <t>Centro Médico Integramédica - Independencia, Clínica Versalles - Comas, Clínica Mundo Salud - Los Olivos, Clínica Montefiori - La Molina, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Centro Médico Ricardo Palma - Chorrillos, Centro Médico Limatambo - Callao, Clínica Limatambo - SJL, Clínica Medavan - Magdalena, Clínica Virgen del Rosario - Magdalena, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Clínica Limatambo - San Isidro, Clínica Aviva - Lima, Centro Médico Los Álamos - Surquillo, Clínica Cayetano Heredia - SMP, Centro Médico Jockey Salud - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Good Hope - Miraflores, Clínica Javier Prado - San Isidro, Clínica Maisón de Sante - Chorrillos, Clínica Aviva - Los Olivos, Clínica San Gabriel - San Miguel, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Maisón de Sante - Lima, Clínica Jesús del Norte - Independencia</t>
+  </si>
+  <si>
+    <t>Clínica Sanna  - San Borja, Clínica Bellavista - Callao, Clínica Especialidades Médicas - San Borja, Clínica El Golf - San Isidro, Clínica Maisón de Sante - Surco, Clínica Tezza - Surco, Clínica Internacional - Lima, Clínica San Pablo - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Miraflores - Miraflores, Centro Médico San Felipe - La Molina, Clínica San Felipe - Jesús María, Centro Médico San Felipe - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Delgado - Miraflores, Clínica Auna - San Isidro</t>
+  </si>
+  <si>
+    <t>Centro Médico Integramédica - Independencia, Clínica Versalles - Comas, Clínica Mundo Salud - Los Olivos, Clínica Montefiori - La Molina, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Centro Médico Ricardo Palma - Chorrillos, Centro Médico Limatambo - Callao, Clínica Limatambo - SJL, Clínica Medavan - Magdalena, Clínica Virgen del Rosario - Magdalena, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Clínica Limatambo - San Isidro, Clínica Aviva - Lima, Centro Médico Los Álamos - Surquillo, Clínica Cayetano Heredia - SMP, Centro Médico Jockey Salud - Surco, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Javier Prado - San Isidro</t>
+  </si>
+  <si>
+    <t>Clínica Good Hope - Miraflores, Clínica Maisón de Sante - Chorrillos, Clínica Aviva - Los Olivos, Clínica San Gabriel - San Miguel, Clínica Maisón de Sante - Lima, Clínica Jesús del Norte - Independencia, Clínica Tezza - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Sanna  - San Borja, Clínica Bellavista - Callao, Clínica Especialidades Médicas - San Borja, Clínica El Golf - San Isidro, Clínica Maisón de Sante - Surco, Clínica Internacional - Lima, Clínica San Pablo - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Santa Isabel - San Borja, Clínica Ricardo Palma - San Isidro, Centro Médico Internacional - San Isidro, Clínica Internacional - San Borja, Centro Médico Internacional - Surco</t>
+  </si>
+  <si>
+    <t>Centro Médico Integramédica - Independencia, Clínica Versalles - Comas, Clínica Mundo Salud - Los Olivos, Clínica Montefiori - La Molina, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Centro Médico Ricardo Palma - Chorrillos, Centro Médico Limatambo - Callao, Clínica Limatambo - SJL, Clínica Medavan - Magdalena, Clínica Virgen del Rosario - Magdalena, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Clínica Limatambo - San Isidro, Clínica Aviva - Lima, Centro Médico Los Álamos - Surquillo, Clínica Cayetano Heredia - SMP, Centro Médico Jockey Salud - Surco, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Javier Prado - San Isidro, Clínica Aviva - Los Olivos</t>
+  </si>
+  <si>
+    <t>Clínica Good Hope - Miraflores, Clínica Maisón de Sante - Chorrillos, Clínica San Gabriel - San Miguel, Clínica Maisón de Sante - Lima, Clínica Jesús del Norte - Independencia, Clínica Tezza - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Miraflores - Miraflores, Clínica Angloamericana - La Molina, Clínica Angloamericana - San Isidro, Centro Médico San Felipe - La Molina, Clínica San Felipe - Jesús María, Centro Médico San Felipe - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Montesur - Surco, Clínica Auna - San Isidro</t>
+  </si>
+  <si>
+    <t>Centro Médico La Positiva - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Cayetano Heredia - SMP, Clínica Montefiori - La Molina</t>
+  </si>
+  <si>
+    <t>Clínica Stella Maris - Pueblo Libre, Clínica Bellavista - Callao, Centro Médico Limatambo - Callao, Clínica Maisón de Sante - Lima, Clínica San Judas Tadeo - San Miguel, Clínica Limatambo - SJL, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM, Clínica Versalles - Comas, Clínica San Juan De Dios - San Luis, Clínica San Bernardo - Pueblo Libre, Clínica La Luz - Lima, Clínica Poémape - Chancay, Clínica La Solidaridad - Barranca, Centro Médico AltaSalud - Barranca, Centro Médico Medex - Surquillo, Clínica Antonio Raymondi - La Victoria, Clínica Aviva - Lima, Clínica Arthrosalud - Lima, Centro Médico Integramédica - Independencia, Clínica Maisón de Sante - Chorrillos, Clínica San Pedro - Huara, Clínica Medavan - Magdalena, Clínica San Clemente - Lince, Centro Médico Cayetano Heredia - Lince, Clínica Aviva - Los Olivos, Clínica Aviva - Lima, Clínica San Bartolomé - Huacho</t>
+  </si>
+  <si>
+    <t>Clínica San Marcos - Huara, Clínica Providencia - San Miguel, Centro Médico Ricardo Palma - Chorrillos, Clínica Sanens - Surquillo, Centro Médico Jockey Salud - Surco, Clínica Limatambo - San Isidro, Centro Médico AltaSalud - San Isidro, Clínica Vesalio - San Borja, Centro Médico Sanna - La Molina, Centro Médico Sanna - Miraflores, Clínica Good Hope - Miraflores, Clínica Corazón de Jesús - Cañete, Centro Médico Clisova - Chancay, Centro Médico Clisova - Huaral, Centro Médico Nueva Esperanza - Huaral</t>
+  </si>
+  <si>
+    <t>Clínica Jesús del Norte - Independencia, Clínica San Gabriel - San Miguel, Clínica Javier Prado - San Isidro, Clínica Tezza - Surco, Clínica Maisón de Sante - Surco</t>
+  </si>
+  <si>
+    <t>Clínica El Golf - San Isidro, Clínica Santa Isabel - San Borja, Centro Médico Sanna - Surco, Clínica Auna - San Isidro, Clínica Alvarez - Surco, Clínica Del Inca - Miraflores</t>
+  </si>
+  <si>
+    <t>Clínica San Pablo - Surco, Clínica Ricardo Palma - San Isidro, Centro Médico Sormedic - Lima, Centro Médico Urozen - San Borja</t>
+  </si>
+  <si>
+    <t>Centro Médico Limatambo - Callao, Clínica Cayetano Heredia - SMP, Clínica Maisón de Sante - Lima, Clínica MegaSalud Universal - Lima, Clínica Limatambo - SJL, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM, Clínica Versalles - Comas, Clínica San Juan De Dios - San Luis, Clínica San Bernardo - Pueblo Libre, Clínica La Luz - Lima, Clínica Poémape - Chancay, Clínica Montefiori - La Molina</t>
+  </si>
+  <si>
+    <t>Centro Médico SBC Medic - Barranco, Clínica La Solidaridad - Barranca, Centro Médico AltaSalud - Barranca, Clínica Antonio Raymondi - La Victoria,  Centro Médico Medex - Surquillo, Clínica Aviva - Lima, Clínica Arthrosalud - Lima, Clínica Bellavista - Callao, Centro Médico Integramédica - Independencia, Clínica Bellavista - Callao, Clínica Maisón de Sante - Chorrillos, Clínica San Judas Tadeo - San Miguel, Clínica San Pedro - Huara, Clínica Stella Maris - Pueblo Libre, Clínica San Clemente - Lince, Centro Médico Cayetano Heredia - Lince, Clínica Aviva - Los Olivos, Clínica San Bartolomé - Huacho</t>
+  </si>
+  <si>
+    <t>Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Providencia - San Miguel, Clínica Good Hope - Miraflores, Clínica Limatambo - San Isidro, Clínica Sanens - Surquillo, Clínica Medavan - Magdalena, Centro Médico Ricardo Palma - Chorrillos, Clínica San Marcos - Huaura, Clínica Vesalio - San Borja, Centro Médico Jockey Salud - Surco, Centro Médico AltaSalud - San Isidro, Centro Médico Sanna - La Molina, Centro Médico Sanna - Miraflores, Clínica Higuereta - Miraflores, Clínica Corazón de Jesús - Cañete, Centro Médico Clisova - Chancay, Centro Médico Clisova - Huaral, Centro Médico Nueva Esperanza - Huaral</t>
+  </si>
+  <si>
+    <t>Centro Médico SBC Medic - Barranco, Clínica La Solidaridad - Barranca, Centro Médico AltaSalud - Barranca, Clínica Antonio Raymondi - La Victoria,  Centro Médico Medex - Surquillo, Clínica Aviva - Lima, Clínica Arthrosalud - Lima, Clínica Bellavista - Callao, Centro Médico Integramédica - Independencia, Clínica Bellavista - Callao, Clínica Maisón de Sante - Chorrillos, Clínica San Judas Tadeo - San Miguel, Clínica San Pedro - Huara, Clínica Stella Maris - Pueblo Libre, Clínica San Clemente - Lince, Centro Médico Cayetano Heredia - Lince, Clínica Aviva - Los Olivos, Clínica San Bartolomé - Huacho, Clínica Medavan - Magdalena</t>
+  </si>
+  <si>
+    <t>Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Providencia - San Miguel, Clínica Good Hope - Miraflores, Clínica Limatambo - San Isidro, Clínica Sanens - Surquillo, Centro Médico Ricardo Palma - Chorrillos, Clínica San Marcos - Huaura, Clínica Vesalio - San Borja, Centro Médico Jockey Salud - Surco, Centro Médico AltaSalud - San Isidro, Centro Médico Sanna - La Molina, Centro Médico Sanna - Miraflores, Clínica Higuereta - Miraflores, Clínica Corazón de Jesús - Cañete, Centro Médico Clisova - Chancay, Centro Médico Clisova - Huaral, Centro Médico Nueva Esperanza - Huaral</t>
+  </si>
+  <si>
+    <t>Clínica Sanna  - San Borja, Clínica Montesur - Surco, Clínica San Pablo - Asia</t>
+  </si>
+  <si>
+    <t>Clínica Internacional - Lima, Centro Médico Internacional - San Isidro, Centro Médico Internacional - Surco, Centro Médico Internacional - La Molina, Clínica Internacional - San Borja, Clínica Delgado - Miraflores, Centro Médico San Felipe - La Molina, Clínica Angloamericana - San Isidro, Clínica Angloamericana - La Molina, Clínica San Felipe - Jesús María</t>
+  </si>
+  <si>
+    <t>Salud Total</t>
+  </si>
+  <si>
+    <t>Red Primaria</t>
+  </si>
+  <si>
+    <t>Red Secundaria</t>
+  </si>
+  <si>
+    <t>S/65 al 90%</t>
+  </si>
+  <si>
+    <t>S/650 al 80%</t>
+  </si>
+  <si>
+    <t>Centro Médico Mapfre - Independencia, Centro Médico Mapfre - Magdalena, Centro Médico Mapfre - San Miguel, Centro Médico Mapfre - Surco, Clínica Integramédica - San Isidro</t>
+  </si>
+  <si>
+    <t>Clínica Ricardo Palma - San Isidro</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -560,16 +719,27 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -592,15 +762,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -903,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -937,19 +1132,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
+      <c r="D2" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>146</v>
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -957,19 +1152,19 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
+      <c r="D3" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
-        <v>140</v>
+      <c r="F3" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -977,19 +1172,19 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
-        <v>15</v>
+      <c r="D4" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
-        <v>141</v>
+      <c r="F4" s="2" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1000,16 +1195,16 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1020,16 +1215,16 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1040,16 +1235,16 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1057,19 +1252,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1077,19 +1272,19 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1097,19 +1292,19 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1120,16 +1315,16 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1140,16 +1335,16 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1160,16 +1355,16 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1180,16 +1375,16 @@
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1200,16 +1395,16 @@
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>108</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1217,19 +1412,19 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1237,19 +1432,19 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1257,19 +1452,19 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1277,19 +1472,19 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
         <v>36</v>
       </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" t="s">
-        <v>39</v>
-      </c>
       <c r="E19" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1297,19 +1492,19 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1317,19 +1512,19 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1337,19 +1532,19 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1357,19 +1552,19 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F23" t="s">
-        <v>108</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1377,19 +1572,19 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F24" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1397,19 +1592,19 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F25" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1417,19 +1612,19 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1437,19 +1632,19 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E27" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1457,19 +1652,19 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F28" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1477,19 +1672,19 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1497,19 +1692,19 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F30" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1517,19 +1712,19 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F31" t="s">
-        <v>108</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1537,19 +1732,19 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E32" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1557,19 +1752,19 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F33" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1577,19 +1772,19 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="E34" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>56</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1597,19 +1792,19 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" t="s">
         <v>49</v>
       </c>
-      <c r="C35" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" t="s">
-        <v>57</v>
-      </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1617,19 +1812,19 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E36" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F36" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1637,19 +1832,19 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="E37" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F37" t="s">
-        <v>52</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1657,19 +1852,19 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E38" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F38" t="s">
-        <v>54</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1677,19 +1872,19 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E39" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>56</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1697,19 +1892,19 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E40" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1717,19 +1912,19 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E41" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1737,19 +1932,19 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E42" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F42" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1757,19 +1952,19 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E43" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F43" t="s">
-        <v>52</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1777,19 +1972,19 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C44" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E44" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F44" t="s">
-        <v>54</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1797,19 +1992,19 @@
         <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="E45" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>56</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1817,16 +2012,16 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C46" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="E46" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F46" t="s">
         <v>170</v>
@@ -1837,1777 +2032,2040 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C47" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>32</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E48" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F48" t="s">
-        <v>68</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E49" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F49" t="s">
-        <v>70</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D50" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E50" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>71</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C51" t="s">
         <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E51" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>68</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B52" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E52" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>75</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E53" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F53" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C54" t="s">
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E54" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F54" t="s">
-        <v>68</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E55" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F55" t="s">
-        <v>75</v>
+        <v>181</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="E56" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>81</v>
+        <v>182</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>65</v>
+      <c r="A57" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E57" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>83</v>
+        <v>180</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E58" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="F58" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="E59" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>88</v>
+        <v>183</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="C60" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="E60" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="F60" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D61" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="E61" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="F61" t="s">
-        <v>93</v>
+        <v>185</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
         <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="E62" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="F62" t="s">
-        <v>96</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B63" t="s">
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D63" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="E63" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="F63" t="s">
-        <v>98</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>65</v>
-      </c>
-      <c r="B64" t="s">
-        <v>99</v>
+        <v>60</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E64" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="F64" t="s">
-        <v>88</v>
+        <v>188</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="E65" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="F65" t="s">
-        <v>100</v>
+        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B66" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D66" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="E66" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="F66" t="s">
-        <v>101</v>
+        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B67" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D67" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="E67" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F67" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B68" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C68" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E68" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F68" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B69" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C69" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F69" t="s">
-        <v>104</v>
+        <v>194</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B70" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C70" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D70" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="E70" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="F70" t="s">
-        <v>32</v>
+        <v>200</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B71" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C71" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="D71" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="E71" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="F71" t="s">
-        <v>108</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B72" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D72" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E72" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F72" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B73" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="C73" t="s">
+        <v>82</v>
+      </c>
+      <c r="D73" t="s">
+        <v>190</v>
+      </c>
+      <c r="E73" t="s">
+        <v>72</v>
+      </c>
+      <c r="F73" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" t="s">
+        <v>84</v>
+      </c>
+      <c r="E74" t="s">
+        <v>74</v>
+      </c>
+      <c r="F74" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B75" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" t="s">
         <v>11</v>
       </c>
-      <c r="D73" t="s">
-        <v>37</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="D75" t="s">
+        <v>36</v>
+      </c>
+      <c r="E75" t="s">
         <v>24</v>
       </c>
-      <c r="F73" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>65</v>
-      </c>
-      <c r="B74" t="s">
-        <v>109</v>
-      </c>
-      <c r="C74" t="s">
-        <v>14</v>
-      </c>
-      <c r="D74" t="s">
-        <v>44</v>
-      </c>
-      <c r="E74" t="s">
-        <v>38</v>
-      </c>
-      <c r="F74" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75" t="s">
-        <v>109</v>
-      </c>
-      <c r="C75" t="s">
-        <v>17</v>
-      </c>
-      <c r="D75" t="s">
-        <v>46</v>
-      </c>
-      <c r="E75" t="s">
-        <v>28</v>
-      </c>
       <c r="F75" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>65</v>
-      </c>
-      <c r="B76" t="s">
-        <v>109</v>
+        <v>60</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="C76" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E76" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F76" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>65</v>
-      </c>
-      <c r="B77" t="s">
-        <v>109</v>
+        <v>60</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E77" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F77" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B78" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="C78" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D78" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E78" t="s">
         <v>13</v>
       </c>
       <c r="F78" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B79" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="D79" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="E79" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F79" t="s">
-        <v>108</v>
+        <v>203</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B80" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="C80" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D80" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="E80" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="F80" t="s">
-        <v>88</v>
+        <v>204</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B81" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="C81" t="s">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="D81" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="E81" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>111</v>
+        <v>168</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B82" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D82" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="E82" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F82" t="s">
-        <v>112</v>
+        <v>191</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D83" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E83" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F83" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B84" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="C84" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E84" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F84" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B85" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="C85" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="E85" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F85" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B86" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="C86" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D86" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F86" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B87" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="D87" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E87" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F87" t="s">
-        <v>108</v>
+        <v>195</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="B88" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="C88" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="D88" t="s">
-        <v>149</v>
+        <v>41</v>
       </c>
       <c r="E88" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="F88" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="B89" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="D89" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="E89" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>117</v>
+      <c r="A90" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="C90" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D90" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="E90" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="F90" t="s">
-        <v>151</v>
+        <v>205</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B91" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D91" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="E91" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F91" t="s">
-        <v>155</v>
+        <v>206</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B92" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="C92" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D92" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E92" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="F92" t="s">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B93" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="C93" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>123</v>
+        <v>46</v>
       </c>
       <c r="E93" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F93" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B94" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="C94" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="E94" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B95" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C95" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="D95" t="s">
-        <v>149</v>
+        <v>93</v>
       </c>
       <c r="E95" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="F95" t="s">
-        <v>120</v>
+        <v>210</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B96" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C96" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D96" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="E96" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="F96" t="s">
-        <v>154</v>
+        <v>211</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B97" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D97" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="E97" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="F97" t="s">
-        <v>157</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B98" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="C98" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D98" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="E98" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F98" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B99" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C99" t="s">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="D99" t="s">
-        <v>149</v>
+        <v>15</v>
       </c>
       <c r="E99" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="F99" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B100" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C100" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="E100" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F100" t="s">
-        <v>154</v>
+        <v>214</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B101" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="C101" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D101" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="E101" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="F101" t="s">
-        <v>157</v>
+        <v>205</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B102" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="C102" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D102" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="E102" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F102" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B103" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="C103" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D103" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="E103" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F103" t="s">
-        <v>152</v>
+        <v>213</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B104" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="C104" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="D104" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="E104" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="F104" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B105" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="C105" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D105" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="E105" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F105" t="s">
-        <v>154</v>
+        <v>209</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B106" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="C106" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D106" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="E106" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="F106" t="s">
-        <v>159</v>
+        <v>205</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B107" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="C107" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D107" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="E107" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F107" t="s">
-        <v>160</v>
+        <v>212</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B108" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="C108" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D108" t="s">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="E108" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F108" t="s">
-        <v>152</v>
+        <v>213</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B109" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="C109" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="D109" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="E109" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="F109" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B110" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="C110" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D110" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E110" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F110" t="s">
-        <v>154</v>
+        <v>209</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B111" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="C111" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D111" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="E111" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F111" t="s">
-        <v>159</v>
+        <v>205</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B112" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="C112" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D112" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E112" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F112" t="s">
-        <v>160</v>
+        <v>212</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B113" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="C113" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D113" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E113" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F113" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B114" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="C114" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E114" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F114" t="s">
-        <v>162</v>
+        <v>216</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B115" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="C115" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D115" t="s">
-        <v>161</v>
+        <v>29</v>
       </c>
       <c r="E115" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F115" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B116" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="C116" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D116" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="E116" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F116" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B117" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="C117" t="s">
-        <v>119</v>
+        <v>31</v>
       </c>
       <c r="D117" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="E117" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="F117" t="s">
-        <v>120</v>
+        <v>211</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B118" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="C118" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D118" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="E118" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F118" t="s">
-        <v>154</v>
+        <v>217</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B119" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C119" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D119" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="E119" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F119" t="s">
-        <v>159</v>
+        <v>205</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B120" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C120" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D120" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E120" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F120" t="s">
-        <v>160</v>
+        <v>212</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B121" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C121" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D121" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E121" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F121" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B122" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C122" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D122" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E122" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F122" t="s">
-        <v>162</v>
+        <v>216</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B123" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C123" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D123" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E123" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F123" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B124" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C124" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D124" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E124" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F124" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B125" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C125" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="D125" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="E125" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F125" t="s">
-        <v>166</v>
+        <v>211</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="B126" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="C126" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="D126" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="E126" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="F126" t="s">
-        <v>135</v>
+        <v>217</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="C127" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="D127" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E127" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F127" t="s">
-        <v>148</v>
+        <v>218</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="C128" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="D128" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="E128" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="F128" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B129" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="C129" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="D129" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="E129" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="F129" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B130" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="C130" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D130" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E130" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F130" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B131" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="C131" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="D131" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="E131" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F131" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B132" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="C132" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D132" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E132" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F132" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B133" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="C133" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>139</v>
+        <v>44</v>
       </c>
       <c r="E133" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F133" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B134" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="C134" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D134" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="E134" t="s">
         <v>16</v>
       </c>
       <c r="F134" t="s">
-        <v>113</v>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>101</v>
+      </c>
+      <c r="B135" t="s">
+        <v>107</v>
+      </c>
+      <c r="C135" t="s">
+        <v>17</v>
+      </c>
+      <c r="D135" t="s">
+        <v>109</v>
+      </c>
+      <c r="E135" t="s">
+        <v>16</v>
+      </c>
+      <c r="F135" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>101</v>
+      </c>
+      <c r="B136" t="s">
+        <v>107</v>
+      </c>
+      <c r="C136" t="s">
+        <v>20</v>
+      </c>
+      <c r="D136" t="s">
+        <v>33</v>
+      </c>
+      <c r="E136" t="s">
+        <v>16</v>
+      </c>
+      <c r="F136" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>101</v>
+      </c>
+      <c r="B137" t="s">
+        <v>219</v>
+      </c>
+      <c r="C137" t="s">
+        <v>220</v>
+      </c>
+      <c r="D137" t="s">
+        <v>65</v>
+      </c>
+      <c r="E137" t="s">
+        <v>74</v>
+      </c>
+      <c r="F137" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>101</v>
+      </c>
+      <c r="B138" t="s">
+        <v>219</v>
+      </c>
+      <c r="C138" t="s">
+        <v>221</v>
+      </c>
+      <c r="D138" t="s">
+        <v>222</v>
+      </c>
+      <c r="E138" t="s">
+        <v>223</v>
+      </c>
+      <c r="F138" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>120</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\COTI SALUD 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C94063-557E-4C2D-9274-D89899604713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0317B73-F799-442C-9CFE-E2D6FE57CA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -278,9 +278,6 @@
     <t>S/45 al 100%</t>
   </si>
   <si>
-    <t>Angloamericana, San Felipe</t>
-  </si>
-  <si>
     <t>S/125 al 60%</t>
   </si>
   <si>
@@ -338,27 +335,15 @@
     <t>S/25 al 90%</t>
   </si>
   <si>
-    <t>Mapfre Independencia, Mapfre Magdalena, Mapfre San Miguel, Mapfre Surco</t>
-  </si>
-  <si>
-    <t>Javier Prado, Cm Jockey Salud, Limatambo, San Gabriel, Good Hope, Vesalio, Tezza, Bellavista, Centenario Peruano Japonesa, Stella Maris, La Luz</t>
-  </si>
-  <si>
     <t>Trébol Salud</t>
   </si>
   <si>
-    <t>Delgado, San Pablo</t>
-  </si>
-  <si>
     <t>S/110 al 65%</t>
   </si>
   <si>
     <t>S/130 al 60%</t>
   </si>
   <si>
-    <t>Montefiori, Providencia, Medavan, Cayetano Heredia, San Judas Tadeo, Santa Martha Del Sur, Especialidades Médicas, Jesús Del Norte, Hogar  San Juan De Dios, San Juan Bautista</t>
-  </si>
-  <si>
     <t>Cubierto al 90%</t>
   </si>
   <si>
@@ -368,9 +353,6 @@
     <t>S/105 al 65%</t>
   </si>
   <si>
-    <t>Ricardo Palma, Sanna San Borja, Maisón De Santé, El Golf, Santa Isabel, Internacional San Borja, Internacional Lima</t>
-  </si>
-  <si>
     <t>Plan Vital</t>
   </si>
   <si>
@@ -699,6 +681,24 @@
   </si>
   <si>
     <t>Clínica Ricardo Palma - San Isidro</t>
+  </si>
+  <si>
+    <t>Centro Médico Mapfre - Independencia, Centro Médico Mapfre - Magdalena, Centro Médico Mapfre - San Miguel, Centro Médico Mapfre - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Montefiori - La Molina, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Clínica Jesús del Norte - Independencia, Centro Médico Medex - Surquillo, Clínica Los Andes - Miraflores, Clínica San Juan Bautista - SJL, Clínica Aviva - Los Olivos, Clínica Virgen del Rosario - Magdalena, Clínica Cayetano Heredia - SMP, Clínica Santa Martha del Sur - SJM, Clínica Limatambo - SJL, Centro Médico Limatambo - Callao, Centro Médico Suiza Lab - Miraflores, Centro Médico Suiza Lab - Surco, Clínica Mundo Salud - Los Olivos, Clínica Medavan - Magdalena, Clínica Santa María - Surquillo, Clínica Especialidades Médicas - San Borja, Clínica Maisón de Sante - Chorrillos, Clínica Maisón de Sante - Lima, Clínica San Juan De Dios - San Luis, Clínica San Vicente - SMP, Clínica Integramédica - San Isidro</t>
+  </si>
+  <si>
+    <t>Clínica Javier Prado - San Isidro, Clínica San Gabriel - San Miguel, Clínica Tezza - Surco, Clínica Centenario Peruano Japonesa - Pueblo Libre, Centro Médico Jockey Salud - Surco, Clínica Good Hope - Miraflores, Clínica Bellavista - Callao, Clínica Stella Maris - Pueblo Libre, Clínica Limatambo - San Isidro, Clínica Vesalio - San Borja, Centro Médico Ricardo Palma - Chorrillos, Clínica La Luz - Lima</t>
+  </si>
+  <si>
+    <t>Clínica Delgado - Miraflores, Clínica Auna - San Isidro, Clínica Ricardo Palma - San Isidro, Clínica San Pablo - Surco, Clínica San Pablo - Asia</t>
+  </si>
+  <si>
+    <t>Clínica Santa Isabel - San Borja, Clínica Sanna  - San Borja, Clínica El Golf - San Isidro, Centro Médico Sanna - La Molina, Clínica Maisón de Sante - Surco, Clínica Internacional - Lima, Clínica Internacional - San Borja</t>
+  </si>
+  <si>
+    <t>Clínica Angloamericana - La Molina, Clínica Angloamericana - San Isidro, Centro Médico San Felipe - La Molina, Clínica San Felipe - Jesús María, Clínica Miraflores - Miraflores, Clínica San Felipe - Jesús María, Clínica Miraflores - Miraflores, Clínica Montesur - Surco</t>
   </si>
 </sst>
 </file>
@@ -777,7 +777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -795,7 +795,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1132,7 +1131,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -1144,7 +1143,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1152,7 +1151,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>11</v>
@@ -1164,7 +1163,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1172,19 +1171,19 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1204,7 +1203,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1224,7 +1223,7 @@
         <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1244,7 +1243,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1264,7 +1263,7 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1284,7 +1283,7 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1304,7 +1303,7 @@
         <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1324,7 +1323,7 @@
         <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1344,7 +1343,7 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1364,7 +1363,7 @@
         <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1384,7 +1383,7 @@
         <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1404,7 +1403,7 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1418,13 +1417,13 @@
         <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1444,7 +1443,7 @@
         <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1458,13 +1457,13 @@
         <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
         <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1484,7 +1483,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1504,7 +1503,7 @@
         <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1524,7 +1523,7 @@
         <v>37</v>
       </c>
       <c r="F21" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1544,7 +1543,7 @@
         <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1564,7 +1563,7 @@
         <v>28</v>
       </c>
       <c r="F23" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1584,7 +1583,7 @@
         <v>13</v>
       </c>
       <c r="F24" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1604,7 +1603,7 @@
         <v>13</v>
       </c>
       <c r="F25" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1624,7 +1623,7 @@
         <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1644,7 +1643,7 @@
         <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1664,7 +1663,7 @@
         <v>26</v>
       </c>
       <c r="F28" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1684,7 +1683,7 @@
         <v>37</v>
       </c>
       <c r="F29" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1704,7 +1703,7 @@
         <v>28</v>
       </c>
       <c r="F30" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1724,7 +1723,7 @@
         <v>28</v>
       </c>
       <c r="F31" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1744,7 +1743,7 @@
         <v>13</v>
       </c>
       <c r="F32" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1764,7 +1763,7 @@
         <v>13</v>
       </c>
       <c r="F33" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1784,7 +1783,7 @@
         <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1804,7 +1803,7 @@
         <v>50</v>
       </c>
       <c r="F35" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1824,7 +1823,7 @@
         <v>37</v>
       </c>
       <c r="F36" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1844,7 +1843,7 @@
         <v>28</v>
       </c>
       <c r="F37" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1864,7 +1863,7 @@
         <v>13</v>
       </c>
       <c r="F38" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1884,7 +1883,7 @@
         <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1904,7 +1903,7 @@
         <v>24</v>
       </c>
       <c r="F40" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1924,7 +1923,7 @@
         <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1944,7 +1943,7 @@
         <v>37</v>
       </c>
       <c r="F42" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1964,7 +1963,7 @@
         <v>28</v>
       </c>
       <c r="F43" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1984,7 +1983,7 @@
         <v>13</v>
       </c>
       <c r="F44" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2004,7 +2003,7 @@
         <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2024,7 +2023,7 @@
         <v>24</v>
       </c>
       <c r="F46" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2044,7 +2043,7 @@
         <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2064,7 +2063,7 @@
         <v>37</v>
       </c>
       <c r="F48" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2084,7 +2083,7 @@
         <v>13</v>
       </c>
       <c r="F49" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2104,7 +2103,7 @@
         <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2124,7 +2123,7 @@
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2144,7 +2143,7 @@
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2164,7 +2163,7 @@
         <v>34</v>
       </c>
       <c r="F53" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2184,7 +2183,7 @@
         <v>37</v>
       </c>
       <c r="F54" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2204,7 +2203,7 @@
         <v>16</v>
       </c>
       <c r="F55" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2224,7 +2223,7 @@
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2244,7 +2243,7 @@
         <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2264,7 +2263,7 @@
         <v>28</v>
       </c>
       <c r="F58" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2284,7 +2283,7 @@
         <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2304,7 +2303,7 @@
         <v>34</v>
       </c>
       <c r="F60" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2324,7 +2323,7 @@
         <v>72</v>
       </c>
       <c r="F61" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2344,7 +2343,7 @@
         <v>28</v>
       </c>
       <c r="F62" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2364,14 +2363,14 @@
         <v>13</v>
       </c>
       <c r="F63" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>60</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" t="s">
         <v>7</v>
       </c>
       <c r="C64" t="s">
@@ -2384,7 +2383,7 @@
         <v>16</v>
       </c>
       <c r="F64" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2404,7 +2403,7 @@
         <v>77</v>
       </c>
       <c r="F65" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2424,7 +2423,7 @@
         <v>74</v>
       </c>
       <c r="F66" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2444,7 +2443,7 @@
         <v>24</v>
       </c>
       <c r="F67" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2464,7 +2463,7 @@
         <v>28</v>
       </c>
       <c r="F68" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2484,7 +2483,7 @@
         <v>16</v>
       </c>
       <c r="F69" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2504,7 +2503,7 @@
         <v>16</v>
       </c>
       <c r="F70" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2524,7 +2523,7 @@
         <v>34</v>
       </c>
       <c r="F71" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2544,7 +2543,7 @@
         <v>72</v>
       </c>
       <c r="F72" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2558,17 +2557,17 @@
         <v>82</v>
       </c>
       <c r="D73" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E73" t="s">
         <v>72</v>
       </c>
       <c r="F73" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
+      <c r="A74" t="s">
         <v>60</v>
       </c>
       <c r="B74" t="s">
@@ -2584,11 +2583,11 @@
         <v>74</v>
       </c>
       <c r="F74" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
+      <c r="A75" t="s">
         <v>60</v>
       </c>
       <c r="B75" t="s">
@@ -2604,14 +2603,14 @@
         <v>24</v>
       </c>
       <c r="F75" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>60</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" t="s">
         <v>83</v>
       </c>
       <c r="C76" t="s">
@@ -2624,14 +2623,14 @@
         <v>37</v>
       </c>
       <c r="F76" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>60</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B77" t="s">
         <v>83</v>
       </c>
       <c r="C77" t="s">
@@ -2644,7 +2643,7 @@
         <v>28</v>
       </c>
       <c r="F77" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2664,7 +2663,7 @@
         <v>13</v>
       </c>
       <c r="F78" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2684,7 +2683,7 @@
         <v>13</v>
       </c>
       <c r="F79" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2704,7 +2703,7 @@
         <v>13</v>
       </c>
       <c r="F80" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2718,13 +2717,13 @@
         <v>82</v>
       </c>
       <c r="D81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2732,7 +2731,7 @@
         <v>60</v>
       </c>
       <c r="B82" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C82" t="s">
         <v>8</v>
@@ -2744,7 +2743,7 @@
         <v>74</v>
       </c>
       <c r="F82" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2752,7 +2751,7 @@
         <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C83" t="s">
         <v>11</v>
@@ -2764,7 +2763,7 @@
         <v>24</v>
       </c>
       <c r="F83" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2772,7 +2771,7 @@
         <v>60</v>
       </c>
       <c r="B84" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
@@ -2784,7 +2783,7 @@
         <v>37</v>
       </c>
       <c r="F84" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2792,7 +2791,7 @@
         <v>60</v>
       </c>
       <c r="B85" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
         <v>17</v>
@@ -2804,7 +2803,7 @@
         <v>28</v>
       </c>
       <c r="F85" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2812,7 +2811,7 @@
         <v>60</v>
       </c>
       <c r="B86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C86" t="s">
         <v>20</v>
@@ -2824,7 +2823,7 @@
         <v>28</v>
       </c>
       <c r="F86" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2832,7 +2831,7 @@
         <v>60</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C87" t="s">
         <v>31</v>
@@ -2844,7 +2843,7 @@
         <v>13</v>
       </c>
       <c r="F87" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2852,7 +2851,7 @@
         <v>60</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C88" t="s">
         <v>32</v>
@@ -2864,7 +2863,7 @@
         <v>13</v>
       </c>
       <c r="F88" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -2872,7 +2871,7 @@
         <v>60</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C89" t="s">
         <v>82</v>
@@ -2884,55 +2883,55 @@
         <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="7" t="s">
+      <c r="A90" t="s">
+        <v>87</v>
+      </c>
+      <c r="B90" t="s">
         <v>88</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>89</v>
       </c>
-      <c r="C90" t="s">
-        <v>90</v>
-      </c>
       <c r="D90" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E90" t="s">
         <v>74</v>
       </c>
       <c r="F90" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>87</v>
+      </c>
+      <c r="B91" t="s">
         <v>88</v>
-      </c>
-      <c r="B91" t="s">
-        <v>89</v>
       </c>
       <c r="C91" t="s">
         <v>8</v>
       </c>
       <c r="D91" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E91" t="s">
         <v>26</v>
       </c>
       <c r="F91" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>87</v>
+      </c>
+      <c r="B92" t="s">
         <v>88</v>
-      </c>
-      <c r="B92" t="s">
-        <v>89</v>
       </c>
       <c r="C92" t="s">
         <v>11</v>
@@ -2941,18 +2940,18 @@
         <v>45</v>
       </c>
       <c r="E92" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F92" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>87</v>
+      </c>
+      <c r="B93" t="s">
         <v>88</v>
-      </c>
-      <c r="B93" t="s">
-        <v>89</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
@@ -2964,15 +2963,15 @@
         <v>13</v>
       </c>
       <c r="F93" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>87</v>
+      </c>
+      <c r="B94" t="s">
         <v>88</v>
-      </c>
-      <c r="B94" t="s">
-        <v>89</v>
       </c>
       <c r="C94" t="s">
         <v>17</v>
@@ -2984,75 +2983,75 @@
         <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>87</v>
+      </c>
+      <c r="B95" t="s">
         <v>88</v>
-      </c>
-      <c r="B95" t="s">
-        <v>89</v>
       </c>
       <c r="C95" t="s">
         <v>20</v>
       </c>
       <c r="D95" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E95" t="s">
         <v>34</v>
       </c>
       <c r="F95" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>87</v>
+      </c>
+      <c r="B96" t="s">
         <v>88</v>
-      </c>
-      <c r="B96" t="s">
-        <v>89</v>
       </c>
       <c r="C96" t="s">
         <v>31</v>
       </c>
       <c r="D96" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E96" t="s">
         <v>72</v>
       </c>
       <c r="F96" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C97" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D97" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E97" t="s">
         <v>74</v>
       </c>
       <c r="F97" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B98" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C98" t="s">
         <v>8</v>
@@ -3064,15 +3063,15 @@
         <v>16</v>
       </c>
       <c r="F98" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B99" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C99" t="s">
         <v>11</v>
@@ -3084,55 +3083,55 @@
         <v>19</v>
       </c>
       <c r="F99" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B100" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C100" t="s">
         <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E100" t="s">
         <v>34</v>
       </c>
       <c r="F100" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B101" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C101" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D101" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E101" t="s">
         <v>74</v>
       </c>
       <c r="F101" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B102" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C102" t="s">
         <v>8</v>
@@ -3144,15 +3143,15 @@
         <v>37</v>
       </c>
       <c r="F102" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B103" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C103" t="s">
         <v>11</v>
@@ -3164,35 +3163,35 @@
         <v>16</v>
       </c>
       <c r="F103" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B104" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C104" t="s">
         <v>14</v>
       </c>
       <c r="D104" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E104" t="s">
         <v>19</v>
       </c>
       <c r="F104" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B105" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C105" t="s">
         <v>17</v>
@@ -3204,35 +3203,35 @@
         <v>34</v>
       </c>
       <c r="F105" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B106" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C106" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D106" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E106" t="s">
         <v>74</v>
       </c>
       <c r="F106" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B107" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C107" t="s">
         <v>8</v>
@@ -3244,35 +3243,35 @@
         <v>37</v>
       </c>
       <c r="F107" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B108" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C108" t="s">
         <v>11</v>
       </c>
       <c r="D108" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E108" t="s">
         <v>13</v>
       </c>
       <c r="F108" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B109" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C109" t="s">
         <v>14</v>
@@ -3284,15 +3283,15 @@
         <v>16</v>
       </c>
       <c r="F109" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B110" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C110" t="s">
         <v>17</v>
@@ -3304,35 +3303,35 @@
         <v>19</v>
       </c>
       <c r="F110" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B111" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C111" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D111" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E111" t="s">
         <v>74</v>
       </c>
       <c r="F111" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B112" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C112" t="s">
         <v>8</v>
@@ -3344,15 +3343,15 @@
         <v>24</v>
       </c>
       <c r="F112" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B113" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C113" t="s">
         <v>11</v>
@@ -3364,15 +3363,15 @@
         <v>26</v>
       </c>
       <c r="F113" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B114" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C114" t="s">
         <v>14</v>
@@ -3384,15 +3383,15 @@
         <v>28</v>
       </c>
       <c r="F114" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B115" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C115" t="s">
         <v>17</v>
@@ -3404,15 +3403,15 @@
         <v>13</v>
       </c>
       <c r="F115" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B116" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C116" t="s">
         <v>20</v>
@@ -3424,35 +3423,35 @@
         <v>16</v>
       </c>
       <c r="F116" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B117" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C117" t="s">
         <v>31</v>
       </c>
       <c r="D117" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E117" t="s">
         <v>19</v>
       </c>
       <c r="F117" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B118" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C118" t="s">
         <v>32</v>
@@ -3464,35 +3463,35 @@
         <v>34</v>
       </c>
       <c r="F118" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B119" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C119" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D119" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E119" t="s">
         <v>74</v>
       </c>
       <c r="F119" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B120" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C120" t="s">
         <v>8</v>
@@ -3504,15 +3503,15 @@
         <v>24</v>
       </c>
       <c r="F120" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B121" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C121" t="s">
         <v>11</v>
@@ -3524,15 +3523,15 @@
         <v>26</v>
       </c>
       <c r="F121" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B122" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C122" t="s">
         <v>14</v>
@@ -3544,15 +3543,15 @@
         <v>37</v>
       </c>
       <c r="F122" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B123" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C123" t="s">
         <v>17</v>
@@ -3564,15 +3563,15 @@
         <v>28</v>
       </c>
       <c r="F123" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B124" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C124" t="s">
         <v>20</v>
@@ -3584,15 +3583,15 @@
         <v>28</v>
       </c>
       <c r="F124" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B125" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C125" t="s">
         <v>31</v>
@@ -3604,15 +3603,15 @@
         <v>13</v>
       </c>
       <c r="F125" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B126" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C126" t="s">
         <v>32</v>
@@ -3624,15 +3623,15 @@
         <v>13</v>
       </c>
       <c r="F126" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B127" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C127" t="s">
         <v>82</v>
@@ -3644,35 +3643,35 @@
         <v>19</v>
       </c>
       <c r="F127" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>100</v>
+      </c>
+      <c r="B128" t="s">
         <v>101</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
         <v>102</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
         <v>103</v>
-      </c>
-      <c r="D128" t="s">
-        <v>104</v>
       </c>
       <c r="E128" t="s">
         <v>74</v>
       </c>
       <c r="F128" t="s">
-        <v>105</v>
+        <v>220</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>100</v>
+      </c>
+      <c r="B129" t="s">
         <v>101</v>
-      </c>
-      <c r="B129" t="s">
-        <v>102</v>
       </c>
       <c r="C129" t="s">
         <v>8</v>
@@ -3684,15 +3683,15 @@
         <v>37</v>
       </c>
       <c r="F129" t="s">
-        <v>111</v>
+        <v>221</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>100</v>
+      </c>
+      <c r="B130" t="s">
         <v>101</v>
-      </c>
-      <c r="B130" t="s">
-        <v>102</v>
       </c>
       <c r="C130" t="s">
         <v>11</v>
@@ -3704,18 +3703,18 @@
         <v>28</v>
       </c>
       <c r="F130" t="s">
-        <v>106</v>
+        <v>222</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B131" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C131" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D131" t="s">
         <v>69</v>
@@ -3724,15 +3723,15 @@
         <v>74</v>
       </c>
       <c r="F131" t="s">
-        <v>105</v>
+        <v>220</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B132" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C132" t="s">
         <v>8</v>
@@ -3744,15 +3743,15 @@
         <v>24</v>
       </c>
       <c r="F132" t="s">
-        <v>111</v>
+        <v>221</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B133" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C133" t="s">
         <v>11</v>
@@ -3764,15 +3763,15 @@
         <v>26</v>
       </c>
       <c r="F133" t="s">
-        <v>106</v>
+        <v>222</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B134" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C134" t="s">
         <v>14</v>
@@ -3784,35 +3783,35 @@
         <v>16</v>
       </c>
       <c r="F134" t="s">
-        <v>108</v>
+        <v>223</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B135" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C135" t="s">
         <v>17</v>
       </c>
       <c r="D135" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E135" t="s">
         <v>16</v>
       </c>
       <c r="F135" t="s">
-        <v>115</v>
+        <v>224</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B136" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C136" t="s">
         <v>20</v>
@@ -3824,18 +3823,18 @@
         <v>16</v>
       </c>
       <c r="F136" t="s">
-        <v>85</v>
+        <v>225</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B137" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C137" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D137" t="s">
         <v>65</v>
@@ -3844,27 +3843,27 @@
         <v>74</v>
       </c>
       <c r="F137" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B138" t="s">
+        <v>213</v>
+      </c>
+      <c r="C138" t="s">
+        <v>215</v>
+      </c>
+      <c r="D138" t="s">
+        <v>216</v>
+      </c>
+      <c r="E138" t="s">
+        <v>217</v>
+      </c>
+      <c r="F138" t="s">
         <v>219</v>
-      </c>
-      <c r="C138" t="s">
-        <v>221</v>
-      </c>
-      <c r="D138" t="s">
-        <v>222</v>
-      </c>
-      <c r="E138" t="s">
-        <v>223</v>
-      </c>
-      <c r="F138" t="s">
-        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -3886,186 +3885,186 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B13" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B14" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B15" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B17" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\COTI SALUD 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0317B73-F799-442C-9CFE-E2D6FE57CA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4B08CC-054B-4C75-90BC-5F43ECEA97C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REDES" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="228">
   <si>
     <t>Aseguradora</t>
   </si>
@@ -533,9 +533,6 @@
     <t>Clínica Angloamericana - La Molina, Clínica Angloamericana - San Isidro</t>
   </si>
   <si>
-    <t xml:space="preserve"> Clínica Santa Isabel - San Borja, Clínica Internacional - San Borja,</t>
-  </si>
-  <si>
     <t>Centro Médico Limatambo - Callao, Clínica Maisón de Sante - Lima, Clínica Maisón de Sante - Chorrillos, Clínica Versalles - Comas, Clínica Mundo Salud - Los Olivos, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM</t>
   </si>
   <si>
@@ -650,9 +647,6 @@
     <t>Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Providencia - San Miguel, Clínica Good Hope - Miraflores, Clínica Limatambo - San Isidro, Clínica Sanens - Surquillo, Clínica Medavan - Magdalena, Centro Médico Ricardo Palma - Chorrillos, Clínica San Marcos - Huaura, Clínica Vesalio - San Borja, Centro Médico Jockey Salud - Surco, Centro Médico AltaSalud - San Isidro, Centro Médico Sanna - La Molina, Centro Médico Sanna - Miraflores, Clínica Higuereta - Miraflores, Clínica Corazón de Jesús - Cañete, Centro Médico Clisova - Chancay, Centro Médico Clisova - Huaral, Centro Médico Nueva Esperanza - Huaral</t>
   </si>
   <si>
-    <t>Centro Médico SBC Medic - Barranco, Clínica La Solidaridad - Barranca, Centro Médico AltaSalud - Barranca, Clínica Antonio Raymondi - La Victoria,  Centro Médico Medex - Surquillo, Clínica Aviva - Lima, Clínica Arthrosalud - Lima, Clínica Bellavista - Callao, Centro Médico Integramédica - Independencia, Clínica Bellavista - Callao, Clínica Maisón de Sante - Chorrillos, Clínica San Judas Tadeo - San Miguel, Clínica San Pedro - Huara, Clínica Stella Maris - Pueblo Libre, Clínica San Clemente - Lince, Centro Médico Cayetano Heredia - Lince, Clínica Aviva - Los Olivos, Clínica San Bartolomé - Huacho, Clínica Medavan - Magdalena</t>
-  </si>
-  <si>
     <t>Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Providencia - San Miguel, Clínica Good Hope - Miraflores, Clínica Limatambo - San Isidro, Clínica Sanens - Surquillo, Centro Médico Ricardo Palma - Chorrillos, Clínica San Marcos - Huaura, Clínica Vesalio - San Borja, Centro Médico Jockey Salud - Surco, Centro Médico AltaSalud - San Isidro, Centro Médico Sanna - La Molina, Centro Médico Sanna - Miraflores, Clínica Higuereta - Miraflores, Clínica Corazón de Jesús - Cañete, Centro Médico Clisova - Chancay, Centro Médico Clisova - Huaral, Centro Médico Nueva Esperanza - Huaral</t>
   </si>
   <si>
@@ -699,6 +693,18 @@
   </si>
   <si>
     <t>Clínica Angloamericana - La Molina, Clínica Angloamericana - San Isidro, Centro Médico San Felipe - La Molina, Clínica San Felipe - Jesús María, Clínica Miraflores - Miraflores, Clínica San Felipe - Jesús María, Clínica Miraflores - Miraflores, Clínica Montesur - Surco</t>
+  </si>
+  <si>
+    <t>Centro Médico Jockey Salud - Surco, Clínica Limatambo - San Isidro, Clínica Montefiori - La Molina, Clínica Providencia - San Miguel, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Clínica Medavan - Magdalena, Clínica Especialidades Médicas - San Borja, Centro Médico Internacional - San Isidro, Clínica San Gabriel - San Miguel, Centro Médico Internacional - Surco, Centro Médico Internacional - La Molina, Clínica Jesús del Norte - Independencia</t>
+  </si>
+  <si>
+    <t>Clínica Santa Isabel - San Borja, Clínica Internacional - San Borja</t>
+  </si>
+  <si>
+    <t>Centro Médico SBC Medic - Barranco, Clínica La Solidaridad - Barranca, Centro Médico AltaSalud - Barranca, Clínica Antonio Raymondi - La Victoria, Centro Médico Medex - Surquillo, Clínica Aviva - Lima, Clínica Arthrosalud - Lima, Clínica Bellavista - Callao, Centro Médico Integramédica - Independencia, Clínica Bellavista - Callao, Clínica Maisón de Sante - Chorrillos, Clínica San Judas Tadeo - San Miguel, Clínica San Pedro - Huara, Clínica Stella Maris - Pueblo Libre, Clínica San Clemente - Lince, Centro Médico Cayetano Heredia - Lince, Clínica Aviva - Los Olivos, Clínica San Bartolomé - Huacho</t>
+  </si>
+  <si>
+    <t>Centro Médico SBC Medic - Barranco, Clínica La Solidaridad - Barranca, Centro Médico AltaSalud - Barranca, Clínica Antonio Raymondi - La Victoria, Centro Médico Medex - Surquillo, Clínica Aviva - Lima, Clínica Arthrosalud - Lima, Clínica Bellavista - Callao, Centro Médico Integramédica - Independencia, Clínica Bellavista - Callao, Clínica Maisón de Sante - Chorrillos, Clínica San Judas Tadeo - San Miguel, Clínica San Pedro - Huara, Clínica Stella Maris - Pueblo Libre, Clínica San Clemente - Lince, Centro Médico Cayetano Heredia - Lince, Clínica Aviva - Los Olivos, Clínica San Bartolomé - Huacho, Clínica Medavan - Magdalena</t>
   </si>
 </sst>
 </file>
@@ -1363,7 +1369,7 @@
         <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>163</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1523,7 +1529,7 @@
         <v>37</v>
       </c>
       <c r="F21" t="s">
-        <v>163</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1683,7 +1689,7 @@
         <v>37</v>
       </c>
       <c r="F29" t="s">
-        <v>163</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1883,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>170</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2123,7 +2129,7 @@
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2143,7 +2149,7 @@
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2163,7 +2169,7 @@
         <v>34</v>
       </c>
       <c r="F53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2183,7 +2189,7 @@
         <v>37</v>
       </c>
       <c r="F54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2203,7 +2209,7 @@
         <v>16</v>
       </c>
       <c r="F55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2223,7 +2229,7 @@
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2243,7 +2249,7 @@
         <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2263,7 +2269,7 @@
         <v>28</v>
       </c>
       <c r="F58" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2283,7 +2289,7 @@
         <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2303,7 +2309,7 @@
         <v>34</v>
       </c>
       <c r="F60" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2323,7 +2329,7 @@
         <v>72</v>
       </c>
       <c r="F61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2343,7 +2349,7 @@
         <v>28</v>
       </c>
       <c r="F62" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2363,7 +2369,7 @@
         <v>13</v>
       </c>
       <c r="F63" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2383,7 +2389,7 @@
         <v>16</v>
       </c>
       <c r="F64" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2403,7 +2409,7 @@
         <v>77</v>
       </c>
       <c r="F65" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2423,7 +2429,7 @@
         <v>74</v>
       </c>
       <c r="F66" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2443,7 +2449,7 @@
         <v>24</v>
       </c>
       <c r="F67" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2463,7 +2469,7 @@
         <v>28</v>
       </c>
       <c r="F68" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2483,7 +2489,7 @@
         <v>16</v>
       </c>
       <c r="F69" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2503,7 +2509,7 @@
         <v>16</v>
       </c>
       <c r="F70" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2523,7 +2529,7 @@
         <v>34</v>
       </c>
       <c r="F71" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2557,13 +2563,13 @@
         <v>82</v>
       </c>
       <c r="D73" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E73" t="s">
         <v>72</v>
       </c>
       <c r="F73" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2583,7 +2589,7 @@
         <v>74</v>
       </c>
       <c r="F74" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2603,7 +2609,7 @@
         <v>24</v>
       </c>
       <c r="F75" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2623,7 +2629,7 @@
         <v>37</v>
       </c>
       <c r="F76" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2643,7 +2649,7 @@
         <v>28</v>
       </c>
       <c r="F77" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2663,7 +2669,7 @@
         <v>13</v>
       </c>
       <c r="F78" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2683,7 +2689,7 @@
         <v>13</v>
       </c>
       <c r="F79" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2703,7 +2709,7 @@
         <v>13</v>
       </c>
       <c r="F80" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2743,7 +2749,7 @@
         <v>74</v>
       </c>
       <c r="F82" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2763,7 +2769,7 @@
         <v>24</v>
       </c>
       <c r="F83" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2783,7 +2789,7 @@
         <v>37</v>
       </c>
       <c r="F84" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2803,7 +2809,7 @@
         <v>28</v>
       </c>
       <c r="F85" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2823,7 +2829,7 @@
         <v>28</v>
       </c>
       <c r="F86" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2843,7 +2849,7 @@
         <v>13</v>
       </c>
       <c r="F87" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2883,7 +2889,7 @@
         <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -2903,7 +2909,7 @@
         <v>74</v>
       </c>
       <c r="F90" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -2923,7 +2929,7 @@
         <v>26</v>
       </c>
       <c r="F91" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -2943,7 +2949,7 @@
         <v>91</v>
       </c>
       <c r="F92" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -2963,7 +2969,7 @@
         <v>13</v>
       </c>
       <c r="F93" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -2983,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3003,7 +3009,7 @@
         <v>34</v>
       </c>
       <c r="F95" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3023,7 +3029,7 @@
         <v>72</v>
       </c>
       <c r="F96" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3043,7 +3049,7 @@
         <v>74</v>
       </c>
       <c r="F97" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3063,7 +3069,7 @@
         <v>16</v>
       </c>
       <c r="F98" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3083,7 +3089,7 @@
         <v>19</v>
       </c>
       <c r="F99" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3103,7 +3109,7 @@
         <v>34</v>
       </c>
       <c r="F100" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3123,7 +3129,7 @@
         <v>74</v>
       </c>
       <c r="F101" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3143,7 +3149,7 @@
         <v>37</v>
       </c>
       <c r="F102" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3163,7 +3169,7 @@
         <v>16</v>
       </c>
       <c r="F103" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3183,7 +3189,7 @@
         <v>19</v>
       </c>
       <c r="F104" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3203,7 +3209,7 @@
         <v>34</v>
       </c>
       <c r="F105" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3223,7 +3229,7 @@
         <v>74</v>
       </c>
       <c r="F106" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3243,7 +3249,7 @@
         <v>37</v>
       </c>
       <c r="F107" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3263,7 +3269,7 @@
         <v>13</v>
       </c>
       <c r="F108" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3283,7 +3289,7 @@
         <v>16</v>
       </c>
       <c r="F109" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3303,7 +3309,7 @@
         <v>19</v>
       </c>
       <c r="F110" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3323,7 +3329,7 @@
         <v>74</v>
       </c>
       <c r="F111" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3343,7 +3349,7 @@
         <v>24</v>
       </c>
       <c r="F112" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3363,7 +3369,7 @@
         <v>26</v>
       </c>
       <c r="F113" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3383,7 +3389,7 @@
         <v>28</v>
       </c>
       <c r="F114" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3403,7 +3409,7 @@
         <v>13</v>
       </c>
       <c r="F115" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3423,7 +3429,7 @@
         <v>16</v>
       </c>
       <c r="F116" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3443,7 +3449,7 @@
         <v>19</v>
       </c>
       <c r="F117" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3463,7 +3469,7 @@
         <v>34</v>
       </c>
       <c r="F118" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3483,7 +3489,7 @@
         <v>74</v>
       </c>
       <c r="F119" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3503,7 +3509,7 @@
         <v>24</v>
       </c>
       <c r="F120" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3523,7 +3529,7 @@
         <v>26</v>
       </c>
       <c r="F121" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3543,7 +3549,7 @@
         <v>37</v>
       </c>
       <c r="F122" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3563,7 +3569,7 @@
         <v>28</v>
       </c>
       <c r="F123" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3583,7 +3589,7 @@
         <v>28</v>
       </c>
       <c r="F124" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3603,7 +3609,7 @@
         <v>13</v>
       </c>
       <c r="F125" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3623,7 +3629,7 @@
         <v>13</v>
       </c>
       <c r="F126" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3643,7 +3649,7 @@
         <v>19</v>
       </c>
       <c r="F127" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -3663,7 +3669,7 @@
         <v>74</v>
       </c>
       <c r="F128" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3683,7 +3689,7 @@
         <v>37</v>
       </c>
       <c r="F129" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3703,7 +3709,7 @@
         <v>28</v>
       </c>
       <c r="F130" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3723,7 +3729,7 @@
         <v>74</v>
       </c>
       <c r="F131" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -3743,7 +3749,7 @@
         <v>24</v>
       </c>
       <c r="F132" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -3763,7 +3769,7 @@
         <v>26</v>
       </c>
       <c r="F133" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -3783,7 +3789,7 @@
         <v>16</v>
       </c>
       <c r="F134" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -3803,7 +3809,7 @@
         <v>16</v>
       </c>
       <c r="F135" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -3823,7 +3829,7 @@
         <v>16</v>
       </c>
       <c r="F136" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -3831,10 +3837,10 @@
         <v>100</v>
       </c>
       <c r="B137" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C137" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D137" t="s">
         <v>65</v>
@@ -3843,7 +3849,7 @@
         <v>74</v>
       </c>
       <c r="F137" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -3851,19 +3857,19 @@
         <v>100</v>
       </c>
       <c r="B138" t="s">
+        <v>211</v>
+      </c>
+      <c r="C138" t="s">
         <v>213</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
+        <v>214</v>
+      </c>
+      <c r="E138" t="s">
         <v>215</v>
       </c>
-      <c r="D138" t="s">
-        <v>216</v>
-      </c>
-      <c r="E138" t="s">
+      <c r="F138" t="s">
         <v>217</v>
-      </c>
-      <c r="F138" t="s">
-        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\COTI SALUD 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4B08CC-054B-4C75-90BC-5F43ECEA97C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DBF9F90-8159-458D-AAC3-BBA29091D2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -545,9 +545,6 @@
     <t>Centro Médico Limatambo - Callao, Clínica Maisón de Sante - Lima, Clínica Maisón de Sante - Chorrillos, Clínica Versalles - Comas, Centro Médico Cayetano Heredia - Lince,  Clínica Mundo Salud - Los Olivos, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM</t>
   </si>
   <si>
-    <t>Centro Médico Ricardo Palma - Chorrillos, Centro Médico Integramédica - Independencia, Sanna Miraflores, Sanna La Molina, Centro Médico Sanna - San Miguel, Sanna Los Olivos, Centro Médico Sanna - San Juan de Lurigancho, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Centro Médico Sanna - Surco, Clínica Limatambo - San Isidro, Clínica Limatambo - SJL, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Aviva - Los Olivos, Clínica Aviva - Lima, Centro Médico Jockey Salud - Surco, Clínica Cayetano Heredia - SMP</t>
-  </si>
-  <si>
     <t>Clínica Montefiori - La Molina, Clínica Good Hope - Miraflores, Clínica San Gabriel - San Miguel</t>
   </si>
   <si>
@@ -569,9 +566,6 @@
     <t>Clínica Good Hope - Miraflores, Clínica Javier Prado - San Isidro, Clínica Maisón de Sante - Chorrillos, Clínica Aviva - Los Olivos, Clínica San Gabriel - San Miguel</t>
   </si>
   <si>
-    <t>Clínica Sanna  - San Borja, Clínica Centenario Peruano Japonesa - Pueblo Libre</t>
-  </si>
-  <si>
     <t>S/160 al 60%</t>
   </si>
   <si>
@@ -705,6 +699,12 @@
   </si>
   <si>
     <t>Centro Médico SBC Medic - Barranco, Clínica La Solidaridad - Barranca, Centro Médico AltaSalud - Barranca, Clínica Antonio Raymondi - La Victoria, Centro Médico Medex - Surquillo, Clínica Aviva - Lima, Clínica Arthrosalud - Lima, Clínica Bellavista - Callao, Centro Médico Integramédica - Independencia, Clínica Bellavista - Callao, Clínica Maisón de Sante - Chorrillos, Clínica San Judas Tadeo - San Miguel, Clínica San Pedro - Huara, Clínica Stella Maris - Pueblo Libre, Clínica San Clemente - Lince, Centro Médico Cayetano Heredia - Lince, Clínica Aviva - Los Olivos, Clínica San Bartolomé - Huacho, Clínica Medavan - Magdalena</t>
+  </si>
+  <si>
+    <t>Clínica Sanna - San Borja, Clínica Centenario Peruano Japonesa - Pueblo Libre</t>
+  </si>
+  <si>
+    <t>Centro Médico Ricardo Palma - Chorrillos, Centro Médico Integramédica - Independencia, Centro Médico Sanna - Miraflores, Centro Médico Sanna - La Molina, Centro Médico Sanna - San Miguel, Centro Médico Sanna - Los Olivos, Centro Médico Sanna - San Juan de Lurigancho, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Centro Médico Sanna - Surco, Clínica Limatambo - San Isidro, Clínica Limatambo - SJL, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Aviva - Los Olivos, Clínica Aviva - Lima, Centro Médico Jockey Salud - Surco, Clínica Cayetano Heredia - SMP</t>
   </si>
 </sst>
 </file>
@@ -731,18 +731,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -783,7 +777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -800,7 +794,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1148,7 +1146,7 @@
       <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="6" t="s">
         <v>150</v>
       </c>
     </row>
@@ -1168,7 +1166,7 @@
       <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="6" t="s">
         <v>151</v>
       </c>
     </row>
@@ -1188,7 +1186,7 @@
       <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="6" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1208,7 +1206,7 @@
       <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="7" t="s">
         <v>154</v>
       </c>
     </row>
@@ -1228,7 +1226,7 @@
       <c r="E6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="7" t="s">
         <v>153</v>
       </c>
     </row>
@@ -1248,7 +1246,7 @@
       <c r="E7" t="s">
         <v>16</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="7" t="s">
         <v>163</v>
       </c>
     </row>
@@ -1268,7 +1266,7 @@
       <c r="E8" t="s">
         <v>19</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="7" t="s">
         <v>155</v>
       </c>
     </row>
@@ -1288,7 +1286,7 @@
       <c r="E9" t="s">
         <v>19</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="7" t="s">
         <v>156</v>
       </c>
     </row>
@@ -1308,7 +1306,7 @@
       <c r="E10" t="s">
         <v>34</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="7" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1328,7 +1326,7 @@
       <c r="E11" t="s">
         <v>24</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="7" t="s">
         <v>154</v>
       </c>
     </row>
@@ -1348,7 +1346,7 @@
       <c r="E12" t="s">
         <v>26</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="7" t="s">
         <v>158</v>
       </c>
     </row>
@@ -1368,8 +1366,8 @@
       <c r="E13" t="s">
         <v>28</v>
       </c>
-      <c r="F13" t="s">
-        <v>224</v>
+      <c r="F13" s="7" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1388,7 +1386,7 @@
       <c r="E14" t="s">
         <v>13</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="7" t="s">
         <v>155</v>
       </c>
     </row>
@@ -1408,7 +1406,7 @@
       <c r="E15" t="s">
         <v>16</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="7" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1428,7 +1426,7 @@
       <c r="E16" t="s">
         <v>19</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="7" t="s">
         <v>160</v>
       </c>
     </row>
@@ -1448,7 +1446,7 @@
       <c r="E17" t="s">
         <v>34</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="7" t="s">
         <v>161</v>
       </c>
     </row>
@@ -1468,7 +1466,7 @@
       <c r="E18" t="s">
         <v>34</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="7" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1488,7 +1486,7 @@
       <c r="E19" t="s">
         <v>24</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="7" t="s">
         <v>154</v>
       </c>
     </row>
@@ -1508,7 +1506,7 @@
       <c r="E20" t="s">
         <v>26</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="7" t="s">
         <v>158</v>
       </c>
     </row>
@@ -1528,8 +1526,8 @@
       <c r="E21" t="s">
         <v>37</v>
       </c>
-      <c r="F21" t="s">
-        <v>224</v>
+      <c r="F21" s="7" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1548,7 +1546,7 @@
       <c r="E22" t="s">
         <v>28</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="7" t="s">
         <v>155</v>
       </c>
     </row>
@@ -1568,7 +1566,7 @@
       <c r="E23" t="s">
         <v>28</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="7" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1588,7 +1586,7 @@
       <c r="E24" t="s">
         <v>13</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="7" t="s">
         <v>160</v>
       </c>
     </row>
@@ -1608,7 +1606,7 @@
       <c r="E25" t="s">
         <v>13</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="7" t="s">
         <v>161</v>
       </c>
     </row>
@@ -1628,7 +1626,7 @@
       <c r="E26" t="s">
         <v>16</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="7" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1648,7 +1646,7 @@
       <c r="E27" t="s">
         <v>24</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="7" t="s">
         <v>154</v>
       </c>
     </row>
@@ -1668,7 +1666,7 @@
       <c r="E28" t="s">
         <v>26</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="7" t="s">
         <v>158</v>
       </c>
     </row>
@@ -1688,8 +1686,8 @@
       <c r="E29" t="s">
         <v>37</v>
       </c>
-      <c r="F29" t="s">
-        <v>224</v>
+      <c r="F29" s="7" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1708,7 +1706,7 @@
       <c r="E30" t="s">
         <v>28</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="7" t="s">
         <v>155</v>
       </c>
     </row>
@@ -1728,7 +1726,7 @@
       <c r="E31" t="s">
         <v>28</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="7" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1748,7 +1746,7 @@
       <c r="E32" t="s">
         <v>13</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="7" t="s">
         <v>160</v>
       </c>
     </row>
@@ -1768,7 +1766,7 @@
       <c r="E33" t="s">
         <v>13</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="7" t="s">
         <v>161</v>
       </c>
     </row>
@@ -1788,7 +1786,7 @@
       <c r="E34" t="s">
         <v>16</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="7" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1808,7 +1806,7 @@
       <c r="E35" t="s">
         <v>50</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="7" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1828,7 +1826,7 @@
       <c r="E36" t="s">
         <v>37</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="7" t="s">
         <v>165</v>
       </c>
     </row>
@@ -1848,7 +1846,7 @@
       <c r="E37" t="s">
         <v>28</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="7" t="s">
         <v>166</v>
       </c>
     </row>
@@ -1868,7 +1866,7 @@
       <c r="E38" t="s">
         <v>13</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="7" t="s">
         <v>167</v>
       </c>
     </row>
@@ -1888,8 +1886,8 @@
       <c r="E39" t="s">
         <v>16</v>
       </c>
-      <c r="F39" t="s">
-        <v>225</v>
+      <c r="F39" s="7" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1908,7 +1906,7 @@
       <c r="E40" t="s">
         <v>24</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="7" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1928,7 +1926,7 @@
       <c r="E41" t="s">
         <v>26</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="7" t="s">
         <v>165</v>
       </c>
     </row>
@@ -1948,7 +1946,7 @@
       <c r="E42" t="s">
         <v>37</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="7" t="s">
         <v>166</v>
       </c>
     </row>
@@ -1968,7 +1966,7 @@
       <c r="E43" t="s">
         <v>28</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="7" t="s">
         <v>167</v>
       </c>
     </row>
@@ -1988,7 +1986,7 @@
       <c r="E44" t="s">
         <v>13</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="7" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2008,7 +2006,7 @@
       <c r="E45" t="s">
         <v>16</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="7" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2028,7 +2026,7 @@
       <c r="E46" t="s">
         <v>24</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="7" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2048,7 +2046,7 @@
       <c r="E47" t="s">
         <v>26</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="7" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2068,7 +2066,7 @@
       <c r="E48" t="s">
         <v>37</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="7" t="s">
         <v>166</v>
       </c>
     </row>
@@ -2088,7 +2086,7 @@
       <c r="E49" t="s">
         <v>13</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="7" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2108,7 +2106,7 @@
       <c r="E50" t="s">
         <v>16</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="7" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2128,7 +2126,7 @@
       <c r="E51" t="s">
         <v>13</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="7" t="s">
         <v>170</v>
       </c>
     </row>
@@ -2148,7 +2146,7 @@
       <c r="E52" t="s">
         <v>19</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="7" t="s">
         <v>171</v>
       </c>
     </row>
@@ -2168,7 +2166,7 @@
       <c r="E53" t="s">
         <v>34</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="7" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2188,7 +2186,7 @@
       <c r="E54" t="s">
         <v>37</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="7" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2208,8 +2206,8 @@
       <c r="E55" t="s">
         <v>16</v>
       </c>
-      <c r="F55" t="s">
-        <v>174</v>
+      <c r="F55" s="7" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2228,12 +2226,12 @@
       <c r="E56" t="s">
         <v>19</v>
       </c>
-      <c r="F56" t="s">
-        <v>175</v>
+      <c r="F56" s="7" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="8" t="s">
         <v>60</v>
       </c>
       <c r="B57" t="s">
@@ -2248,7 +2246,7 @@
       <c r="E57" t="s">
         <v>26</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="7" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2268,8 +2266,8 @@
       <c r="E58" t="s">
         <v>28</v>
       </c>
-      <c r="F58" t="s">
-        <v>174</v>
+      <c r="F58" s="7" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2288,8 +2286,8 @@
       <c r="E59" t="s">
         <v>16</v>
       </c>
-      <c r="F59" t="s">
-        <v>176</v>
+      <c r="F59" s="7" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2308,8 +2306,8 @@
       <c r="E60" t="s">
         <v>34</v>
       </c>
-      <c r="F60" t="s">
-        <v>177</v>
+      <c r="F60" s="7" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2328,8 +2326,8 @@
       <c r="E61" t="s">
         <v>72</v>
       </c>
-      <c r="F61" t="s">
-        <v>178</v>
+      <c r="F61" s="7" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2348,8 +2346,8 @@
       <c r="E62" t="s">
         <v>28</v>
       </c>
-      <c r="F62" t="s">
-        <v>179</v>
+      <c r="F62" s="7" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2368,8 +2366,8 @@
       <c r="E63" t="s">
         <v>13</v>
       </c>
-      <c r="F63" t="s">
-        <v>180</v>
+      <c r="F63" s="7" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2388,8 +2386,8 @@
       <c r="E64" t="s">
         <v>16</v>
       </c>
-      <c r="F64" t="s">
-        <v>181</v>
+      <c r="F64" s="7" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2408,8 +2406,8 @@
       <c r="E65" t="s">
         <v>77</v>
       </c>
-      <c r="F65" t="s">
-        <v>182</v>
+      <c r="F65" s="7" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2428,8 +2426,8 @@
       <c r="E66" t="s">
         <v>74</v>
       </c>
-      <c r="F66" t="s">
-        <v>184</v>
+      <c r="F66" s="7" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2448,8 +2446,8 @@
       <c r="E67" t="s">
         <v>24</v>
       </c>
-      <c r="F67" t="s">
-        <v>185</v>
+      <c r="F67" s="7" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2468,8 +2466,8 @@
       <c r="E68" t="s">
         <v>28</v>
       </c>
-      <c r="F68" t="s">
-        <v>186</v>
+      <c r="F68" s="7" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2488,8 +2486,8 @@
       <c r="E69" t="s">
         <v>16</v>
       </c>
-      <c r="F69" t="s">
-        <v>187</v>
+      <c r="F69" s="7" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2508,8 +2506,8 @@
       <c r="E70" t="s">
         <v>16</v>
       </c>
-      <c r="F70" t="s">
-        <v>193</v>
+      <c r="F70" s="7" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2528,8 +2526,8 @@
       <c r="E71" t="s">
         <v>34</v>
       </c>
-      <c r="F71" t="s">
-        <v>188</v>
+      <c r="F71" s="7" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2548,7 +2546,7 @@
       <c r="E72" t="s">
         <v>72</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F72" s="7" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2563,13 +2561,13 @@
         <v>82</v>
       </c>
       <c r="D73" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E73" t="s">
         <v>72</v>
       </c>
-      <c r="F73" t="s">
-        <v>189</v>
+      <c r="F73" s="7" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2588,8 +2586,8 @@
       <c r="E74" t="s">
         <v>74</v>
       </c>
-      <c r="F74" t="s">
-        <v>184</v>
+      <c r="F74" s="7" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2608,8 +2606,8 @@
       <c r="E75" t="s">
         <v>24</v>
       </c>
-      <c r="F75" t="s">
-        <v>194</v>
+      <c r="F75" s="7" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2628,8 +2626,8 @@
       <c r="E76" t="s">
         <v>37</v>
       </c>
-      <c r="F76" t="s">
-        <v>195</v>
+      <c r="F76" s="7" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2648,8 +2646,8 @@
       <c r="E77" t="s">
         <v>28</v>
       </c>
-      <c r="F77" t="s">
-        <v>192</v>
+      <c r="F77" s="7" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2668,8 +2666,8 @@
       <c r="E78" t="s">
         <v>13</v>
       </c>
-      <c r="F78" t="s">
-        <v>193</v>
+      <c r="F78" s="7" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2688,8 +2686,8 @@
       <c r="E79" t="s">
         <v>13</v>
       </c>
-      <c r="F79" t="s">
-        <v>196</v>
+      <c r="F79" s="7" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2708,8 +2706,8 @@
       <c r="E80" t="s">
         <v>13</v>
       </c>
-      <c r="F80" t="s">
-        <v>197</v>
+      <c r="F80" s="7" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2728,7 +2726,7 @@
       <c r="E81" t="s">
         <v>19</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="7" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2748,8 +2746,8 @@
       <c r="E82" t="s">
         <v>74</v>
       </c>
-      <c r="F82" t="s">
-        <v>184</v>
+      <c r="F82" s="7" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2768,8 +2766,8 @@
       <c r="E83" t="s">
         <v>24</v>
       </c>
-      <c r="F83" t="s">
-        <v>190</v>
+      <c r="F83" s="7" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2788,8 +2786,8 @@
       <c r="E84" t="s">
         <v>37</v>
       </c>
-      <c r="F84" t="s">
-        <v>191</v>
+      <c r="F84" s="7" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2808,8 +2806,8 @@
       <c r="E85" t="s">
         <v>28</v>
       </c>
-      <c r="F85" t="s">
-        <v>192</v>
+      <c r="F85" s="7" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2828,8 +2826,8 @@
       <c r="E86" t="s">
         <v>28</v>
       </c>
-      <c r="F86" t="s">
-        <v>193</v>
+      <c r="F86" s="7" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2848,8 +2846,8 @@
       <c r="E87" t="s">
         <v>13</v>
       </c>
-      <c r="F87" t="s">
-        <v>188</v>
+      <c r="F87" s="7" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2868,7 +2866,7 @@
       <c r="E88" t="s">
         <v>13</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F88" s="7" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2888,8 +2886,8 @@
       <c r="E89" t="s">
         <v>19</v>
       </c>
-      <c r="F89" t="s">
-        <v>189</v>
+      <c r="F89" s="7" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -2908,8 +2906,8 @@
       <c r="E90" t="s">
         <v>74</v>
       </c>
-      <c r="F90" t="s">
-        <v>198</v>
+      <c r="F90" s="7" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -2928,8 +2926,8 @@
       <c r="E91" t="s">
         <v>26</v>
       </c>
-      <c r="F91" t="s">
-        <v>199</v>
+      <c r="F91" s="7" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -2948,8 +2946,8 @@
       <c r="E92" t="s">
         <v>91</v>
       </c>
-      <c r="F92" t="s">
-        <v>200</v>
+      <c r="F92" s="7" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -2968,8 +2966,8 @@
       <c r="E93" t="s">
         <v>13</v>
       </c>
-      <c r="F93" t="s">
-        <v>201</v>
+      <c r="F93" s="7" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -2988,8 +2986,8 @@
       <c r="E94" t="s">
         <v>16</v>
       </c>
-      <c r="F94" t="s">
-        <v>202</v>
+      <c r="F94" s="7" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3008,8 +3006,8 @@
       <c r="E95" t="s">
         <v>34</v>
       </c>
-      <c r="F95" t="s">
-        <v>203</v>
+      <c r="F95" s="7" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3028,8 +3026,8 @@
       <c r="E96" t="s">
         <v>72</v>
       </c>
-      <c r="F96" t="s">
-        <v>204</v>
+      <c r="F96" s="7" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3048,8 +3046,8 @@
       <c r="E97" t="s">
         <v>74</v>
       </c>
-      <c r="F97" t="s">
-        <v>198</v>
+      <c r="F97" s="7" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3068,8 +3066,8 @@
       <c r="E98" t="s">
         <v>16</v>
       </c>
-      <c r="F98" t="s">
-        <v>205</v>
+      <c r="F98" s="7" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3088,8 +3086,8 @@
       <c r="E99" t="s">
         <v>19</v>
       </c>
-      <c r="F99" t="s">
-        <v>206</v>
+      <c r="F99" s="7" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3108,8 +3106,8 @@
       <c r="E100" t="s">
         <v>34</v>
       </c>
-      <c r="F100" t="s">
-        <v>207</v>
+      <c r="F100" s="7" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3128,8 +3126,8 @@
       <c r="E101" t="s">
         <v>74</v>
       </c>
-      <c r="F101" t="s">
-        <v>198</v>
+      <c r="F101" s="7" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3148,8 +3146,8 @@
       <c r="E102" t="s">
         <v>37</v>
       </c>
-      <c r="F102" t="s">
-        <v>205</v>
+      <c r="F102" s="7" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3168,8 +3166,8 @@
       <c r="E103" t="s">
         <v>16</v>
       </c>
-      <c r="F103" t="s">
-        <v>226</v>
+      <c r="F103" s="7" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3188,8 +3186,8 @@
       <c r="E104" t="s">
         <v>19</v>
       </c>
-      <c r="F104" t="s">
-        <v>207</v>
+      <c r="F104" s="7" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3208,8 +3206,8 @@
       <c r="E105" t="s">
         <v>34</v>
       </c>
-      <c r="F105" t="s">
-        <v>202</v>
+      <c r="F105" s="7" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3228,8 +3226,8 @@
       <c r="E106" t="s">
         <v>74</v>
       </c>
-      <c r="F106" t="s">
-        <v>198</v>
+      <c r="F106" s="7" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3248,8 +3246,8 @@
       <c r="E107" t="s">
         <v>37</v>
       </c>
-      <c r="F107" t="s">
-        <v>205</v>
+      <c r="F107" s="7" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3268,8 +3266,8 @@
       <c r="E108" t="s">
         <v>13</v>
       </c>
-      <c r="F108" t="s">
-        <v>226</v>
+      <c r="F108" s="7" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3288,8 +3286,8 @@
       <c r="E109" t="s">
         <v>16</v>
       </c>
-      <c r="F109" t="s">
-        <v>207</v>
+      <c r="F109" s="7" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3308,8 +3306,8 @@
       <c r="E110" t="s">
         <v>19</v>
       </c>
-      <c r="F110" t="s">
-        <v>202</v>
+      <c r="F110" s="7" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3328,8 +3326,8 @@
       <c r="E111" t="s">
         <v>74</v>
       </c>
-      <c r="F111" t="s">
-        <v>198</v>
+      <c r="F111" s="7" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3348,8 +3346,8 @@
       <c r="E112" t="s">
         <v>24</v>
       </c>
-      <c r="F112" t="s">
-        <v>205</v>
+      <c r="F112" s="7" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3368,8 +3366,8 @@
       <c r="E113" t="s">
         <v>26</v>
       </c>
-      <c r="F113" t="s">
-        <v>227</v>
+      <c r="F113" s="7" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3388,8 +3386,8 @@
       <c r="E114" t="s">
         <v>28</v>
       </c>
-      <c r="F114" t="s">
-        <v>208</v>
+      <c r="F114" s="7" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3408,8 +3406,8 @@
       <c r="E115" t="s">
         <v>13</v>
       </c>
-      <c r="F115" t="s">
-        <v>202</v>
+      <c r="F115" s="7" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3428,8 +3426,8 @@
       <c r="E116" t="s">
         <v>16</v>
       </c>
-      <c r="F116" t="s">
-        <v>203</v>
+      <c r="F116" s="7" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3448,8 +3446,8 @@
       <c r="E117" t="s">
         <v>19</v>
       </c>
-      <c r="F117" t="s">
-        <v>204</v>
+      <c r="F117" s="7" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3468,8 +3466,8 @@
       <c r="E118" t="s">
         <v>34</v>
       </c>
-      <c r="F118" t="s">
-        <v>209</v>
+      <c r="F118" s="7" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3488,8 +3486,8 @@
       <c r="E119" t="s">
         <v>74</v>
       </c>
-      <c r="F119" t="s">
-        <v>198</v>
+      <c r="F119" s="7" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3508,8 +3506,8 @@
       <c r="E120" t="s">
         <v>24</v>
       </c>
-      <c r="F120" t="s">
-        <v>205</v>
+      <c r="F120" s="7" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3528,8 +3526,8 @@
       <c r="E121" t="s">
         <v>26</v>
       </c>
-      <c r="F121" t="s">
-        <v>227</v>
+      <c r="F121" s="7" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3548,8 +3546,8 @@
       <c r="E122" t="s">
         <v>37</v>
       </c>
-      <c r="F122" t="s">
-        <v>208</v>
+      <c r="F122" s="7" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3568,8 +3566,8 @@
       <c r="E123" t="s">
         <v>28</v>
       </c>
-      <c r="F123" t="s">
-        <v>202</v>
+      <c r="F123" s="7" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3588,8 +3586,8 @@
       <c r="E124" t="s">
         <v>28</v>
       </c>
-      <c r="F124" t="s">
-        <v>203</v>
+      <c r="F124" s="7" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3608,8 +3606,8 @@
       <c r="E125" t="s">
         <v>13</v>
       </c>
-      <c r="F125" t="s">
-        <v>204</v>
+      <c r="F125" s="7" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3628,8 +3626,8 @@
       <c r="E126" t="s">
         <v>13</v>
       </c>
-      <c r="F126" t="s">
-        <v>209</v>
+      <c r="F126" s="7" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3648,8 +3646,8 @@
       <c r="E127" t="s">
         <v>19</v>
       </c>
-      <c r="F127" t="s">
-        <v>210</v>
+      <c r="F127" s="7" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -3668,8 +3666,8 @@
       <c r="E128" t="s">
         <v>74</v>
       </c>
-      <c r="F128" t="s">
-        <v>218</v>
+      <c r="F128" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3688,8 +3686,8 @@
       <c r="E129" t="s">
         <v>37</v>
       </c>
-      <c r="F129" t="s">
-        <v>219</v>
+      <c r="F129" s="7" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3708,8 +3706,8 @@
       <c r="E130" t="s">
         <v>28</v>
       </c>
-      <c r="F130" t="s">
-        <v>220</v>
+      <c r="F130" s="7" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3728,8 +3726,8 @@
       <c r="E131" t="s">
         <v>74</v>
       </c>
-      <c r="F131" t="s">
-        <v>218</v>
+      <c r="F131" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -3748,8 +3746,8 @@
       <c r="E132" t="s">
         <v>24</v>
       </c>
-      <c r="F132" t="s">
-        <v>219</v>
+      <c r="F132" s="7" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -3768,8 +3766,8 @@
       <c r="E133" t="s">
         <v>26</v>
       </c>
-      <c r="F133" t="s">
-        <v>220</v>
+      <c r="F133" s="7" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -3788,8 +3786,8 @@
       <c r="E134" t="s">
         <v>16</v>
       </c>
-      <c r="F134" t="s">
-        <v>221</v>
+      <c r="F134" s="7" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -3808,8 +3806,8 @@
       <c r="E135" t="s">
         <v>16</v>
       </c>
-      <c r="F135" t="s">
-        <v>222</v>
+      <c r="F135" s="7" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -3828,8 +3826,8 @@
       <c r="E136" t="s">
         <v>16</v>
       </c>
-      <c r="F136" t="s">
-        <v>223</v>
+      <c r="F136" s="7" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -3837,10 +3835,10 @@
         <v>100</v>
       </c>
       <c r="B137" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C137" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D137" t="s">
         <v>65</v>
@@ -3848,8 +3846,8 @@
       <c r="E137" t="s">
         <v>74</v>
       </c>
-      <c r="F137" t="s">
-        <v>216</v>
+      <c r="F137" s="7" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -3857,19 +3855,19 @@
         <v>100</v>
       </c>
       <c r="B138" t="s">
+        <v>209</v>
+      </c>
+      <c r="C138" t="s">
         <v>211</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
+        <v>212</v>
+      </c>
+      <c r="E138" t="s">
         <v>213</v>
       </c>
-      <c r="D138" t="s">
-        <v>214</v>
-      </c>
-      <c r="E138" t="s">
+      <c r="F138" s="7" t="s">
         <v>215</v>
-      </c>
-      <c r="F138" t="s">
-        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\COTI SALUD 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DBF9F90-8159-458D-AAC3-BBA29091D2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A779A3-BCF6-4693-8CDA-D337B1647E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REDES" sheetId="1" r:id="rId1"/>
@@ -503,9 +503,6 @@
     <t xml:space="preserve">Clínica Tezza - Surco, Clínica Internacional - Lima, Clínica Ricardo Palma - San Isidro, Clínica San Pablo - Surco, Clínica Santa Isabel - San Borja, Clínica San Juan De Dios - San Luis, Centro Médico Sanna - La Molina, Clínica El Golf - San Isidro, Centro Médico Sanna - Surco, Centro Médico Sanna - Miraflores  </t>
   </si>
   <si>
-    <t>Clínica Internacional - San Borja, Clínica Sanna  - San Borja, Clínica Montesur - Surco</t>
-  </si>
-  <si>
     <t>Clínica Angloamericana - La Molina, Clínica Angloamericana - San Isidro, Centro Médico San Felipe - La Molina, Clínica San Felipe - Jesús María, Clínica Miraflores - Miraflores</t>
   </si>
   <si>
@@ -527,9 +524,6 @@
     <t>Clínica Internacional - Lima, Centro Médico Internacional - Surco, Clínica Jesús del Norte - Independencia</t>
   </si>
   <si>
-    <t>Clínica San Pablo - Surco, Clínica Ricardo Palma - San Isidro, Clínica Santa Isabel - San Borja, Clínica El Golf - San Isidro, Clínica Internacional - San Borja, Clínica Sanna  - San Borja, Clínica San Juan De Dios - San Luis, Centro Médico Sanna - La Molina</t>
-  </si>
-  <si>
     <t>Clínica Angloamericana - La Molina, Clínica Angloamericana - San Isidro</t>
   </si>
   <si>
@@ -551,9 +545,6 @@
     <t>Clínica Montefiori - La Molina, Clínica Good Hope - Miraflores, Clínica San Gabriel - San Miguel, Clínica Jesús del Norte - Independencia, Clínica Javier Prado - San Isidro</t>
   </si>
   <si>
-    <t>Clínica Internacional - Lima, Clínica Sanna  - San Borja, Clínica El Golf - San Isidro, Clínica Tezza - Surco</t>
-  </si>
-  <si>
     <t>Clínica Ricardo Palma - San Isidro, Clínica San Pablo - Surco, Clínica Internacional - San Borja</t>
   </si>
   <si>
@@ -578,9 +569,6 @@
     <t>Clínica Good Hope - Miraflores, Clínica Javier Prado - San Isidro, Clínica Maisón de Sante - Chorrillos, Clínica Aviva - Los Olivos, Clínica San Gabriel - San Miguel, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Maisón de Sante - Lima, Clínica Jesús del Norte - Independencia</t>
   </si>
   <si>
-    <t>Clínica Sanna  - San Borja, Clínica Bellavista - Callao, Clínica Especialidades Médicas - San Borja, Clínica El Golf - San Isidro, Clínica Maisón de Sante - Surco, Clínica Tezza - Surco, Clínica Internacional - Lima, Clínica San Pablo - Surco</t>
-  </si>
-  <si>
     <t>Clínica Miraflores - Miraflores, Centro Médico San Felipe - La Molina, Clínica San Felipe - Jesús María, Centro Médico San Felipe - Surco</t>
   </si>
   <si>
@@ -593,9 +581,6 @@
     <t>Clínica Good Hope - Miraflores, Clínica Maisón de Sante - Chorrillos, Clínica Aviva - Los Olivos, Clínica San Gabriel - San Miguel, Clínica Maisón de Sante - Lima, Clínica Jesús del Norte - Independencia, Clínica Tezza - Surco</t>
   </si>
   <si>
-    <t>Clínica Sanna  - San Borja, Clínica Bellavista - Callao, Clínica Especialidades Médicas - San Borja, Clínica El Golf - San Isidro, Clínica Maisón de Sante - Surco, Clínica Internacional - Lima, Clínica San Pablo - Surco</t>
-  </si>
-  <si>
     <t>Clínica Santa Isabel - San Borja, Clínica Ricardo Palma - San Isidro, Centro Médico Internacional - San Isidro, Clínica Internacional - San Borja, Centro Médico Internacional - Surco</t>
   </si>
   <si>
@@ -644,9 +629,6 @@
     <t>Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Providencia - San Miguel, Clínica Good Hope - Miraflores, Clínica Limatambo - San Isidro, Clínica Sanens - Surquillo, Centro Médico Ricardo Palma - Chorrillos, Clínica San Marcos - Huaura, Clínica Vesalio - San Borja, Centro Médico Jockey Salud - Surco, Centro Médico AltaSalud - San Isidro, Centro Médico Sanna - La Molina, Centro Médico Sanna - Miraflores, Clínica Higuereta - Miraflores, Clínica Corazón de Jesús - Cañete, Centro Médico Clisova - Chancay, Centro Médico Clisova - Huaral, Centro Médico Nueva Esperanza - Huaral</t>
   </si>
   <si>
-    <t>Clínica Sanna  - San Borja, Clínica Montesur - Surco, Clínica San Pablo - Asia</t>
-  </si>
-  <si>
     <t>Clínica Internacional - Lima, Centro Médico Internacional - San Isidro, Centro Médico Internacional - Surco, Centro Médico Internacional - La Molina, Clínica Internacional - San Borja, Clínica Delgado - Miraflores, Centro Médico San Felipe - La Molina, Clínica Angloamericana - San Isidro, Clínica Angloamericana - La Molina, Clínica San Felipe - Jesús María</t>
   </si>
   <si>
@@ -683,9 +665,6 @@
     <t>Clínica Delgado - Miraflores, Clínica Auna - San Isidro, Clínica Ricardo Palma - San Isidro, Clínica San Pablo - Surco, Clínica San Pablo - Asia</t>
   </si>
   <si>
-    <t>Clínica Santa Isabel - San Borja, Clínica Sanna  - San Borja, Clínica El Golf - San Isidro, Centro Médico Sanna - La Molina, Clínica Maisón de Sante - Surco, Clínica Internacional - Lima, Clínica Internacional - San Borja</t>
-  </si>
-  <si>
     <t>Clínica Angloamericana - La Molina, Clínica Angloamericana - San Isidro, Centro Médico San Felipe - La Molina, Clínica San Felipe - Jesús María, Clínica Miraflores - Miraflores, Clínica San Felipe - Jesús María, Clínica Miraflores - Miraflores, Clínica Montesur - Surco</t>
   </si>
   <si>
@@ -705,6 +684,27 @@
   </si>
   <si>
     <t>Centro Médico Ricardo Palma - Chorrillos, Centro Médico Integramédica - Independencia, Centro Médico Sanna - Miraflores, Centro Médico Sanna - La Molina, Centro Médico Sanna - San Miguel, Centro Médico Sanna - Los Olivos, Centro Médico Sanna - San Juan de Lurigancho, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Centro Médico Sanna - Surco, Clínica Limatambo - San Isidro, Clínica Limatambo - SJL, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Aviva - Los Olivos, Clínica Aviva - Lima, Centro Médico Jockey Salud - Surco, Clínica Cayetano Heredia - SMP</t>
+  </si>
+  <si>
+    <t>Clínica Internacional - San Borja, Clínica Sanna - San Borja, Clínica Montesur - Surco</t>
+  </si>
+  <si>
+    <t>Clínica San Pablo - Surco, Clínica Ricardo Palma - San Isidro, Clínica Santa Isabel - San Borja, Clínica El Golf - San Isidro, Clínica Internacional - San Borja, Clínica Sanna - San Borja, Clínica San Juan De Dios - San Luis, Centro Médico Sanna - La Molina</t>
+  </si>
+  <si>
+    <t>Clínica Internacional - Lima, Clínica Sanna - San Borja, Clínica El Golf - San Isidro, Clínica Tezza - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Sanna - San Borja, Clínica Bellavista - Callao, Clínica Especialidades Médicas - San Borja, Clínica El Golf - San Isidro, Clínica Maisón de Sante - Surco, Clínica Tezza - Surco, Clínica Internacional - Lima, Clínica San Pablo - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Sanna - San Borja, Clínica Bellavista - Callao, Clínica Especialidades Médicas - San Borja, Clínica El Golf - San Isidro, Clínica Maisón de Sante - Surco, Clínica Internacional - Lima, Clínica San Pablo - Surco</t>
+  </si>
+  <si>
+    <t>Clínica Sanna - San Borja, Clínica Montesur - Surco, Clínica San Pablo - Asia</t>
+  </si>
+  <si>
+    <t>Clínica Santa Isabel - San Borja, Clínica Sanna - San Borja, Clínica El Golf - San Isidro, Centro Médico Sanna - La Molina, Clínica Maisón de Sante - Surco, Clínica Internacional - Lima, Clínica Internacional - San Borja</t>
   </si>
 </sst>
 </file>
@@ -777,7 +777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -797,8 +797,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1206,7 +1204,7 @@
       <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" t="s">
         <v>154</v>
       </c>
     </row>
@@ -1226,7 +1224,7 @@
       <c r="E6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" t="s">
         <v>153</v>
       </c>
     </row>
@@ -1246,8 +1244,8 @@
       <c r="E7" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>163</v>
+      <c r="F7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1266,7 +1264,7 @@
       <c r="E8" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" t="s">
         <v>155</v>
       </c>
     </row>
@@ -1286,7 +1284,7 @@
       <c r="E9" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" t="s">
         <v>156</v>
       </c>
     </row>
@@ -1306,7 +1304,7 @@
       <c r="E10" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1326,7 +1324,7 @@
       <c r="E11" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" t="s">
         <v>154</v>
       </c>
     </row>
@@ -1346,7 +1344,7 @@
       <c r="E12" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" t="s">
         <v>158</v>
       </c>
     </row>
@@ -1366,8 +1364,8 @@
       <c r="E13" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>222</v>
+      <c r="F13" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1386,7 +1384,7 @@
       <c r="E14" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" t="s">
         <v>155</v>
       </c>
     </row>
@@ -1406,7 +1404,7 @@
       <c r="E15" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1426,8 +1424,8 @@
       <c r="E16" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>160</v>
+      <c r="F16" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1446,8 +1444,8 @@
       <c r="E17" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>161</v>
+      <c r="F17" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1466,8 +1464,8 @@
       <c r="E18" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>162</v>
+      <c r="F18" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1486,7 +1484,7 @@
       <c r="E19" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" t="s">
         <v>154</v>
       </c>
     </row>
@@ -1506,7 +1504,7 @@
       <c r="E20" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" t="s">
         <v>158</v>
       </c>
     </row>
@@ -1526,8 +1524,8 @@
       <c r="E21" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>222</v>
+      <c r="F21" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1546,7 +1544,7 @@
       <c r="E22" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" t="s">
         <v>155</v>
       </c>
     </row>
@@ -1566,7 +1564,7 @@
       <c r="E23" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1586,8 +1584,8 @@
       <c r="E24" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>160</v>
+      <c r="F24" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1606,8 +1604,8 @@
       <c r="E25" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>161</v>
+      <c r="F25" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1626,8 +1624,8 @@
       <c r="E26" t="s">
         <v>16</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>162</v>
+      <c r="F26" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1646,7 +1644,7 @@
       <c r="E27" t="s">
         <v>24</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" t="s">
         <v>154</v>
       </c>
     </row>
@@ -1666,7 +1664,7 @@
       <c r="E28" t="s">
         <v>26</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" t="s">
         <v>158</v>
       </c>
     </row>
@@ -1686,8 +1684,8 @@
       <c r="E29" t="s">
         <v>37</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>222</v>
+      <c r="F29" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1706,7 +1704,7 @@
       <c r="E30" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" t="s">
         <v>155</v>
       </c>
     </row>
@@ -1726,7 +1724,7 @@
       <c r="E31" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1746,8 +1744,8 @@
       <c r="E32" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="7" t="s">
-        <v>160</v>
+      <c r="F32" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1766,8 +1764,8 @@
       <c r="E33" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>161</v>
+      <c r="F33" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1786,8 +1784,8 @@
       <c r="E34" t="s">
         <v>16</v>
       </c>
-      <c r="F34" s="7" t="s">
-        <v>162</v>
+      <c r="F34" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1806,8 +1804,8 @@
       <c r="E35" t="s">
         <v>50</v>
       </c>
-      <c r="F35" s="7" t="s">
-        <v>164</v>
+      <c r="F35" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1826,8 +1824,8 @@
       <c r="E36" t="s">
         <v>37</v>
       </c>
-      <c r="F36" s="7" t="s">
-        <v>165</v>
+      <c r="F36" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1846,8 +1844,8 @@
       <c r="E37" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="7" t="s">
-        <v>166</v>
+      <c r="F37" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1866,8 +1864,8 @@
       <c r="E38" t="s">
         <v>13</v>
       </c>
-      <c r="F38" s="7" t="s">
-        <v>167</v>
+      <c r="F38" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1886,8 +1884,8 @@
       <c r="E39" t="s">
         <v>16</v>
       </c>
-      <c r="F39" s="7" t="s">
-        <v>223</v>
+      <c r="F39" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1906,8 +1904,8 @@
       <c r="E40" t="s">
         <v>24</v>
       </c>
-      <c r="F40" s="7" t="s">
-        <v>164</v>
+      <c r="F40" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1926,8 +1924,8 @@
       <c r="E41" t="s">
         <v>26</v>
       </c>
-      <c r="F41" s="7" t="s">
-        <v>165</v>
+      <c r="F41" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1946,8 +1944,8 @@
       <c r="E42" t="s">
         <v>37</v>
       </c>
-      <c r="F42" s="7" t="s">
-        <v>166</v>
+      <c r="F42" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1966,8 +1964,8 @@
       <c r="E43" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="7" t="s">
-        <v>167</v>
+      <c r="F43" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1986,8 +1984,8 @@
       <c r="E44" t="s">
         <v>13</v>
       </c>
-      <c r="F44" s="7" t="s">
-        <v>168</v>
+      <c r="F44" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2006,8 +2004,8 @@
       <c r="E45" t="s">
         <v>16</v>
       </c>
-      <c r="F45" s="7" t="s">
-        <v>169</v>
+      <c r="F45" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2026,8 +2024,8 @@
       <c r="E46" t="s">
         <v>24</v>
       </c>
-      <c r="F46" s="7" t="s">
-        <v>164</v>
+      <c r="F46" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2046,8 +2044,8 @@
       <c r="E47" t="s">
         <v>26</v>
       </c>
-      <c r="F47" s="7" t="s">
-        <v>165</v>
+      <c r="F47" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2066,8 +2064,8 @@
       <c r="E48" t="s">
         <v>37</v>
       </c>
-      <c r="F48" s="7" t="s">
-        <v>166</v>
+      <c r="F48" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2086,8 +2084,8 @@
       <c r="E49" t="s">
         <v>13</v>
       </c>
-      <c r="F49" s="7" t="s">
-        <v>167</v>
+      <c r="F49" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2106,8 +2104,8 @@
       <c r="E50" t="s">
         <v>16</v>
       </c>
-      <c r="F50" s="7" t="s">
-        <v>168</v>
+      <c r="F50" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2126,8 +2124,8 @@
       <c r="E51" t="s">
         <v>13</v>
       </c>
-      <c r="F51" s="7" t="s">
-        <v>170</v>
+      <c r="F51" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2146,8 +2144,8 @@
       <c r="E52" t="s">
         <v>19</v>
       </c>
-      <c r="F52" s="7" t="s">
-        <v>171</v>
+      <c r="F52" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2166,8 +2164,8 @@
       <c r="E53" t="s">
         <v>34</v>
       </c>
-      <c r="F53" s="7" t="s">
-        <v>172</v>
+      <c r="F53" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2186,8 +2184,8 @@
       <c r="E54" t="s">
         <v>37</v>
       </c>
-      <c r="F54" s="7" t="s">
-        <v>173</v>
+      <c r="F54" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2206,8 +2204,8 @@
       <c r="E55" t="s">
         <v>16</v>
       </c>
-      <c r="F55" s="7" t="s">
-        <v>227</v>
+      <c r="F55" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2226,12 +2224,12 @@
       <c r="E56" t="s">
         <v>19</v>
       </c>
-      <c r="F56" s="7" t="s">
-        <v>174</v>
+      <c r="F56" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" t="s">
         <v>60</v>
       </c>
       <c r="B57" t="s">
@@ -2246,8 +2244,8 @@
       <c r="E57" t="s">
         <v>26</v>
       </c>
-      <c r="F57" s="7" t="s">
-        <v>173</v>
+      <c r="F57" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2266,8 +2264,8 @@
       <c r="E58" t="s">
         <v>28</v>
       </c>
-      <c r="F58" s="7" t="s">
-        <v>227</v>
+      <c r="F58" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2286,8 +2284,8 @@
       <c r="E59" t="s">
         <v>16</v>
       </c>
-      <c r="F59" s="7" t="s">
-        <v>175</v>
+      <c r="F59" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2306,8 +2304,8 @@
       <c r="E60" t="s">
         <v>34</v>
       </c>
-      <c r="F60" s="7" t="s">
-        <v>176</v>
+      <c r="F60" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2326,8 +2324,8 @@
       <c r="E61" t="s">
         <v>72</v>
       </c>
-      <c r="F61" s="7" t="s">
-        <v>177</v>
+      <c r="F61" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2346,8 +2344,8 @@
       <c r="E62" t="s">
         <v>28</v>
       </c>
-      <c r="F62" s="7" t="s">
-        <v>178</v>
+      <c r="F62" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2366,8 +2364,8 @@
       <c r="E63" t="s">
         <v>13</v>
       </c>
-      <c r="F63" s="7" t="s">
-        <v>179</v>
+      <c r="F63" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2386,8 +2384,8 @@
       <c r="E64" t="s">
         <v>16</v>
       </c>
-      <c r="F64" s="7" t="s">
-        <v>180</v>
+      <c r="F64" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2406,8 +2404,8 @@
       <c r="E65" t="s">
         <v>77</v>
       </c>
-      <c r="F65" s="7" t="s">
-        <v>226</v>
+      <c r="F65" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2426,8 +2424,8 @@
       <c r="E66" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="7" t="s">
-        <v>182</v>
+      <c r="F66" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2446,8 +2444,8 @@
       <c r="E67" t="s">
         <v>24</v>
       </c>
-      <c r="F67" s="7" t="s">
-        <v>183</v>
+      <c r="F67" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2466,8 +2464,8 @@
       <c r="E68" t="s">
         <v>28</v>
       </c>
-      <c r="F68" s="7" t="s">
-        <v>184</v>
+      <c r="F68" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2486,8 +2484,8 @@
       <c r="E69" t="s">
         <v>16</v>
       </c>
-      <c r="F69" s="7" t="s">
-        <v>185</v>
+      <c r="F69" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2506,8 +2504,8 @@
       <c r="E70" t="s">
         <v>16</v>
       </c>
-      <c r="F70" s="7" t="s">
-        <v>191</v>
+      <c r="F70" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2526,8 +2524,8 @@
       <c r="E71" t="s">
         <v>34</v>
       </c>
-      <c r="F71" s="7" t="s">
-        <v>186</v>
+      <c r="F71" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2546,8 +2544,8 @@
       <c r="E72" t="s">
         <v>72</v>
       </c>
-      <c r="F72" s="7" t="s">
-        <v>169</v>
+      <c r="F72" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2561,13 +2559,13 @@
         <v>82</v>
       </c>
       <c r="D73" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E73" t="s">
         <v>72</v>
       </c>
-      <c r="F73" s="7" t="s">
-        <v>187</v>
+      <c r="F73" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2586,8 +2584,8 @@
       <c r="E74" t="s">
         <v>74</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>182</v>
+      <c r="F74" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2606,8 +2604,8 @@
       <c r="E75" t="s">
         <v>24</v>
       </c>
-      <c r="F75" s="7" t="s">
-        <v>192</v>
+      <c r="F75" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2626,8 +2624,8 @@
       <c r="E76" t="s">
         <v>37</v>
       </c>
-      <c r="F76" s="7" t="s">
-        <v>193</v>
+      <c r="F76" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2646,8 +2644,8 @@
       <c r="E77" t="s">
         <v>28</v>
       </c>
-      <c r="F77" s="7" t="s">
-        <v>190</v>
+      <c r="F77" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2666,8 +2664,8 @@
       <c r="E78" t="s">
         <v>13</v>
       </c>
-      <c r="F78" s="7" t="s">
-        <v>191</v>
+      <c r="F78" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2686,8 +2684,8 @@
       <c r="E79" t="s">
         <v>13</v>
       </c>
-      <c r="F79" s="7" t="s">
-        <v>194</v>
+      <c r="F79" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2706,8 +2704,8 @@
       <c r="E80" t="s">
         <v>13</v>
       </c>
-      <c r="F80" s="7" t="s">
-        <v>195</v>
+      <c r="F80" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2726,8 +2724,8 @@
       <c r="E81" t="s">
         <v>19</v>
       </c>
-      <c r="F81" s="7" t="s">
-        <v>162</v>
+      <c r="F81" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2746,8 +2744,8 @@
       <c r="E82" t="s">
         <v>74</v>
       </c>
-      <c r="F82" s="7" t="s">
-        <v>182</v>
+      <c r="F82" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2766,8 +2764,8 @@
       <c r="E83" t="s">
         <v>24</v>
       </c>
-      <c r="F83" s="7" t="s">
-        <v>188</v>
+      <c r="F83" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2786,8 +2784,8 @@
       <c r="E84" t="s">
         <v>37</v>
       </c>
-      <c r="F84" s="7" t="s">
-        <v>189</v>
+      <c r="F84" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2806,8 +2804,8 @@
       <c r="E85" t="s">
         <v>28</v>
       </c>
-      <c r="F85" s="7" t="s">
-        <v>190</v>
+      <c r="F85" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2826,8 +2824,8 @@
       <c r="E86" t="s">
         <v>28</v>
       </c>
-      <c r="F86" s="7" t="s">
-        <v>191</v>
+      <c r="F86" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2846,8 +2844,8 @@
       <c r="E87" t="s">
         <v>13</v>
       </c>
-      <c r="F87" s="7" t="s">
-        <v>186</v>
+      <c r="F87" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2866,8 +2864,8 @@
       <c r="E88" t="s">
         <v>13</v>
       </c>
-      <c r="F88" s="7" t="s">
-        <v>169</v>
+      <c r="F88" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -2886,8 +2884,8 @@
       <c r="E89" t="s">
         <v>19</v>
       </c>
-      <c r="F89" s="7" t="s">
-        <v>187</v>
+      <c r="F89" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -2906,8 +2904,8 @@
       <c r="E90" t="s">
         <v>74</v>
       </c>
-      <c r="F90" s="7" t="s">
-        <v>196</v>
+      <c r="F90" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -2926,8 +2924,8 @@
       <c r="E91" t="s">
         <v>26</v>
       </c>
-      <c r="F91" s="7" t="s">
-        <v>197</v>
+      <c r="F91" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -2946,8 +2944,8 @@
       <c r="E92" t="s">
         <v>91</v>
       </c>
-      <c r="F92" s="7" t="s">
-        <v>198</v>
+      <c r="F92" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -2966,8 +2964,8 @@
       <c r="E93" t="s">
         <v>13</v>
       </c>
-      <c r="F93" s="7" t="s">
-        <v>199</v>
+      <c r="F93" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -2986,8 +2984,8 @@
       <c r="E94" t="s">
         <v>16</v>
       </c>
-      <c r="F94" s="7" t="s">
-        <v>200</v>
+      <c r="F94" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3006,8 +3004,8 @@
       <c r="E95" t="s">
         <v>34</v>
       </c>
-      <c r="F95" s="7" t="s">
-        <v>201</v>
+      <c r="F95" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3026,8 +3024,8 @@
       <c r="E96" t="s">
         <v>72</v>
       </c>
-      <c r="F96" s="7" t="s">
-        <v>202</v>
+      <c r="F96" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3046,8 +3044,8 @@
       <c r="E97" t="s">
         <v>74</v>
       </c>
-      <c r="F97" s="7" t="s">
-        <v>196</v>
+      <c r="F97" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3066,8 +3064,8 @@
       <c r="E98" t="s">
         <v>16</v>
       </c>
-      <c r="F98" s="7" t="s">
-        <v>203</v>
+      <c r="F98" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3086,8 +3084,8 @@
       <c r="E99" t="s">
         <v>19</v>
       </c>
-      <c r="F99" s="7" t="s">
-        <v>204</v>
+      <c r="F99" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3106,8 +3104,8 @@
       <c r="E100" t="s">
         <v>34</v>
       </c>
-      <c r="F100" s="7" t="s">
-        <v>205</v>
+      <c r="F100" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3126,8 +3124,8 @@
       <c r="E101" t="s">
         <v>74</v>
       </c>
-      <c r="F101" s="7" t="s">
-        <v>196</v>
+      <c r="F101" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3146,8 +3144,8 @@
       <c r="E102" t="s">
         <v>37</v>
       </c>
-      <c r="F102" s="7" t="s">
-        <v>203</v>
+      <c r="F102" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3166,8 +3164,8 @@
       <c r="E103" t="s">
         <v>16</v>
       </c>
-      <c r="F103" s="7" t="s">
-        <v>224</v>
+      <c r="F103" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3186,8 +3184,8 @@
       <c r="E104" t="s">
         <v>19</v>
       </c>
-      <c r="F104" s="7" t="s">
-        <v>205</v>
+      <c r="F104" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3206,8 +3204,8 @@
       <c r="E105" t="s">
         <v>34</v>
       </c>
-      <c r="F105" s="7" t="s">
-        <v>200</v>
+      <c r="F105" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3226,8 +3224,8 @@
       <c r="E106" t="s">
         <v>74</v>
       </c>
-      <c r="F106" s="7" t="s">
-        <v>196</v>
+      <c r="F106" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3246,8 +3244,8 @@
       <c r="E107" t="s">
         <v>37</v>
       </c>
-      <c r="F107" s="7" t="s">
-        <v>203</v>
+      <c r="F107" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3266,8 +3264,8 @@
       <c r="E108" t="s">
         <v>13</v>
       </c>
-      <c r="F108" s="7" t="s">
-        <v>224</v>
+      <c r="F108" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3286,8 +3284,8 @@
       <c r="E109" t="s">
         <v>16</v>
       </c>
-      <c r="F109" s="7" t="s">
-        <v>205</v>
+      <c r="F109" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3306,8 +3304,8 @@
       <c r="E110" t="s">
         <v>19</v>
       </c>
-      <c r="F110" s="7" t="s">
-        <v>200</v>
+      <c r="F110" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3326,8 +3324,8 @@
       <c r="E111" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="7" t="s">
-        <v>196</v>
+      <c r="F111" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3346,8 +3344,8 @@
       <c r="E112" t="s">
         <v>24</v>
       </c>
-      <c r="F112" s="7" t="s">
-        <v>203</v>
+      <c r="F112" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3366,8 +3364,8 @@
       <c r="E113" t="s">
         <v>26</v>
       </c>
-      <c r="F113" s="7" t="s">
-        <v>225</v>
+      <c r="F113" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3386,8 +3384,8 @@
       <c r="E114" t="s">
         <v>28</v>
       </c>
-      <c r="F114" s="7" t="s">
-        <v>206</v>
+      <c r="F114" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3406,8 +3404,8 @@
       <c r="E115" t="s">
         <v>13</v>
       </c>
-      <c r="F115" s="7" t="s">
-        <v>200</v>
+      <c r="F115" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3426,8 +3424,8 @@
       <c r="E116" t="s">
         <v>16</v>
       </c>
-      <c r="F116" s="7" t="s">
-        <v>201</v>
+      <c r="F116" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3446,8 +3444,8 @@
       <c r="E117" t="s">
         <v>19</v>
       </c>
-      <c r="F117" s="7" t="s">
-        <v>202</v>
+      <c r="F117" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3466,8 +3464,8 @@
       <c r="E118" t="s">
         <v>34</v>
       </c>
-      <c r="F118" s="7" t="s">
-        <v>207</v>
+      <c r="F118" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3486,8 +3484,8 @@
       <c r="E119" t="s">
         <v>74</v>
       </c>
-      <c r="F119" s="7" t="s">
-        <v>196</v>
+      <c r="F119" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3506,8 +3504,8 @@
       <c r="E120" t="s">
         <v>24</v>
       </c>
-      <c r="F120" s="7" t="s">
-        <v>203</v>
+      <c r="F120" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3526,8 +3524,8 @@
       <c r="E121" t="s">
         <v>26</v>
       </c>
-      <c r="F121" s="7" t="s">
-        <v>225</v>
+      <c r="F121" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3546,8 +3544,8 @@
       <c r="E122" t="s">
         <v>37</v>
       </c>
-      <c r="F122" s="7" t="s">
-        <v>206</v>
+      <c r="F122" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3566,8 +3564,8 @@
       <c r="E123" t="s">
         <v>28</v>
       </c>
-      <c r="F123" s="7" t="s">
-        <v>200</v>
+      <c r="F123" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3586,8 +3584,8 @@
       <c r="E124" t="s">
         <v>28</v>
       </c>
-      <c r="F124" s="7" t="s">
-        <v>201</v>
+      <c r="F124" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3606,8 +3604,8 @@
       <c r="E125" t="s">
         <v>13</v>
       </c>
-      <c r="F125" s="7" t="s">
-        <v>202</v>
+      <c r="F125" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3626,8 +3624,8 @@
       <c r="E126" t="s">
         <v>13</v>
       </c>
-      <c r="F126" s="7" t="s">
-        <v>207</v>
+      <c r="F126" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3646,8 +3644,8 @@
       <c r="E127" t="s">
         <v>19</v>
       </c>
-      <c r="F127" s="7" t="s">
-        <v>208</v>
+      <c r="F127" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -3666,8 +3664,8 @@
       <c r="E128" t="s">
         <v>74</v>
       </c>
-      <c r="F128" s="7" t="s">
-        <v>216</v>
+      <c r="F128" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3686,8 +3684,8 @@
       <c r="E129" t="s">
         <v>37</v>
       </c>
-      <c r="F129" s="7" t="s">
-        <v>217</v>
+      <c r="F129" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3706,8 +3704,8 @@
       <c r="E130" t="s">
         <v>28</v>
       </c>
-      <c r="F130" s="7" t="s">
-        <v>218</v>
+      <c r="F130" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3726,8 +3724,8 @@
       <c r="E131" t="s">
         <v>74</v>
       </c>
-      <c r="F131" s="7" t="s">
-        <v>216</v>
+      <c r="F131" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -3746,8 +3744,8 @@
       <c r="E132" t="s">
         <v>24</v>
       </c>
-      <c r="F132" s="7" t="s">
-        <v>217</v>
+      <c r="F132" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -3766,8 +3764,8 @@
       <c r="E133" t="s">
         <v>26</v>
       </c>
-      <c r="F133" s="7" t="s">
-        <v>218</v>
+      <c r="F133" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -3786,8 +3784,8 @@
       <c r="E134" t="s">
         <v>16</v>
       </c>
-      <c r="F134" s="7" t="s">
-        <v>219</v>
+      <c r="F134" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -3806,8 +3804,8 @@
       <c r="E135" t="s">
         <v>16</v>
       </c>
-      <c r="F135" s="7" t="s">
-        <v>220</v>
+      <c r="F135" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -3826,8 +3824,8 @@
       <c r="E136" t="s">
         <v>16</v>
       </c>
-      <c r="F136" s="7" t="s">
-        <v>221</v>
+      <c r="F136" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -3835,10 +3833,10 @@
         <v>100</v>
       </c>
       <c r="B137" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C137" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D137" t="s">
         <v>65</v>
@@ -3846,8 +3844,8 @@
       <c r="E137" t="s">
         <v>74</v>
       </c>
-      <c r="F137" s="7" t="s">
-        <v>214</v>
+      <c r="F137" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -3855,19 +3853,19 @@
         <v>100</v>
       </c>
       <c r="B138" t="s">
+        <v>203</v>
+      </c>
+      <c r="C138" t="s">
+        <v>205</v>
+      </c>
+      <c r="D138" t="s">
+        <v>206</v>
+      </c>
+      <c r="E138" t="s">
+        <v>207</v>
+      </c>
+      <c r="F138" t="s">
         <v>209</v>
-      </c>
-      <c r="C138" t="s">
-        <v>211</v>
-      </c>
-      <c r="D138" t="s">
-        <v>212</v>
-      </c>
-      <c r="E138" t="s">
-        <v>213</v>
-      </c>
-      <c r="F138" s="7" t="s">
-        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\COTI SALUD 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A779A3-BCF6-4693-8CDA-D337B1647E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14415" windowHeight="11835"/>
   </bookViews>
   <sheets>
     <sheet name="REDES" sheetId="1" r:id="rId1"/>
     <sheet name="INFO_PLAN" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -473,165 +472,9 @@
     <t>Good Hope</t>
   </si>
   <si>
-    <t>Centro Médico Limatambo - Callao, Centro Médico Suiza Lab - Miraflores, Centro Médico Integramédica - Independencia, Clínica San Juan Bautista - SJL, Clínica Aviva - Los Olivos</t>
-  </si>
-  <si>
-    <t>Clínica Limatambo - SJL, Clínica Limatambo - San Isidro, Clínica Internacional - Lima, Clínica Santa Martha del Sur - SJM, Clínica Maisón de Sante - Chorrillos, Centro Médico Internacional - Surco, Clínica San Judas Tadeo - San Miguel, Clínica Vesalio - San Borja</t>
-  </si>
-  <si>
-    <t>Clínica Stella Maris - Pueblo Libre, Clínica Montefiori - La Molina, Clínica Jesús del Norte - Independencia, Clínica San Gabriel - San Miguel, Centro Médico Jockey Salud - Surco, Clínica Cayetano Heredia - SMP, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Good Hope - Miraflores, Clínica Limatambo - San Isidro</t>
-  </si>
-  <si>
-    <t>Clínica Limatambo - SJL, Clínica San Judas Tadeo - San Miguel, Clínica Santa Martha del Sur - SJM, Centro Médico Avendaño - Miraflores, Clínica Aviva - Los Olivos, Clínica Aviva - Lima, Clínica Maisón de Sante - Chorrillos</t>
-  </si>
-  <si>
-    <t>Centro Médico Limatambo - Callao, Clínica Bellavista - Callao, Centro Médico Suiza Lab - Miraflores, Clínica San Juan Bautista - SJL, Clínica Integramédica - San Isidro, Centro Médico Integramédica - Independencia, Clínica Cayetano Heredia - Lince, Centro Médico Ricardo Palma - Chorrillos, Centro Médico Medex - Surquillo</t>
-  </si>
-  <si>
-    <t>Clínica Good Hope - Miraflores, Clínica Cayetano Heredia - SMP, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Javier Prado - San Isidro</t>
-  </si>
-  <si>
-    <t>Clínica Tezza - Surco, Clínica Internacional - Lima, Clínica San Pablo - Surco</t>
-  </si>
-  <si>
-    <t>Clínica Internacional - San Borja</t>
-  </si>
-  <si>
-    <t>Centro Médico Avendaño - Miraflores, Clínica Limatambo - SJL, Clínica San Judas Tadeo - San Miguel, Clínica Santa Martha del Sur - SJM, Clínica Aviva - Los Olivos, Clínica Aviva - Lima, Clínica Maisón de Sante - Chorrillos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clínica Tezza - Surco, Clínica Internacional - Lima, Clínica Ricardo Palma - San Isidro, Clínica San Pablo - Surco, Clínica Santa Isabel - San Borja, Clínica San Juan De Dios - San Luis, Centro Médico Sanna - La Molina, Clínica El Golf - San Isidro, Centro Médico Sanna - Surco, Centro Médico Sanna - Miraflores  </t>
-  </si>
-  <si>
-    <t>Clínica Angloamericana - La Molina, Clínica Angloamericana - San Isidro, Centro Médico San Felipe - La Molina, Clínica San Felipe - Jesús María, Clínica Miraflores - Miraflores</t>
-  </si>
-  <si>
-    <t>Clínica Delgado - Miraflores</t>
-  </si>
-  <si>
-    <t>Centro Médico Jockey Salud - Surco, Clínica Limatambo - San Isidro, Clínica Montefiori - La Molina, Clínica Providencia - San Miguel, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Clínica Medavan - Magdalena, Clínica Especialidades Médicas - San Borja, Centro Médico Internacional - San Isidro, Clínica San Gabriel - San Miguel, Centro Médico Internacional - Surco, Centro Médico Internacional - La Molina,  Clínica Jesús del Norte - Independencia</t>
-  </si>
-  <si>
-    <t>Clínica San Judas Tadeo - San Miguel, Centro Médico Suiza Lab - Miraflores, Clínica Santa Martha del Sur - SJM, Centro Médico Limatambo - Callao, Clínica Limatambo - SJL, Centro Médico Integramédica - Independencia, Clínica Integramédica - San Isidro, Clínica San Bernardo - Pueblo Libre, Clínica San Juan Bautista - SJL, Clínica MegaSalud Universal - Lima</t>
-  </si>
-  <si>
-    <t>Clínica Bellavista - Callao, Clínica Limatambo - San Isidro, Clínica Good Hope - Miraflores, Clínica Montefiori - La Molina, Centro Médico Jockey Salud - Surco, Clínica Medavan - Magdalena, Clínica Providencia - San Miguel, Clínica Versalles - Comas, Centro Médico Medex - Surquillo, Clínica Maisón de Sante - Chorrillos, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Clínica Cayetano Heredia - SMP</t>
-  </si>
-  <si>
-    <t>Centro Médico Internacional - San Isidro, Centro Médico Internacional - La Molina, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Tezza - Surco, Clínica San Gabriel - San Miguel, Clínica Javier Prado - San Isidro, Clínica Especialidades Médicas - San Borja</t>
-  </si>
-  <si>
-    <t>Clínica Internacional - Lima, Centro Médico Internacional - Surco, Clínica Jesús del Norte - Independencia</t>
-  </si>
-  <si>
-    <t>Clínica Angloamericana - La Molina, Clínica Angloamericana - San Isidro</t>
-  </si>
-  <si>
-    <t>Centro Médico Limatambo - Callao, Clínica Maisón de Sante - Lima, Clínica Maisón de Sante - Chorrillos, Clínica Versalles - Comas, Clínica Mundo Salud - Los Olivos, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM</t>
-  </si>
-  <si>
-    <t>Centro Médico Jockey Salud - Surco, Centro Médico Sanna - La Molina, Centro Médico Sanna - Miraflores, Centro Médico Sanna - Surco, Centro Médico Sanna - Los Olivos, Centro Médico Sanna - San Miguel, Centro Médico Sanna - San Juan de Lurigancho, Centro Médico Ricardo Palma - Chorrillos, Centro Médico Integramédica - Independencia, Clínica Medavan - Magdalena, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Clínica Limatambo - San Isidro, Clínica Limatambo - SJL, Clínica Cayetano Heredia - SMP, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Clínica Aviva - Los Olivos, Clínica Aviva - Lima</t>
-  </si>
-  <si>
-    <t>Clínica Montefiori - La Molina, Clínica Good Hope - Miraflores, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica San Gabriel - San Miguel</t>
-  </si>
-  <si>
-    <t>Centro Médico Limatambo - Callao, Clínica Maisón de Sante - Lima, Clínica Maisón de Sante - Chorrillos, Clínica Versalles - Comas, Centro Médico Cayetano Heredia - Lince,  Clínica Mundo Salud - Los Olivos, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM</t>
-  </si>
-  <si>
-    <t>Clínica Montefiori - La Molina, Clínica Good Hope - Miraflores, Clínica San Gabriel - San Miguel</t>
-  </si>
-  <si>
-    <t>Clínica Montefiori - La Molina, Clínica Good Hope - Miraflores, Clínica San Gabriel - San Miguel, Clínica Jesús del Norte - Independencia, Clínica Javier Prado - San Isidro</t>
-  </si>
-  <si>
-    <t>Clínica Ricardo Palma - San Isidro, Clínica San Pablo - Surco, Clínica Internacional - San Borja</t>
-  </si>
-  <si>
-    <t>Centro Médico Integramédica - Independencia, Clínica Versalles - Comas, Clínica Mundo Salud - Los Olivos, Clínica Virgen del Rosario - Magdalena, Clínica Montefiori - La Molina, Clínica Providencia - San Miguel, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM</t>
-  </si>
-  <si>
-    <t>Centro Médico Sanna - Miraflores, Centro Médico Sanna - Surco, Centro Médico Sanna - La Molina, Centro Médico Sanna - Los Olivos, Centro Médico Sanna - San Miguel, Centro Médico Sanna - San Juan de Lurigancho, Centro Médico Ricardo Palma - Chorrillos, Clínica Bellavista - Callao, Clínica Medavan - Magdalena, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Centro Médico Limatambo - Callao, Centro Médico Los Álamos - Surquillo, Clínica Limatambo - San Isidro, Clínica Limatambo - SJL, Clínica Cayetano Heredia - SMP, Clínica San Judas Tadeo - San Miguel, Centro Médico Jockey Salud - Surco, Clínica Aviva - Lima</t>
-  </si>
-  <si>
-    <t>Clínica Good Hope - Miraflores, Clínica Javier Prado - San Isidro, Clínica Maisón de Sante - Chorrillos, Clínica Aviva - Los Olivos, Clínica San Gabriel - San Miguel</t>
-  </si>
-  <si>
     <t>S/160 al 60%</t>
   </si>
   <si>
-    <t>Centro Médico Sanna - Miraflores, Centro Médico Sanna - Surco, Centro Médico Sanna - La Molina, Centro Médico Sanna - Los Olivos, Centro Médico Sanna - San Miguel, Centro Médico Sanna - San Juan de Lurigancho</t>
-  </si>
-  <si>
-    <t>Centro Médico Integramédica - Independencia, Clínica Versalles - Comas, Clínica Mundo Salud - Los Olivos, Clínica Montefiori - La Molina, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Centro Médico Ricardo Palma - Chorrillos, Centro Médico Limatambo - Callao, Clínica Limatambo - SJL, Clínica Medavan - Magdalena, Clínica Virgen del Rosario - Magdalena, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Clínica Limatambo - San Isidro, Clínica Aviva - Lima, Centro Médico Los Álamos - Surquillo, Clínica Cayetano Heredia - SMP, Centro Médico Jockey Salud - Surco</t>
-  </si>
-  <si>
-    <t>Clínica Good Hope - Miraflores, Clínica Javier Prado - San Isidro, Clínica Maisón de Sante - Chorrillos, Clínica Aviva - Los Olivos, Clínica San Gabriel - San Miguel, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Maisón de Sante - Lima, Clínica Jesús del Norte - Independencia</t>
-  </si>
-  <si>
-    <t>Clínica Miraflores - Miraflores, Centro Médico San Felipe - La Molina, Clínica San Felipe - Jesús María, Centro Médico San Felipe - Surco</t>
-  </si>
-  <si>
-    <t>Clínica Delgado - Miraflores, Clínica Auna - San Isidro</t>
-  </si>
-  <si>
-    <t>Centro Médico Integramédica - Independencia, Clínica Versalles - Comas, Clínica Mundo Salud - Los Olivos, Clínica Montefiori - La Molina, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Centro Médico Ricardo Palma - Chorrillos, Centro Médico Limatambo - Callao, Clínica Limatambo - SJL, Clínica Medavan - Magdalena, Clínica Virgen del Rosario - Magdalena, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Clínica Limatambo - San Isidro, Clínica Aviva - Lima, Centro Médico Los Álamos - Surquillo, Clínica Cayetano Heredia - SMP, Centro Médico Jockey Salud - Surco, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Javier Prado - San Isidro</t>
-  </si>
-  <si>
-    <t>Clínica Good Hope - Miraflores, Clínica Maisón de Sante - Chorrillos, Clínica Aviva - Los Olivos, Clínica San Gabriel - San Miguel, Clínica Maisón de Sante - Lima, Clínica Jesús del Norte - Independencia, Clínica Tezza - Surco</t>
-  </si>
-  <si>
-    <t>Clínica Santa Isabel - San Borja, Clínica Ricardo Palma - San Isidro, Centro Médico Internacional - San Isidro, Clínica Internacional - San Borja, Centro Médico Internacional - Surco</t>
-  </si>
-  <si>
-    <t>Centro Médico Integramédica - Independencia, Clínica Versalles - Comas, Clínica Mundo Salud - Los Olivos, Clínica Montefiori - La Molina, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Centro Médico Ricardo Palma - Chorrillos, Centro Médico Limatambo - Callao, Clínica Limatambo - SJL, Clínica Medavan - Magdalena, Clínica Virgen del Rosario - Magdalena, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Clínica Limatambo - San Isidro, Clínica Aviva - Lima, Centro Médico Los Álamos - Surquillo, Clínica Cayetano Heredia - SMP, Centro Médico Jockey Salud - Surco, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Javier Prado - San Isidro, Clínica Aviva - Los Olivos</t>
-  </si>
-  <si>
-    <t>Clínica Good Hope - Miraflores, Clínica Maisón de Sante - Chorrillos, Clínica San Gabriel - San Miguel, Clínica Maisón de Sante - Lima, Clínica Jesús del Norte - Independencia, Clínica Tezza - Surco</t>
-  </si>
-  <si>
-    <t>Clínica Miraflores - Miraflores, Clínica Angloamericana - La Molina, Clínica Angloamericana - San Isidro, Centro Médico San Felipe - La Molina, Clínica San Felipe - Jesús María, Centro Médico San Felipe - Surco</t>
-  </si>
-  <si>
-    <t>Clínica Montesur - Surco, Clínica Auna - San Isidro</t>
-  </si>
-  <si>
-    <t>Centro Médico La Positiva - Surco</t>
-  </si>
-  <si>
-    <t>Clínica Cayetano Heredia - SMP, Clínica Montefiori - La Molina</t>
-  </si>
-  <si>
-    <t>Clínica Stella Maris - Pueblo Libre, Clínica Bellavista - Callao, Centro Médico Limatambo - Callao, Clínica Maisón de Sante - Lima, Clínica San Judas Tadeo - San Miguel, Clínica Limatambo - SJL, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM, Clínica Versalles - Comas, Clínica San Juan De Dios - San Luis, Clínica San Bernardo - Pueblo Libre, Clínica La Luz - Lima, Clínica Poémape - Chancay, Clínica La Solidaridad - Barranca, Centro Médico AltaSalud - Barranca, Centro Médico Medex - Surquillo, Clínica Antonio Raymondi - La Victoria, Clínica Aviva - Lima, Clínica Arthrosalud - Lima, Centro Médico Integramédica - Independencia, Clínica Maisón de Sante - Chorrillos, Clínica San Pedro - Huara, Clínica Medavan - Magdalena, Clínica San Clemente - Lince, Centro Médico Cayetano Heredia - Lince, Clínica Aviva - Los Olivos, Clínica Aviva - Lima, Clínica San Bartolomé - Huacho</t>
-  </si>
-  <si>
-    <t>Clínica San Marcos - Huara, Clínica Providencia - San Miguel, Centro Médico Ricardo Palma - Chorrillos, Clínica Sanens - Surquillo, Centro Médico Jockey Salud - Surco, Clínica Limatambo - San Isidro, Centro Médico AltaSalud - San Isidro, Clínica Vesalio - San Borja, Centro Médico Sanna - La Molina, Centro Médico Sanna - Miraflores, Clínica Good Hope - Miraflores, Clínica Corazón de Jesús - Cañete, Centro Médico Clisova - Chancay, Centro Médico Clisova - Huaral, Centro Médico Nueva Esperanza - Huaral</t>
-  </si>
-  <si>
-    <t>Clínica Jesús del Norte - Independencia, Clínica San Gabriel - San Miguel, Clínica Javier Prado - San Isidro, Clínica Tezza - Surco, Clínica Maisón de Sante - Surco</t>
-  </si>
-  <si>
-    <t>Clínica El Golf - San Isidro, Clínica Santa Isabel - San Borja, Centro Médico Sanna - Surco, Clínica Auna - San Isidro, Clínica Alvarez - Surco, Clínica Del Inca - Miraflores</t>
-  </si>
-  <si>
-    <t>Clínica San Pablo - Surco, Clínica Ricardo Palma - San Isidro, Centro Médico Sormedic - Lima, Centro Médico Urozen - San Borja</t>
-  </si>
-  <si>
-    <t>Centro Médico Limatambo - Callao, Clínica Cayetano Heredia - SMP, Clínica Maisón de Sante - Lima, Clínica MegaSalud Universal - Lima, Clínica Limatambo - SJL, Clínica San Juan Bautista - SJL, Clínica Santa Martha del Sur - SJM, Clínica Versalles - Comas, Clínica San Juan De Dios - San Luis, Clínica San Bernardo - Pueblo Libre, Clínica La Luz - Lima, Clínica Poémape - Chancay, Clínica Montefiori - La Molina</t>
-  </si>
-  <si>
-    <t>Centro Médico SBC Medic - Barranco, Clínica La Solidaridad - Barranca, Centro Médico AltaSalud - Barranca, Clínica Antonio Raymondi - La Victoria,  Centro Médico Medex - Surquillo, Clínica Aviva - Lima, Clínica Arthrosalud - Lima, Clínica Bellavista - Callao, Centro Médico Integramédica - Independencia, Clínica Bellavista - Callao, Clínica Maisón de Sante - Chorrillos, Clínica San Judas Tadeo - San Miguel, Clínica San Pedro - Huara, Clínica Stella Maris - Pueblo Libre, Clínica San Clemente - Lince, Centro Médico Cayetano Heredia - Lince, Clínica Aviva - Los Olivos, Clínica San Bartolomé - Huacho</t>
-  </si>
-  <si>
-    <t>Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Providencia - San Miguel, Clínica Good Hope - Miraflores, Clínica Limatambo - San Isidro, Clínica Sanens - Surquillo, Clínica Medavan - Magdalena, Centro Médico Ricardo Palma - Chorrillos, Clínica San Marcos - Huaura, Clínica Vesalio - San Borja, Centro Médico Jockey Salud - Surco, Centro Médico AltaSalud - San Isidro, Centro Médico Sanna - La Molina, Centro Médico Sanna - Miraflores, Clínica Higuereta - Miraflores, Clínica Corazón de Jesús - Cañete, Centro Médico Clisova - Chancay, Centro Médico Clisova - Huaral, Centro Médico Nueva Esperanza - Huaral</t>
-  </si>
-  <si>
-    <t>Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Providencia - San Miguel, Clínica Good Hope - Miraflores, Clínica Limatambo - San Isidro, Clínica Sanens - Surquillo, Centro Médico Ricardo Palma - Chorrillos, Clínica San Marcos - Huaura, Clínica Vesalio - San Borja, Centro Médico Jockey Salud - Surco, Centro Médico AltaSalud - San Isidro, Centro Médico Sanna - La Molina, Centro Médico Sanna - Miraflores, Clínica Higuereta - Miraflores, Clínica Corazón de Jesús - Cañete, Centro Médico Clisova - Chancay, Centro Médico Clisova - Huaral, Centro Médico Nueva Esperanza - Huaral</t>
-  </si>
-  <si>
-    <t>Clínica Internacional - Lima, Centro Médico Internacional - San Isidro, Centro Médico Internacional - Surco, Centro Médico Internacional - La Molina, Clínica Internacional - San Borja, Clínica Delgado - Miraflores, Centro Médico San Felipe - La Molina, Clínica Angloamericana - San Isidro, Clínica Angloamericana - La Molina, Clínica San Felipe - Jesús María</t>
-  </si>
-  <si>
     <t>Salud Total</t>
   </si>
   <si>
@@ -647,70 +490,226 @@
     <t>S/650 al 80%</t>
   </si>
   <si>
-    <t>Centro Médico Mapfre - Independencia, Centro Médico Mapfre - Magdalena, Centro Médico Mapfre - San Miguel, Centro Médico Mapfre - Surco, Clínica Integramédica - San Isidro</t>
-  </si>
-  <si>
-    <t>Clínica Ricardo Palma - San Isidro</t>
-  </si>
-  <si>
-    <t>Centro Médico Mapfre - Independencia, Centro Médico Mapfre - Magdalena, Centro Médico Mapfre - San Miguel, Centro Médico Mapfre - Surco</t>
-  </si>
-  <si>
-    <t>Clínica Montefiori - La Molina, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Clínica Jesús del Norte - Independencia, Centro Médico Medex - Surquillo, Clínica Los Andes - Miraflores, Clínica San Juan Bautista - SJL, Clínica Aviva - Los Olivos, Clínica Virgen del Rosario - Magdalena, Clínica Cayetano Heredia - SMP, Clínica Santa Martha del Sur - SJM, Clínica Limatambo - SJL, Centro Médico Limatambo - Callao, Centro Médico Suiza Lab - Miraflores, Centro Médico Suiza Lab - Surco, Clínica Mundo Salud - Los Olivos, Clínica Medavan - Magdalena, Clínica Santa María - Surquillo, Clínica Especialidades Médicas - San Borja, Clínica Maisón de Sante - Chorrillos, Clínica Maisón de Sante - Lima, Clínica San Juan De Dios - San Luis, Clínica San Vicente - SMP, Clínica Integramédica - San Isidro</t>
-  </si>
-  <si>
-    <t>Clínica Javier Prado - San Isidro, Clínica San Gabriel - San Miguel, Clínica Tezza - Surco, Clínica Centenario Peruano Japonesa - Pueblo Libre, Centro Médico Jockey Salud - Surco, Clínica Good Hope - Miraflores, Clínica Bellavista - Callao, Clínica Stella Maris - Pueblo Libre, Clínica Limatambo - San Isidro, Clínica Vesalio - San Borja, Centro Médico Ricardo Palma - Chorrillos, Clínica La Luz - Lima</t>
-  </si>
-  <si>
-    <t>Clínica Delgado - Miraflores, Clínica Auna - San Isidro, Clínica Ricardo Palma - San Isidro, Clínica San Pablo - Surco, Clínica San Pablo - Asia</t>
-  </si>
-  <si>
-    <t>Clínica Angloamericana - La Molina, Clínica Angloamericana - San Isidro, Centro Médico San Felipe - La Molina, Clínica San Felipe - Jesús María, Clínica Miraflores - Miraflores, Clínica San Felipe - Jesús María, Clínica Miraflores - Miraflores, Clínica Montesur - Surco</t>
-  </si>
-  <si>
-    <t>Centro Médico Jockey Salud - Surco, Clínica Limatambo - San Isidro, Clínica Montefiori - La Molina, Clínica Providencia - San Miguel, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Clínica Medavan - Magdalena, Clínica Especialidades Médicas - San Borja, Centro Médico Internacional - San Isidro, Clínica San Gabriel - San Miguel, Centro Médico Internacional - Surco, Centro Médico Internacional - La Molina, Clínica Jesús del Norte - Independencia</t>
-  </si>
-  <si>
-    <t>Clínica Santa Isabel - San Borja, Clínica Internacional - San Borja</t>
-  </si>
-  <si>
-    <t>Centro Médico SBC Medic - Barranco, Clínica La Solidaridad - Barranca, Centro Médico AltaSalud - Barranca, Clínica Antonio Raymondi - La Victoria, Centro Médico Medex - Surquillo, Clínica Aviva - Lima, Clínica Arthrosalud - Lima, Clínica Bellavista - Callao, Centro Médico Integramédica - Independencia, Clínica Bellavista - Callao, Clínica Maisón de Sante - Chorrillos, Clínica San Judas Tadeo - San Miguel, Clínica San Pedro - Huara, Clínica Stella Maris - Pueblo Libre, Clínica San Clemente - Lince, Centro Médico Cayetano Heredia - Lince, Clínica Aviva - Los Olivos, Clínica San Bartolomé - Huacho</t>
-  </si>
-  <si>
-    <t>Centro Médico SBC Medic - Barranco, Clínica La Solidaridad - Barranca, Centro Médico AltaSalud - Barranca, Clínica Antonio Raymondi - La Victoria, Centro Médico Medex - Surquillo, Clínica Aviva - Lima, Clínica Arthrosalud - Lima, Clínica Bellavista - Callao, Centro Médico Integramédica - Independencia, Clínica Bellavista - Callao, Clínica Maisón de Sante - Chorrillos, Clínica San Judas Tadeo - San Miguel, Clínica San Pedro - Huara, Clínica Stella Maris - Pueblo Libre, Clínica San Clemente - Lince, Centro Médico Cayetano Heredia - Lince, Clínica Aviva - Los Olivos, Clínica San Bartolomé - Huacho, Clínica Medavan - Magdalena</t>
-  </si>
-  <si>
-    <t>Clínica Sanna - San Borja, Clínica Centenario Peruano Japonesa - Pueblo Libre</t>
-  </si>
-  <si>
-    <t>Centro Médico Ricardo Palma - Chorrillos, Centro Médico Integramédica - Independencia, Centro Médico Sanna - Miraflores, Centro Médico Sanna - La Molina, Centro Médico Sanna - San Miguel, Centro Médico Sanna - Los Olivos, Centro Médico Sanna - San Juan de Lurigancho, Clínica Stella Maris - Pueblo Libre, Clínica Vesalio - San Borja, Centro Médico Sanna - Surco, Clínica Limatambo - San Isidro, Clínica Limatambo - SJL, Clínica Providencia - San Miguel, Clínica San Judas Tadeo - San Miguel, Clínica Centenario Peruano Japonesa - Pueblo Libre, Clínica Aviva - Los Olivos, Clínica Aviva - Lima, Centro Médico Jockey Salud - Surco, Clínica Cayetano Heredia - SMP</t>
-  </si>
-  <si>
-    <t>Clínica Internacional - San Borja, Clínica Sanna - San Borja, Clínica Montesur - Surco</t>
-  </si>
-  <si>
-    <t>Clínica San Pablo - Surco, Clínica Ricardo Palma - San Isidro, Clínica Santa Isabel - San Borja, Clínica El Golf - San Isidro, Clínica Internacional - San Borja, Clínica Sanna - San Borja, Clínica San Juan De Dios - San Luis, Centro Médico Sanna - La Molina</t>
-  </si>
-  <si>
-    <t>Clínica Internacional - Lima, Clínica Sanna - San Borja, Clínica El Golf - San Isidro, Clínica Tezza - Surco</t>
-  </si>
-  <si>
-    <t>Clínica Sanna - San Borja, Clínica Bellavista - Callao, Clínica Especialidades Médicas - San Borja, Clínica El Golf - San Isidro, Clínica Maisón de Sante - Surco, Clínica Tezza - Surco, Clínica Internacional - Lima, Clínica San Pablo - Surco</t>
-  </si>
-  <si>
-    <t>Clínica Sanna - San Borja, Clínica Bellavista - Callao, Clínica Especialidades Médicas - San Borja, Clínica El Golf - San Isidro, Clínica Maisón de Sante - Surco, Clínica Internacional - Lima, Clínica San Pablo - Surco</t>
-  </si>
-  <si>
-    <t>Clínica Sanna - San Borja, Clínica Montesur - Surco, Clínica San Pablo - Asia</t>
-  </si>
-  <si>
-    <t>Clínica Santa Isabel - San Borja, Clínica Sanna - San Borja, Clínica El Golf - San Isidro, Centro Médico Sanna - La Molina, Clínica Maisón de Sante - Surco, Clínica Internacional - Lima, Clínica Internacional - San Borja</t>
+    <t>Cl. Good Hope - Miraflores, Cl. Cayetano Heredia - SMP, Cl. Centenario Peruano Japonesa - Pueblo Libre, Cl. Javier Prado - San Isidro</t>
+  </si>
+  <si>
+    <t>Cl. Tezza - Surco, Cl. Internacional - Lima, Cl. San Pablo - Surco</t>
+  </si>
+  <si>
+    <t>Cl. Internacional - San Borja</t>
+  </si>
+  <si>
+    <t>Cl. Internacional - San Borja, Cl. Sanna - San Borja, Cl. Montesur - Surco</t>
+  </si>
+  <si>
+    <t>Cl. Delgado - Miraflores</t>
+  </si>
+  <si>
+    <t>Cl. Santa Isabel - San Borja, Cl. Internacional - San Borja</t>
+  </si>
+  <si>
+    <t>Cl. Angloamericana - La Molina, Cl. Angloamericana - San Isidro</t>
+  </si>
+  <si>
+    <t>Cl. Montefiori - La Molina, Cl. Good Hope - Miraflores, Cl. Centenario Peruano Japonesa - Pueblo Libre, Cl. San Gabriel - San Miguel</t>
+  </si>
+  <si>
+    <t>Cl. Montefiori - La Molina, Cl. Good Hope - Miraflores, Cl. San Gabriel - San Miguel</t>
+  </si>
+  <si>
+    <t>Cl. Montefiori - La Molina, Cl. Good Hope - Miraflores, Cl. San Gabriel - San Miguel, Cl. Jesús del Norte - Independencia, Cl. Javier Prado - San Isidro</t>
+  </si>
+  <si>
+    <t>Cl. Internacional - Lima, Cl. Sanna - San Borja, Cl. El Golf - San Isidro, Cl. Tezza - Surco</t>
+  </si>
+  <si>
+    <t>Cl. Ricardo Palma - San Isidro, Cl. San Pablo - Surco, Cl. Internacional - San Borja</t>
+  </si>
+  <si>
+    <t>Cl. Good Hope - Miraflores, Cl. Javier Prado - San Isidro, Cl. Maisón de Sante - Chorrillos, Cl. Aviva - Los Olivos, Cl. San Gabriel - San Miguel</t>
+  </si>
+  <si>
+    <t>Cl. Sanna - San Borja, Cl. Centenario Peruano Japonesa - Pueblo Libre</t>
+  </si>
+  <si>
+    <t>Cl. Good Hope - Miraflores, Cl. Javier Prado - San Isidro, Cl. Maisón de Sante - Chorrillos, Cl. Aviva - Los Olivos, Cl. San Gabriel - San Miguel, Cl. Centenario Peruano Japonesa - Pueblo Libre, Cl. Maisón de Sante - Lima, Cl. Jesús del Norte - Independencia</t>
+  </si>
+  <si>
+    <t>Cl. Sanna - San Borja, Cl. Bellavista - Callao, Cl. Especialidades Médicas - San Borja, Cl. El Golf - San Isidro, Cl. Maisón de Sante - Surco, Cl. Tezza - Surco, Cl. Internacional - Lima, Cl. San Pablo - Surco</t>
+  </si>
+  <si>
+    <t>Cl. Delgado - Miraflores, Cl. Auna - San Isidro</t>
+  </si>
+  <si>
+    <t>Cl. Good Hope - Miraflores, Cl. Maisón de Sante - Chorrillos, Cl. San Gabriel - San Miguel, Cl. Maisón de Sante - Lima, Cl. Jesús del Norte - Independencia, Cl. Tezza - Surco</t>
+  </si>
+  <si>
+    <t>Cl. Sanna - San Borja, Cl. Bellavista - Callao, Cl. Especialidades Médicas - San Borja, Cl. El Golf - San Isidro, Cl. Maisón de Sante - Surco, Cl. Internacional - Lima, Cl. San Pablo - Surco</t>
+  </si>
+  <si>
+    <t>Cl. Montesur - Surco, Cl. Auna - San Isidro</t>
+  </si>
+  <si>
+    <t>Cl. Good Hope - Miraflores, Cl. Maisón de Sante - Chorrillos, Cl. Aviva - Los Olivos, Cl. San Gabriel - San Miguel, Cl. Maisón de Sante - Lima, Cl. Jesús del Norte - Independencia, Cl. Tezza - Surco</t>
+  </si>
+  <si>
+    <t>Cl. Cayetano Heredia - SMP, Cl. Montefiori - La Molina</t>
+  </si>
+  <si>
+    <t>Cl. Jesús del Norte - Independencia, Cl. San Gabriel - San Miguel, Cl. Javier Prado - San Isidro, Cl. Tezza - Surco, Cl. Maisón de Sante - Surco</t>
+  </si>
+  <si>
+    <t>Cl. Sanna - San Borja, Cl. Montesur - Surco, Cl. San Pablo - Asia</t>
+  </si>
+  <si>
+    <t>Cl. Delgado - Miraflores, Cl. Auna - San Isidro, Cl. Ricardo Palma - San Isidro, Cl. San Pablo - Surco, Cl. San Pablo - Asia</t>
+  </si>
+  <si>
+    <t>Cl. Ricardo Palma - San Isidro</t>
+  </si>
+  <si>
+    <t>C.M. Limatambo - Callao, C.M. Suiza Lab - Miraflores, C.M. Integramédica - Independencia, Cl. San Juan Bautista - SJL, Cl. Aviva - Los Olivos</t>
+  </si>
+  <si>
+    <t>Cl. Limatambo - SJL, Cl. Limatambo - San Isidro, Cl. Internacional - Lima, Cl. Santa Martha del Sur - SJM, Cl. Maisón de Sante - Chorrillos, C.M. Internacional - Surco, Cl. San Judas Tadeo - San Miguel, Cl. Vesalio - San Borja</t>
+  </si>
+  <si>
+    <t>Cl. Stella Maris - Pueblo Libre, Cl. Montefiori - La Molina, Cl. Jesús del Norte - Independencia, Cl. San Gabriel - San Miguel, C.M. Jockey Salud - Surco, Cl. Cayetano Heredia - SMP, Cl. Centenario Peruano Japonesa - Pueblo Libre, Cl. Good Hope - Miraflores, Cl. Limatambo - San Isidro</t>
+  </si>
+  <si>
+    <t>C.M. Limatambo - Callao, Cl. Bellavista - Callao, C.M. Suiza Lab - Miraflores, Cl. San Juan Bautista - SJL, Cl. Integramédica - San Isidro, C.M. Integramédica - Independencia, Cl. Cayetano Heredia - Lince, C.M. Ricardo Palma - Chorrillos, C.M. Medex - Surquillo</t>
+  </si>
+  <si>
+    <t>Cl. Limatambo - SJL, Cl. San Judas Tadeo - San Miguel, Cl. Santa Martha del Sur - SJM, C.M. Avendaño - Miraflores, Cl. Aviva - Los Olivos, Cl. Aviva - Lima, Cl. Maisón de Sante - Chorrillos</t>
+  </si>
+  <si>
+    <t>C.M. Jockey Salud - Surco, Cl. Limatambo - San Isidro, Cl. Montefiori - La Molina, Cl. Providencia - San Miguel, Cl. Stella Maris - Pueblo Libre, Cl. Vesalio - San Borja, Cl. Medavan - Magdalena, Cl. Especialidades Médicas - San Borja, C.M. Internacional - San Isidro, Cl. San Gabriel - San Miguel, C.M. Internacional - Surco, C.M. Internacional - La Molina,  Cl. Jesús del Norte - Independencia</t>
+  </si>
+  <si>
+    <t>C.M. Avendaño - Miraflores, Cl. Limatambo - SJL, Cl. San Judas Tadeo - San Miguel, Cl. Santa Martha del Sur - SJM, Cl. Aviva - Los Olivos, Cl. Aviva - Lima, Cl. Maisón de Sante - Chorrillos</t>
+  </si>
+  <si>
+    <t>C.M. Jockey Salud - Surco, Cl. Limatambo - San Isidro, Cl. Montefiori - La Molina, Cl. Providencia - San Miguel, Cl. Stella Maris - Pueblo Libre, Cl. Vesalio - San Borja, Cl. Medavan - Magdalena, Cl. Especialidades Médicas - San Borja, C.M. Internacional - San Isidro, Cl. San Gabriel - San Miguel, C.M. Internacional - Surco, C.M. Internacional - La Molina, Cl. Jesús del Norte - Independencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cl. Tezza - Surco, Cl. Internacional - Lima, Cl. Ricardo Palma - San Isidro, Cl. San Pablo - Surco, Cl. Santa Isabel - San Borja, Cl. San Juan De Dios - San Luis, C.M. Sanna - La Molina, Cl. El Golf - San Isidro, C.M. Sanna - Surco, C.M. Sanna - Miraflores  </t>
+  </si>
+  <si>
+    <t>Cl. Angloamericana - La Molina, Cl. Angloamericana - San Isidro, C.M. San Felipe - La Molina, Cl. San Felipe - Jesús María, Cl. Miraflores - Miraflores</t>
+  </si>
+  <si>
+    <t>Cl. San Judas Tadeo - San Miguel, C.M. Suiza Lab - Miraflores, Cl. Santa Martha del Sur - SJM, C.M. Limatambo - Callao, Cl. Limatambo - SJL, C.M. Integramédica - Independencia, Cl. Integramédica - San Isidro, Cl. San Bernardo - Pueblo Libre, Cl. San Juan Bautista - SJL, Cl. MegaSalud Universal - Lima</t>
+  </si>
+  <si>
+    <t>Cl. Bellavista - Callao, Cl. Limatambo - San Isidro, Cl. Good Hope - Miraflores, Cl. Montefiori - La Molina, C.M. Jockey Salud - Surco, Cl. Medavan - Magdalena, Cl. Providencia - San Miguel, Cl. Versalles - Comas, C.M. Medex - Surquillo, Cl. Maisón de Sante - Chorrillos, Cl. Stella Maris - Pueblo Libre, Cl. Vesalio - San Borja, Cl. Cayetano Heredia - SMP</t>
+  </si>
+  <si>
+    <t>C.M. Internacional - San Isidro, C.M. Internacional - La Molina, Cl. Centenario Peruano Japonesa - Pueblo Libre, Cl. Tezza - Surco, Cl. San Gabriel - San Miguel, Cl. Javier Prado - San Isidro, Cl. Especialidades Médicas - San Borja</t>
+  </si>
+  <si>
+    <t>Cl. Internacional - Lima, C.M. Internacional - Surco, Cl. Jesús del Norte - Independencia</t>
+  </si>
+  <si>
+    <t>Cl. San Pablo - Surco, Cl. Ricardo Palma - San Isidro, Cl. Santa Isabel - San Borja, Cl. El Golf - San Isidro, Cl. Internacional - San Borja, Cl. Sanna - San Borja, Cl. San Juan De Dios - San Luis, C.M. Sanna - La Molina</t>
+  </si>
+  <si>
+    <t>C.M. Limatambo - Callao, Cl. Maisón de Sante - Lima, Cl. Maisón de Sante - Chorrillos, Cl. Versalles - Comas, Cl. Mundo Salud - Los Olivos, Cl. San Juan Bautista - SJL, Cl. Santa Martha del Sur - SJM</t>
+  </si>
+  <si>
+    <t>C.M. Jockey Salud - Surco, C.M. Sanna - La Molina, C.M. Sanna - Miraflores, C.M. Sanna - Surco, C.M. Sanna - Los Olivos, C.M. Sanna - San Miguel, C.M. Sanna - San Juan de Lurigancho, C.M. Ricardo Palma - Chorrillos, C.M. Integramédica - Independencia, Cl. Medavan - Magdalena, Cl. Stella Maris - Pueblo Libre, Cl. Vesalio - San Borja, Cl. Limatambo - San Isidro, Cl. Limatambo - SJL, Cl. Cayetano Heredia - SMP, Cl. Providencia - San Miguel, Cl. San Judas Tadeo - San Miguel, Cl. Aviva - Los Olivos, Cl. Aviva - Lima</t>
+  </si>
+  <si>
+    <t>C.M. Limatambo - Callao, Cl. Maisón de Sante - Lima, Cl. Maisón de Sante - Chorrillos, Cl. Versalles - Comas, C.M. Cayetano Heredia - Lince,  Cl. Mundo Salud - Los Olivos, Cl. San Juan Bautista - SJL, Cl. Santa Martha del Sur - SJM</t>
+  </si>
+  <si>
+    <t>C.M. Ricardo Palma - Chorrillos, C.M. Integramédica - Independencia, C.M. Sanna - Miraflores, C.M. Sanna - La Molina, C.M. Sanna - San Miguel, C.M. Sanna - Los Olivos, C.M. Sanna - San Juan de Lurigancho, Cl. Stella Maris - Pueblo Libre, Cl. Vesalio - San Borja, C.M. Sanna - Surco, Cl. Limatambo - San Isidro, Cl. Limatambo - SJL, Cl. Providencia - San Miguel, Cl. San Judas Tadeo - San Miguel, Cl. Centenario Peruano Japonesa - Pueblo Libre, Cl. Aviva - Los Olivos, Cl. Aviva - Lima, C.M. Jockey Salud - Surco, Cl. Cayetano Heredia - SMP</t>
+  </si>
+  <si>
+    <t>C.M. Integramédica - Independencia, Cl. Versalles - Comas, Cl. Mundo Salud - Los Olivos, Cl. Virgen del Rosario - Magdalena, Cl. Montefiori - La Molina, Cl. Providencia - San Miguel, Cl. San Juan Bautista - SJL, Cl. Santa Martha del Sur - SJM</t>
+  </si>
+  <si>
+    <t>C.M. Sanna - Miraflores, C.M. Sanna - Surco, C.M. Sanna - La Molina, C.M. Sanna - Los Olivos, C.M. Sanna - San Miguel, C.M. Sanna - San Juan de Lurigancho, C.M. Ricardo Palma - Chorrillos, Cl. Bellavista - Callao, Cl. Medavan - Magdalena, Cl. Stella Maris - Pueblo Libre, Cl. Vesalio - San Borja, C.M. Limatambo - Callao, C.M. Los Álamos - Surquillo, Cl. Limatambo - San Isidro, Cl. Limatambo - SJL, Cl. Cayetano Heredia - SMP, Cl. San Judas Tadeo - San Miguel, C.M. Jockey Salud - Surco, Cl. Aviva - Lima</t>
+  </si>
+  <si>
+    <t>C.M. Sanna - Miraflores, C.M. Sanna - Surco, C.M. Sanna - La Molina, C.M. Sanna - Los Olivos, C.M. Sanna - San Miguel, C.M. Sanna - San Juan de Lurigancho</t>
+  </si>
+  <si>
+    <t>C.M. Integramédica - Independencia, Cl. Versalles - Comas, Cl. Mundo Salud - Los Olivos, Cl. Montefiori - La Molina, Cl. San Juan Bautista - SJL, Cl. Santa Martha del Sur - SJM, Cl. Providencia - San Miguel, Cl. San Judas Tadeo - San Miguel, C.M. Ricardo Palma - Chorrillos, C.M. Limatambo - Callao, Cl. Limatambo - SJL, Cl. Medavan - Magdalena, Cl. Virgen del Rosario - Magdalena, Cl. Stella Maris - Pueblo Libre, Cl. Vesalio - San Borja, Cl. Limatambo - San Isidro, Cl. Aviva - Lima, C.M. Los Álamos - Surquillo, Cl. Cayetano Heredia - SMP, C.M. Jockey Salud - Surco</t>
+  </si>
+  <si>
+    <t>Cl. Santa Isabel - San Borja, Cl. Ricardo Palma - San Isidro, C.M. Internacional - San Isidro, Cl. Internacional - San Borja, C.M. Internacional - Surco</t>
+  </si>
+  <si>
+    <t>Cl. Miraflores - Miraflores, C.M. San Felipe - La Molina, Cl. San Felipe - Jesús María, C.M. San Felipe - Surco</t>
+  </si>
+  <si>
+    <t>C.M. Integramédica - Independencia, Cl. Versalles - Comas, Cl. Mundo Salud - Los Olivos, Cl. Montefiori - La Molina, Cl. San Juan Bautista - SJL, Cl. Santa Martha del Sur - SJM, Cl. Providencia - San Miguel, Cl. San Judas Tadeo - San Miguel, C.M. Ricardo Palma - Chorrillos, C.M. Limatambo - Callao, Cl. Limatambo - SJL, Cl. Medavan - Magdalena, Cl. Virgen del Rosario - Magdalena, Cl. Stella Maris - Pueblo Libre, Cl. Vesalio - San Borja, Cl. Limatambo - San Isidro, Cl. Aviva - Lima, C.M. Los Álamos - Surquillo, Cl. Cayetano Heredia - SMP, C.M. Jockey Salud - Surco, Cl. Centenario Peruano Japonesa - Pueblo Libre, Cl. Javier Prado - San Isidro, Cl. Aviva - Los Olivos</t>
+  </si>
+  <si>
+    <t>Cl. Miraflores - Miraflores, Cl. Angloamericana - La Molina, Cl. Angloamericana - San Isidro, C.M. San Felipe - La Molina, Cl. San Felipe - Jesús María, C.M. San Felipe - Surco</t>
+  </si>
+  <si>
+    <t>C.M. Integramédica - Independencia, Cl. Versalles - Comas, Cl. Mundo Salud - Los Olivos, Cl. Montefiori - La Molina, Cl. San Juan Bautista - SJL, Cl. Santa Martha del Sur - SJM, Cl. Providencia - San Miguel, Cl. San Judas Tadeo - San Miguel, C.M. Ricardo Palma - Chorrillos, C.M. Limatambo - Callao, Cl. Limatambo - SJL, Cl. Medavan - Magdalena, Cl. Virgen del Rosario - Magdalena, Cl. Stella Maris - Pueblo Libre, Cl. Vesalio - San Borja, Cl. Limatambo - San Isidro, Cl. Aviva - Lima, C.M. Los Álamos - Surquillo, Cl. Cayetano Heredia - SMP, C.M. Jockey Salud - Surco, Cl. Centenario Peruano Japonesa - Pueblo Libre, Cl. Javier Prado - San Isidro</t>
+  </si>
+  <si>
+    <t>C.M. La Positiva - Surco</t>
+  </si>
+  <si>
+    <t>Cl. Stella Maris - Pueblo Libre, Cl. Bellavista - Callao, C.M. Limatambo - Callao, Cl. Maisón de Sante - Lima, Cl. San Judas Tadeo - San Miguel, Cl. Limatambo - SJL, Cl. San Juan Bautista - SJL, Cl. Santa Martha del Sur - SJM, Cl. Versalles - Comas, Cl. San Juan De Dios - San Luis, Cl. San Bernardo - Pueblo Libre, Cl. La Luz - Lima, Cl. Poémape - Chancay, Cl. La Solidaridad - Barranca, C.M. AltaSalud - Barranca, C.M. Medex - Surquillo, Cl. Antonio Raymondi - La Victoria, Cl. Aviva - Lima, Cl. Arthrosalud - Lima, C.M. Integramédica - Independencia, Cl. Maisón de Sante - Chorrillos, Cl. San Pedro - Huara, Cl. Medavan - Magdalena, Cl. San Clemente - Lince, C.M. Cayetano Heredia - Lince, Cl. Aviva - Los Olivos, Cl. Aviva - Lima, Cl. San Bartolomé - Huacho</t>
+  </si>
+  <si>
+    <t>Cl. San Marcos - Huara, Cl. Providencia - San Miguel, C.M. Ricardo Palma - Chorrillos, Cl. Sanens - Surquillo, C.M. Jockey Salud - Surco, Cl. Limatambo - San Isidro, C.M. AltaSalud - San Isidro, Cl. Vesalio - San Borja, C.M. Sanna - La Molina, C.M. Sanna - Miraflores, Cl. Good Hope - Miraflores, Cl. Corazón de Jesús - Cañete, C.M. Clisova - Chancay, C.M. Clisova - Huaral, C.M. Nueva Esperanza - Huaral</t>
+  </si>
+  <si>
+    <t>Cl. El Golf - San Isidro, Cl. Santa Isabel - San Borja, C.M. Sanna - Surco, Cl. Auna - San Isidro, Cl. Alvarez - Surco, Cl. Del Inca - Miraflores</t>
+  </si>
+  <si>
+    <t>Cl. San Pablo - Surco, Cl. Ricardo Palma - San Isidro, C.M. Sormedic - Lima, C.M. Urozen - San Borja</t>
+  </si>
+  <si>
+    <t>C.M. Limatambo - Callao, Cl. Cayetano Heredia - SMP, Cl. Maisón de Sante - Lima, Cl. MegaSalud Universal - Lima, Cl. Limatambo - SJL, Cl. San Juan Bautista - SJL, Cl. Santa Martha del Sur - SJM, Cl. Versalles - Comas, Cl. San Juan De Dios - San Luis, Cl. San Bernardo - Pueblo Libre, Cl. La Luz - Lima, Cl. Poémape - Chancay, Cl. Montefiori - La Molina</t>
+  </si>
+  <si>
+    <t>C.M. SBC Medic - Barranco, Cl. La Solidaridad - Barranca, C.M. AltaSalud - Barranca, Cl. Antonio Raymondi - La Victoria,  C.M. Medex - Surquillo, Cl. Aviva - Lima, Cl. Arthrosalud - Lima, Cl. Bellavista - Callao, C.M. Integramédica - Independencia, Cl. Bellavista - Callao, Cl. Maisón de Sante - Chorrillos, Cl. San Judas Tadeo - San Miguel, Cl. San Pedro - Huara, Cl. Stella Maris - Pueblo Libre, Cl. San Clemente - Lince, C.M. Cayetano Heredia - Lince, Cl. Aviva - Los Olivos, Cl. San Bartolomé - Huacho</t>
+  </si>
+  <si>
+    <t>Cl. Centenario Peruano Japonesa - Pueblo Libre, Cl. Providencia - San Miguel, Cl. Good Hope - Miraflores, Cl. Limatambo - San Isidro, Cl. Sanens - Surquillo, Cl. Medavan - Magdalena, C.M. Ricardo Palma - Chorrillos, Cl. San Marcos - Huaura, Cl. Vesalio - San Borja, C.M. Jockey Salud - Surco, C.M. AltaSalud - San Isidro, C.M. Sanna - La Molina, C.M. Sanna - Miraflores, Cl. Higuereta - Miraflores, Cl. Corazón de Jesús - Cañete, C.M. Clisova - Chancay, C.M. Clisova - Huaral, C.M. Nueva Esperanza - Huaral</t>
+  </si>
+  <si>
+    <t>C.M. SBC Medic - Barranco, Cl. La Solidaridad - Barranca, C.M. AltaSalud - Barranca, Cl. Antonio Raymondi - La Victoria, C.M. Medex - Surquillo, Cl. Aviva - Lima, Cl. Arthrosalud - Lima, Cl. Bellavista - Callao, C.M. Integramédica - Independencia, Cl. Bellavista - Callao, Cl. Maisón de Sante - Chorrillos, Cl. San Judas Tadeo - San Miguel, Cl. San Pedro - Huara, Cl. Stella Maris - Pueblo Libre, Cl. San Clemente - Lince, C.M. Cayetano Heredia - Lince, Cl. Aviva - Los Olivos, Cl. San Bartolomé - Huacho</t>
+  </si>
+  <si>
+    <t>C.M. SBC Medic - Barranco, Cl. La Solidaridad - Barranca, C.M. AltaSalud - Barranca, Cl. Antonio Raymondi - La Victoria, C.M. Medex - Surquillo, Cl. Aviva - Lima, Cl. Arthrosalud - Lima, Cl. Bellavista - Callao, C.M. Integramédica - Independencia, Cl. Bellavista - Callao, Cl. Maisón de Sante - Chorrillos, Cl. San Judas Tadeo - San Miguel, Cl. San Pedro - Huara, Cl. Stella Maris - Pueblo Libre, Cl. San Clemente - Lince, C.M. Cayetano Heredia - Lince, Cl. Aviva - Los Olivos, Cl. San Bartolomé - Huacho, Cl. Medavan - Magdalena</t>
+  </si>
+  <si>
+    <t>Cl. Centenario Peruano Japonesa - Pueblo Libre, Cl. Providencia - San Miguel, Cl. Good Hope - Miraflores, Cl. Limatambo - San Isidro, Cl. Sanens - Surquillo, C.M. Ricardo Palma - Chorrillos, Cl. San Marcos - Huaura, Cl. Vesalio - San Borja, C.M. Jockey Salud - Surco, C.M. AltaSalud - San Isidro, C.M. Sanna - La Molina, C.M. Sanna - Miraflores, Cl. Higuereta - Miraflores, Cl. Corazón de Jesús - Cañete, C.M. Clisova - Chancay, C.M. Clisova - Huaral, C.M. Nueva Esperanza - Huaral</t>
+  </si>
+  <si>
+    <t>Cl. Internacional - Lima, C.M. Internacional - San Isidro, C.M. Internacional - Surco, C.M. Internacional - La Molina, Cl. Internacional - San Borja, Cl. Delgado - Miraflores, C.M. San Felipe - La Molina, Cl. Angloamericana - San Isidro, Cl. Angloamericana - La Molina, Cl. San Felipe - Jesús María</t>
+  </si>
+  <si>
+    <t>C.M. Mapfre - Independencia, C.M. Mapfre - Magdalena, C.M. Mapfre - San Miguel, C.M. Mapfre - Surco</t>
+  </si>
+  <si>
+    <t>Cl. Montefiori - La Molina, Cl. Providencia - San Miguel, Cl. San Judas Tadeo - San Miguel, Cl. Jesús del Norte - Independencia, C.M. Medex - Surquillo, Cl. Los Andes - Miraflores, Cl. San Juan Bautista - SJL, Cl. Aviva - Los Olivos, Cl. Virgen del Rosario - Magdalena, Cl. Cayetano Heredia - SMP, Cl. Santa Martha del Sur - SJM, Cl. Limatambo - SJL, C.M. Limatambo - Callao, C.M. Suiza Lab - Miraflores, C.M. Suiza Lab - Surco, Cl. Mundo Salud - Los Olivos, Cl. Medavan - Magdalena, Cl. Santa María - Surquillo, Cl. Especialidades Médicas - San Borja, Cl. Maisón de Sante - Chorrillos, Cl. Maisón de Sante - Lima, Cl. San Juan De Dios - San Luis, Cl. San Vicente - SMP, Cl. Integramédica - San Isidro</t>
+  </si>
+  <si>
+    <t>Cl. Javier Prado - San Isidro, Cl. San Gabriel - San Miguel, Cl. Tezza - Surco, Cl. Centenario Peruano Japonesa - Pueblo Libre, C.M. Jockey Salud - Surco, Cl. Good Hope - Miraflores, Cl. Bellavista - Callao, Cl. Stella Maris - Pueblo Libre, Cl. Limatambo - San Isidro, Cl. Vesalio - San Borja, C.M. Ricardo Palma - Chorrillos, Cl. La Luz - Lima</t>
+  </si>
+  <si>
+    <t>Cl. Santa Isabel - San Borja, Cl. Sanna - San Borja, Cl. El Golf - San Isidro, C.M. Sanna - La Molina, Cl. Maisón de Sante - Surco, Cl. Internacional - Lima, Cl. Internacional - San Borja</t>
+  </si>
+  <si>
+    <t>Cl. Angloamericana - La Molina, Cl. Angloamericana - San Isidro, C.M. San Felipe - La Molina, Cl. San Felipe - Jesús María, Cl. Miraflores - Miraflores, Cl. San Felipe - Jesús María, Cl. Miraflores - Miraflores, Cl. Montesur - Surco</t>
+  </si>
+  <si>
+    <t>C.M. Mapfre - Independencia, C.M. Mapfre - Magdalena, C.M. Mapfre - San Miguel, C.M. Mapfre - Surco, Cl. Integramédica - San Isidro</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1098,7 +1097,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F138"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1145,7 +1144,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1165,7 +1164,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1185,7 +1184,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1205,7 +1204,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1225,7 +1224,7 @@
         <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1245,7 +1244,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1265,7 +1264,7 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1285,7 +1284,7 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1305,7 +1304,7 @@
         <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1325,7 +1324,7 @@
         <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1345,7 +1344,7 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1365,7 +1364,7 @@
         <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1385,7 +1384,7 @@
         <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1405,7 +1404,7 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1425,7 +1424,7 @@
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>221</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1445,7 +1444,7 @@
         <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1465,7 +1464,7 @@
         <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1485,7 +1484,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1505,7 +1504,7 @@
         <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1525,7 +1524,7 @@
         <v>37</v>
       </c>
       <c r="F21" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1545,7 +1544,7 @@
         <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1565,7 +1564,7 @@
         <v>28</v>
       </c>
       <c r="F23" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1585,7 +1584,7 @@
         <v>13</v>
       </c>
       <c r="F24" t="s">
-        <v>221</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1605,7 +1604,7 @@
         <v>13</v>
       </c>
       <c r="F25" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1625,7 +1624,7 @@
         <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1645,7 +1644,7 @@
         <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1665,7 +1664,7 @@
         <v>26</v>
       </c>
       <c r="F28" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1685,7 +1684,7 @@
         <v>37</v>
       </c>
       <c r="F29" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1705,7 +1704,7 @@
         <v>28</v>
       </c>
       <c r="F30" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1725,7 +1724,7 @@
         <v>28</v>
       </c>
       <c r="F31" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1745,7 +1744,7 @@
         <v>13</v>
       </c>
       <c r="F32" t="s">
-        <v>221</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1765,7 +1764,7 @@
         <v>13</v>
       </c>
       <c r="F33" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1785,7 +1784,7 @@
         <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1805,7 +1804,7 @@
         <v>50</v>
       </c>
       <c r="F35" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1825,7 +1824,7 @@
         <v>37</v>
       </c>
       <c r="F36" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1845,7 +1844,7 @@
         <v>28</v>
       </c>
       <c r="F37" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1865,7 +1864,7 @@
         <v>13</v>
       </c>
       <c r="F38" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1885,7 +1884,7 @@
         <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>216</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1905,7 +1904,7 @@
         <v>24</v>
       </c>
       <c r="F40" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1925,7 +1924,7 @@
         <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1945,7 +1944,7 @@
         <v>37</v>
       </c>
       <c r="F42" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1965,7 +1964,7 @@
         <v>28</v>
       </c>
       <c r="F43" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1985,7 +1984,7 @@
         <v>13</v>
       </c>
       <c r="F44" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2005,7 +2004,7 @@
         <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2025,7 +2024,7 @@
         <v>24</v>
       </c>
       <c r="F46" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2045,7 +2044,7 @@
         <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2065,7 +2064,7 @@
         <v>37</v>
       </c>
       <c r="F48" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2085,7 +2084,7 @@
         <v>13</v>
       </c>
       <c r="F49" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2105,7 +2104,7 @@
         <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2125,7 +2124,7 @@
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2145,7 +2144,7 @@
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2165,7 +2164,7 @@
         <v>34</v>
       </c>
       <c r="F53" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2185,7 +2184,7 @@
         <v>37</v>
       </c>
       <c r="F54" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2205,7 +2204,7 @@
         <v>16</v>
       </c>
       <c r="F55" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2225,7 +2224,7 @@
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2245,7 +2244,7 @@
         <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2265,7 +2264,7 @@
         <v>28</v>
       </c>
       <c r="F58" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2285,7 +2284,7 @@
         <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2305,7 +2304,7 @@
         <v>34</v>
       </c>
       <c r="F60" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2325,7 +2324,7 @@
         <v>72</v>
       </c>
       <c r="F61" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2345,7 +2344,7 @@
         <v>28</v>
       </c>
       <c r="F62" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2365,7 +2364,7 @@
         <v>13</v>
       </c>
       <c r="F63" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2385,7 +2384,7 @@
         <v>16</v>
       </c>
       <c r="F64" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2405,7 +2404,7 @@
         <v>77</v>
       </c>
       <c r="F65" t="s">
-        <v>219</v>
+        <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2425,7 +2424,7 @@
         <v>74</v>
       </c>
       <c r="F66" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2445,7 +2444,7 @@
         <v>24</v>
       </c>
       <c r="F67" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2465,7 +2464,7 @@
         <v>28</v>
       </c>
       <c r="F68" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2485,7 +2484,7 @@
         <v>16</v>
       </c>
       <c r="F69" t="s">
-        <v>224</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2505,7 +2504,7 @@
         <v>16</v>
       </c>
       <c r="F70" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2525,7 +2524,7 @@
         <v>34</v>
       </c>
       <c r="F71" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2545,7 +2544,7 @@
         <v>72</v>
       </c>
       <c r="F72" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2559,13 +2558,13 @@
         <v>82</v>
       </c>
       <c r="D73" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="E73" t="s">
         <v>72</v>
       </c>
       <c r="F73" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2585,7 +2584,7 @@
         <v>74</v>
       </c>
       <c r="F74" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2605,7 +2604,7 @@
         <v>24</v>
       </c>
       <c r="F75" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2625,7 +2624,7 @@
         <v>37</v>
       </c>
       <c r="F76" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2645,7 +2644,7 @@
         <v>28</v>
       </c>
       <c r="F77" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2665,7 +2664,7 @@
         <v>13</v>
       </c>
       <c r="F78" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2685,7 +2684,7 @@
         <v>13</v>
       </c>
       <c r="F79" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2705,7 +2704,7 @@
         <v>13</v>
       </c>
       <c r="F80" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2725,7 +2724,7 @@
         <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2745,7 +2744,7 @@
         <v>74</v>
       </c>
       <c r="F82" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2765,7 +2764,7 @@
         <v>24</v>
       </c>
       <c r="F83" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2785,7 +2784,7 @@
         <v>37</v>
       </c>
       <c r="F84" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2805,7 +2804,7 @@
         <v>28</v>
       </c>
       <c r="F85" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2825,7 +2824,7 @@
         <v>28</v>
       </c>
       <c r="F86" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2845,7 +2844,7 @@
         <v>13</v>
       </c>
       <c r="F87" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2865,7 +2864,7 @@
         <v>13</v>
       </c>
       <c r="F88" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -2885,7 +2884,7 @@
         <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -2905,7 +2904,7 @@
         <v>74</v>
       </c>
       <c r="F90" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -2925,7 +2924,7 @@
         <v>26</v>
       </c>
       <c r="F91" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -2945,7 +2944,7 @@
         <v>91</v>
       </c>
       <c r="F92" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -2965,7 +2964,7 @@
         <v>13</v>
       </c>
       <c r="F93" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -2985,7 +2984,7 @@
         <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3005,7 +3004,7 @@
         <v>34</v>
       </c>
       <c r="F95" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3025,7 +3024,7 @@
         <v>72</v>
       </c>
       <c r="F96" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3045,7 +3044,7 @@
         <v>74</v>
       </c>
       <c r="F97" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3065,7 +3064,7 @@
         <v>16</v>
       </c>
       <c r="F98" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3085,7 +3084,7 @@
         <v>19</v>
       </c>
       <c r="F99" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3105,7 +3104,7 @@
         <v>34</v>
       </c>
       <c r="F100" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3125,7 +3124,7 @@
         <v>74</v>
       </c>
       <c r="F101" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3145,7 +3144,7 @@
         <v>37</v>
       </c>
       <c r="F102" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3165,7 +3164,7 @@
         <v>16</v>
       </c>
       <c r="F103" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3185,7 +3184,7 @@
         <v>19</v>
       </c>
       <c r="F104" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3205,7 +3204,7 @@
         <v>34</v>
       </c>
       <c r="F105" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3225,7 +3224,7 @@
         <v>74</v>
       </c>
       <c r="F106" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3245,7 +3244,7 @@
         <v>37</v>
       </c>
       <c r="F107" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3265,7 +3264,7 @@
         <v>13</v>
       </c>
       <c r="F108" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3285,7 +3284,7 @@
         <v>16</v>
       </c>
       <c r="F109" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3305,7 +3304,7 @@
         <v>19</v>
       </c>
       <c r="F110" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3325,7 +3324,7 @@
         <v>74</v>
       </c>
       <c r="F111" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3345,7 +3344,7 @@
         <v>24</v>
       </c>
       <c r="F112" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3365,7 +3364,7 @@
         <v>26</v>
       </c>
       <c r="F113" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3385,7 +3384,7 @@
         <v>28</v>
       </c>
       <c r="F114" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3405,7 +3404,7 @@
         <v>13</v>
       </c>
       <c r="F115" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3425,7 +3424,7 @@
         <v>16</v>
       </c>
       <c r="F116" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3445,7 +3444,7 @@
         <v>19</v>
       </c>
       <c r="F117" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3465,7 +3464,7 @@
         <v>34</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>179</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3485,7 +3484,7 @@
         <v>74</v>
       </c>
       <c r="F119" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3505,7 +3504,7 @@
         <v>24</v>
       </c>
       <c r="F120" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3525,7 +3524,7 @@
         <v>26</v>
       </c>
       <c r="F121" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3545,7 +3544,7 @@
         <v>37</v>
       </c>
       <c r="F122" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3565,7 +3564,7 @@
         <v>28</v>
       </c>
       <c r="F123" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3585,7 +3584,7 @@
         <v>28</v>
       </c>
       <c r="F124" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3605,7 +3604,7 @@
         <v>13</v>
       </c>
       <c r="F125" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3625,7 +3624,7 @@
         <v>13</v>
       </c>
       <c r="F126" t="s">
-        <v>226</v>
+        <v>179</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3645,7 +3644,7 @@
         <v>19</v>
       </c>
       <c r="F127" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -3665,7 +3664,7 @@
         <v>74</v>
       </c>
       <c r="F128" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3685,7 +3684,7 @@
         <v>37</v>
       </c>
       <c r="F129" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3705,7 +3704,7 @@
         <v>28</v>
       </c>
       <c r="F130" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3725,7 +3724,7 @@
         <v>74</v>
       </c>
       <c r="F131" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -3745,7 +3744,7 @@
         <v>24</v>
       </c>
       <c r="F132" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -3765,7 +3764,7 @@
         <v>26</v>
       </c>
       <c r="F133" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -3785,7 +3784,7 @@
         <v>16</v>
       </c>
       <c r="F134" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -3805,7 +3804,7 @@
         <v>16</v>
       </c>
       <c r="F135" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -3825,7 +3824,7 @@
         <v>16</v>
       </c>
       <c r="F136" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -3833,10 +3832,10 @@
         <v>100</v>
       </c>
       <c r="B137" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
       <c r="C137" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="D137" t="s">
         <v>65</v>
@@ -3845,7 +3844,7 @@
         <v>74</v>
       </c>
       <c r="F137" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -3853,19 +3852,19 @@
         <v>100</v>
       </c>
       <c r="B138" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
       <c r="C138" t="s">
-        <v>205</v>
+        <v>153</v>
       </c>
       <c r="D138" t="s">
-        <v>206</v>
+        <v>154</v>
       </c>
       <c r="E138" t="s">
-        <v>207</v>
+        <v>155</v>
       </c>
       <c r="F138" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -3875,7 +3874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\COTI SALUD 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C9C19C-D29D-4A9B-81E5-1595EF59E280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14415" windowHeight="11835"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REDES" sheetId="1" r:id="rId1"/>
     <sheet name="INFO_PLAN" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="221">
   <si>
     <t>Aseguradora</t>
   </si>
@@ -310,9 +311,6 @@
     <t>S/75 al 65%</t>
   </si>
   <si>
-    <t>Medisalud Base</t>
-  </si>
-  <si>
     <t>Medisalud</t>
   </si>
   <si>
@@ -346,9 +344,6 @@
     <t>Cubierto al 90%</t>
   </si>
   <si>
-    <t>S/60 al 70%</t>
-  </si>
-  <si>
     <t>S/105 al 65%</t>
   </si>
   <si>
@@ -553,9 +548,6 @@
     <t>Cl. Good Hope - Miraflores, Cl. Maisón de Sante - Chorrillos, Cl. Aviva - Los Olivos, Cl. San Gabriel - San Miguel, Cl. Maisón de Sante - Lima, Cl. Jesús del Norte - Independencia, Cl. Tezza - Surco</t>
   </si>
   <si>
-    <t>Cl. Cayetano Heredia - SMP, Cl. Montefiori - La Molina</t>
-  </si>
-  <si>
     <t>Cl. Jesús del Norte - Independencia, Cl. San Gabriel - San Miguel, Cl. Javier Prado - San Isidro, Cl. Tezza - Surco, Cl. Maisón de Sante - Surco</t>
   </si>
   <si>
@@ -655,12 +647,6 @@
     <t>C.M. La Positiva - Surco</t>
   </si>
   <si>
-    <t>Cl. Stella Maris - Pueblo Libre, Cl. Bellavista - Callao, C.M. Limatambo - Callao, Cl. Maisón de Sante - Lima, Cl. San Judas Tadeo - San Miguel, Cl. Limatambo - SJL, Cl. San Juan Bautista - SJL, Cl. Santa Martha del Sur - SJM, Cl. Versalles - Comas, Cl. San Juan De Dios - San Luis, Cl. San Bernardo - Pueblo Libre, Cl. La Luz - Lima, Cl. Poémape - Chancay, Cl. La Solidaridad - Barranca, C.M. AltaSalud - Barranca, C.M. Medex - Surquillo, Cl. Antonio Raymondi - La Victoria, Cl. Aviva - Lima, Cl. Arthrosalud - Lima, C.M. Integramédica - Independencia, Cl. Maisón de Sante - Chorrillos, Cl. San Pedro - Huara, Cl. Medavan - Magdalena, Cl. San Clemente - Lince, C.M. Cayetano Heredia - Lince, Cl. Aviva - Los Olivos, Cl. Aviva - Lima, Cl. San Bartolomé - Huacho</t>
-  </si>
-  <si>
-    <t>Cl. San Marcos - Huara, Cl. Providencia - San Miguel, C.M. Ricardo Palma - Chorrillos, Cl. Sanens - Surquillo, C.M. Jockey Salud - Surco, Cl. Limatambo - San Isidro, C.M. AltaSalud - San Isidro, Cl. Vesalio - San Borja, C.M. Sanna - La Molina, C.M. Sanna - Miraflores, Cl. Good Hope - Miraflores, Cl. Corazón de Jesús - Cañete, C.M. Clisova - Chancay, C.M. Clisova - Huaral, C.M. Nueva Esperanza - Huaral</t>
-  </si>
-  <si>
     <t>Cl. El Golf - San Isidro, Cl. Santa Isabel - San Borja, C.M. Sanna - Surco, Cl. Auna - San Isidro, Cl. Alvarez - Surco, Cl. Del Inca - Miraflores</t>
   </si>
   <si>
@@ -670,21 +656,9 @@
     <t>C.M. Limatambo - Callao, Cl. Cayetano Heredia - SMP, Cl. Maisón de Sante - Lima, Cl. MegaSalud Universal - Lima, Cl. Limatambo - SJL, Cl. San Juan Bautista - SJL, Cl. Santa Martha del Sur - SJM, Cl. Versalles - Comas, Cl. San Juan De Dios - San Luis, Cl. San Bernardo - Pueblo Libre, Cl. La Luz - Lima, Cl. Poémape - Chancay, Cl. Montefiori - La Molina</t>
   </si>
   <si>
-    <t>C.M. SBC Medic - Barranco, Cl. La Solidaridad - Barranca, C.M. AltaSalud - Barranca, Cl. Antonio Raymondi - La Victoria,  C.M. Medex - Surquillo, Cl. Aviva - Lima, Cl. Arthrosalud - Lima, Cl. Bellavista - Callao, C.M. Integramédica - Independencia, Cl. Bellavista - Callao, Cl. Maisón de Sante - Chorrillos, Cl. San Judas Tadeo - San Miguel, Cl. San Pedro - Huara, Cl. Stella Maris - Pueblo Libre, Cl. San Clemente - Lince, C.M. Cayetano Heredia - Lince, Cl. Aviva - Los Olivos, Cl. San Bartolomé - Huacho</t>
-  </si>
-  <si>
     <t>Cl. Centenario Peruano Japonesa - Pueblo Libre, Cl. Providencia - San Miguel, Cl. Good Hope - Miraflores, Cl. Limatambo - San Isidro, Cl. Sanens - Surquillo, Cl. Medavan - Magdalena, C.M. Ricardo Palma - Chorrillos, Cl. San Marcos - Huaura, Cl. Vesalio - San Borja, C.M. Jockey Salud - Surco, C.M. AltaSalud - San Isidro, C.M. Sanna - La Molina, C.M. Sanna - Miraflores, Cl. Higuereta - Miraflores, Cl. Corazón de Jesús - Cañete, C.M. Clisova - Chancay, C.M. Clisova - Huaral, C.M. Nueva Esperanza - Huaral</t>
   </si>
   <si>
-    <t>C.M. SBC Medic - Barranco, Cl. La Solidaridad - Barranca, C.M. AltaSalud - Barranca, Cl. Antonio Raymondi - La Victoria, C.M. Medex - Surquillo, Cl. Aviva - Lima, Cl. Arthrosalud - Lima, Cl. Bellavista - Callao, C.M. Integramédica - Independencia, Cl. Bellavista - Callao, Cl. Maisón de Sante - Chorrillos, Cl. San Judas Tadeo - San Miguel, Cl. San Pedro - Huara, Cl. Stella Maris - Pueblo Libre, Cl. San Clemente - Lince, C.M. Cayetano Heredia - Lince, Cl. Aviva - Los Olivos, Cl. San Bartolomé - Huacho</t>
-  </si>
-  <si>
-    <t>C.M. SBC Medic - Barranco, Cl. La Solidaridad - Barranca, C.M. AltaSalud - Barranca, Cl. Antonio Raymondi - La Victoria, C.M. Medex - Surquillo, Cl. Aviva - Lima, Cl. Arthrosalud - Lima, Cl. Bellavista - Callao, C.M. Integramédica - Independencia, Cl. Bellavista - Callao, Cl. Maisón de Sante - Chorrillos, Cl. San Judas Tadeo - San Miguel, Cl. San Pedro - Huara, Cl. Stella Maris - Pueblo Libre, Cl. San Clemente - Lince, C.M. Cayetano Heredia - Lince, Cl. Aviva - Los Olivos, Cl. San Bartolomé - Huacho, Cl. Medavan - Magdalena</t>
-  </si>
-  <si>
-    <t>Cl. Centenario Peruano Japonesa - Pueblo Libre, Cl. Providencia - San Miguel, Cl. Good Hope - Miraflores, Cl. Limatambo - San Isidro, Cl. Sanens - Surquillo, C.M. Ricardo Palma - Chorrillos, Cl. San Marcos - Huaura, Cl. Vesalio - San Borja, C.M. Jockey Salud - Surco, C.M. AltaSalud - San Isidro, C.M. Sanna - La Molina, C.M. Sanna - Miraflores, Cl. Higuereta - Miraflores, Cl. Corazón de Jesús - Cañete, C.M. Clisova - Chancay, C.M. Clisova - Huaral, C.M. Nueva Esperanza - Huaral</t>
-  </si>
-  <si>
     <t>Cl. Internacional - Lima, C.M. Internacional - San Isidro, C.M. Internacional - Surco, C.M. Internacional - La Molina, Cl. Internacional - San Borja, Cl. Delgado - Miraflores, C.M. San Felipe - La Molina, Cl. Angloamericana - San Isidro, Cl. Angloamericana - La Molina, Cl. San Felipe - Jesús María</t>
   </si>
   <si>
@@ -704,12 +678,18 @@
   </si>
   <si>
     <t>C.M. Mapfre - Independencia, C.M. Mapfre - Magdalena, C.M. Mapfre - San Miguel, C.M. Mapfre - Surco, Cl. Integramédica - San Isidro</t>
+  </si>
+  <si>
+    <t>C.M. SBC Medic - Barranco, Cl. La Solidaridad - Barranca, Cl. Antonio Raymondi - La Victoria,  C.M. Medex - Surquillo, Cl. Aviva - Lima, Cl. Arthrosalud - Lima, Cl. Bellavista - Callao, C.M. Integramédica - Independencia, Cl. Bellavista - Callao, Cl. Maisón de Sante - Chorrillos, Cl. San Judas Tadeo - San Miguel, Cl. San Pedro - Huara, Cl. Stella Maris - Pueblo Libre, Cl. San Clemente - Lince, C.M. Cayetano Heredia - Lince, Cl. Aviva - Los Olivos, Cl. San Bartolomé - Huacho, C.M. Medex - Surquillo</t>
+  </si>
+  <si>
+    <t>Cl. El Golf - San Isidro, Cl. Auna - San Isidro, Cl. Alvarez - Surco, Cl. Del Inca - Miraflores</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1097,8 +1077,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F138"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -1132,7 +1112,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -1144,7 +1124,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1152,7 +1132,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>11</v>
@@ -1164,7 +1144,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1172,19 +1152,19 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1204,7 +1184,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1224,7 +1204,7 @@
         <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1244,7 +1224,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1264,7 +1244,7 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1284,7 +1264,7 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1304,7 +1284,7 @@
         <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1324,7 +1304,7 @@
         <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1344,7 +1324,7 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1364,7 +1344,7 @@
         <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1384,7 +1364,7 @@
         <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1404,7 +1384,7 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1418,13 +1398,13 @@
         <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1444,7 +1424,7 @@
         <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1458,13 +1438,13 @@
         <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E18" t="s">
         <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1484,7 +1464,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1504,7 +1484,7 @@
         <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1524,7 +1504,7 @@
         <v>37</v>
       </c>
       <c r="F21" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1544,7 +1524,7 @@
         <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1564,7 +1544,7 @@
         <v>28</v>
       </c>
       <c r="F23" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1584,7 +1564,7 @@
         <v>13</v>
       </c>
       <c r="F24" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1604,7 +1584,7 @@
         <v>13</v>
       </c>
       <c r="F25" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1624,7 +1604,7 @@
         <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1644,7 +1624,7 @@
         <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1664,7 +1644,7 @@
         <v>26</v>
       </c>
       <c r="F28" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1684,7 +1664,7 @@
         <v>37</v>
       </c>
       <c r="F29" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1704,7 +1684,7 @@
         <v>28</v>
       </c>
       <c r="F30" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1724,7 +1704,7 @@
         <v>28</v>
       </c>
       <c r="F31" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1744,7 +1724,7 @@
         <v>13</v>
       </c>
       <c r="F32" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1764,7 +1744,7 @@
         <v>13</v>
       </c>
       <c r="F33" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1784,7 +1764,7 @@
         <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1804,7 +1784,7 @@
         <v>50</v>
       </c>
       <c r="F35" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1824,7 +1804,7 @@
         <v>37</v>
       </c>
       <c r="F36" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1844,7 +1824,7 @@
         <v>28</v>
       </c>
       <c r="F37" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1864,7 +1844,7 @@
         <v>13</v>
       </c>
       <c r="F38" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1884,7 +1864,7 @@
         <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1904,7 +1884,7 @@
         <v>24</v>
       </c>
       <c r="F40" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1924,7 +1904,7 @@
         <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1944,7 +1924,7 @@
         <v>37</v>
       </c>
       <c r="F42" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1964,7 +1944,7 @@
         <v>28</v>
       </c>
       <c r="F43" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1984,7 +1964,7 @@
         <v>13</v>
       </c>
       <c r="F44" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2004,7 +1984,7 @@
         <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2024,7 +2004,7 @@
         <v>24</v>
       </c>
       <c r="F46" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2044,7 +2024,7 @@
         <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2064,7 +2044,7 @@
         <v>37</v>
       </c>
       <c r="F48" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2084,7 +2064,7 @@
         <v>13</v>
       </c>
       <c r="F49" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2104,7 +2084,7 @@
         <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2124,7 +2104,7 @@
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2144,7 +2124,7 @@
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2164,7 +2144,7 @@
         <v>34</v>
       </c>
       <c r="F53" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2184,7 +2164,7 @@
         <v>37</v>
       </c>
       <c r="F54" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2204,7 +2184,7 @@
         <v>16</v>
       </c>
       <c r="F55" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2224,7 +2204,7 @@
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2244,7 +2224,7 @@
         <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2264,7 +2244,7 @@
         <v>28</v>
       </c>
       <c r="F58" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2284,7 +2264,7 @@
         <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2304,7 +2284,7 @@
         <v>34</v>
       </c>
       <c r="F60" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2324,7 +2304,7 @@
         <v>72</v>
       </c>
       <c r="F61" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2344,7 +2324,7 @@
         <v>28</v>
       </c>
       <c r="F62" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2364,7 +2344,7 @@
         <v>13</v>
       </c>
       <c r="F63" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2384,7 +2364,7 @@
         <v>16</v>
       </c>
       <c r="F64" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2404,7 +2384,7 @@
         <v>77</v>
       </c>
       <c r="F65" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2424,7 +2404,7 @@
         <v>74</v>
       </c>
       <c r="F66" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2444,7 +2424,7 @@
         <v>24</v>
       </c>
       <c r="F67" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2464,7 +2444,7 @@
         <v>28</v>
       </c>
       <c r="F68" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2484,7 +2464,7 @@
         <v>16</v>
       </c>
       <c r="F69" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2504,7 +2484,7 @@
         <v>16</v>
       </c>
       <c r="F70" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2524,7 +2504,7 @@
         <v>34</v>
       </c>
       <c r="F71" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2544,7 +2524,7 @@
         <v>72</v>
       </c>
       <c r="F72" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2558,13 +2538,13 @@
         <v>82</v>
       </c>
       <c r="D73" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E73" t="s">
         <v>72</v>
       </c>
       <c r="F73" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2584,7 +2564,7 @@
         <v>74</v>
       </c>
       <c r="F74" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2604,7 +2584,7 @@
         <v>24</v>
       </c>
       <c r="F75" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2624,7 +2604,7 @@
         <v>37</v>
       </c>
       <c r="F76" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2644,7 +2624,7 @@
         <v>28</v>
       </c>
       <c r="F77" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2664,7 +2644,7 @@
         <v>13</v>
       </c>
       <c r="F78" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2684,7 +2664,7 @@
         <v>13</v>
       </c>
       <c r="F79" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2704,7 +2684,7 @@
         <v>13</v>
       </c>
       <c r="F80" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2724,7 +2704,7 @@
         <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2744,7 +2724,7 @@
         <v>74</v>
       </c>
       <c r="F82" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2764,7 +2744,7 @@
         <v>24</v>
       </c>
       <c r="F83" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2784,7 +2764,7 @@
         <v>37</v>
       </c>
       <c r="F84" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2804,7 +2784,7 @@
         <v>28</v>
       </c>
       <c r="F85" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2824,7 +2804,7 @@
         <v>28</v>
       </c>
       <c r="F86" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2844,7 +2824,7 @@
         <v>13</v>
       </c>
       <c r="F87" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2864,7 +2844,7 @@
         <v>13</v>
       </c>
       <c r="F88" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -2884,7 +2864,7 @@
         <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -2898,13 +2878,13 @@
         <v>89</v>
       </c>
       <c r="D90" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E90" t="s">
         <v>74</v>
       </c>
       <c r="F90" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -2924,7 +2904,7 @@
         <v>26</v>
       </c>
       <c r="F91" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -2944,7 +2924,7 @@
         <v>91</v>
       </c>
       <c r="F92" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -2964,7 +2944,7 @@
         <v>13</v>
       </c>
       <c r="F93" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -2984,7 +2964,7 @@
         <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3004,7 +2984,7 @@
         <v>34</v>
       </c>
       <c r="F95" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3024,7 +3004,7 @@
         <v>72</v>
       </c>
       <c r="F96" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3038,13 +3018,13 @@
         <v>89</v>
       </c>
       <c r="D97" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E97" t="s">
         <v>74</v>
       </c>
       <c r="F97" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3064,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="F98" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3084,7 +3064,7 @@
         <v>19</v>
       </c>
       <c r="F99" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3104,7 +3084,7 @@
         <v>34</v>
       </c>
       <c r="F100" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3118,13 +3098,13 @@
         <v>89</v>
       </c>
       <c r="D101" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E101" t="s">
         <v>74</v>
       </c>
       <c r="F101" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3138,13 +3118,13 @@
         <v>8</v>
       </c>
       <c r="D102" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="E102" t="s">
         <v>37</v>
       </c>
       <c r="F102" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3161,10 +3141,10 @@
         <v>15</v>
       </c>
       <c r="E103" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F103" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3181,10 +3161,10 @@
         <v>95</v>
       </c>
       <c r="E104" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F104" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3201,10 +3181,10 @@
         <v>71</v>
       </c>
       <c r="E105" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F105" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3212,19 +3192,19 @@
         <v>87</v>
       </c>
       <c r="B106" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C106" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="D106" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="E106" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="F106" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3235,16 +3215,16 @@
         <v>97</v>
       </c>
       <c r="C107" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="D107" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="E107" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="F107" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3255,16 +3235,16 @@
         <v>97</v>
       </c>
       <c r="C108" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D108" t="s">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="E108" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F108" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3275,16 +3255,16 @@
         <v>97</v>
       </c>
       <c r="C109" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D109" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="E109" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F109" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3295,16 +3275,16 @@
         <v>97</v>
       </c>
       <c r="C110" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E110" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F110" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3312,19 +3292,19 @@
         <v>87</v>
       </c>
       <c r="B111" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C111" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="D111" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
       <c r="E111" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="F111" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3332,19 +3312,19 @@
         <v>87</v>
       </c>
       <c r="B112" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C112" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D112" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E112" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F112" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3352,19 +3332,19 @@
         <v>87</v>
       </c>
       <c r="B113" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C113" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D113" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="E113" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F113" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3372,19 +3352,19 @@
         <v>87</v>
       </c>
       <c r="B114" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C114" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D114" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="E114" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F114" t="s">
-        <v>220</v>
+        <v>176</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3395,16 +3375,16 @@
         <v>98</v>
       </c>
       <c r="C115" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="D115" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E115" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="F115" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3415,16 +3395,16 @@
         <v>98</v>
       </c>
       <c r="C116" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D116" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E116" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F116" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3435,16 +3415,16 @@
         <v>98</v>
       </c>
       <c r="C117" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D117" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="E117" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F117" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3455,16 +3435,16 @@
         <v>98</v>
       </c>
       <c r="C118" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D118" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="E118" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F118" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3472,19 +3452,19 @@
         <v>87</v>
       </c>
       <c r="B119" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C119" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="E119" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="F119" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3492,19 +3472,19 @@
         <v>87</v>
       </c>
       <c r="B120" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C120" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D120" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E120" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F120" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3512,19 +3492,19 @@
         <v>87</v>
       </c>
       <c r="B121" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C121" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D121" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E121" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F121" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3532,19 +3512,19 @@
         <v>87</v>
       </c>
       <c r="B122" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C122" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D122" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E122" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F122" t="s">
-        <v>220</v>
+        <v>176</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3552,36 +3532,36 @@
         <v>87</v>
       </c>
       <c r="B123" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C123" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="D123" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="E123" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F123" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B124" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C124" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="D124" t="s">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="E124" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="F124" t="s">
         <v>213</v>
@@ -3589,19 +3569,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B125" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C125" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D125" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E125" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F125" t="s">
         <v>214</v>
@@ -3609,262 +3589,182 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B126" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C126" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D126" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="E126" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F126" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B127" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C127" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D127" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E127" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="F127" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B128" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C128" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="D128" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="E128" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="F128" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B129" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C129" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D129" t="s">
         <v>44</v>
       </c>
       <c r="E129" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F129" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B130" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C130" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D130" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="E130" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F130" t="s">
-        <v>224</v>
+        <v>177</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B131" t="s">
+        <v>103</v>
+      </c>
+      <c r="C131" t="s">
+        <v>17</v>
+      </c>
+      <c r="D131" t="s">
         <v>104</v>
       </c>
-      <c r="C131" t="s">
-        <v>102</v>
-      </c>
-      <c r="D131" t="s">
-        <v>69</v>
-      </c>
       <c r="E131" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="F131" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B132" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C132" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D132" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E132" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F132" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B133" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="C133" t="s">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="D133" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="E133" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F133" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B134" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="C134" t="s">
-        <v>14</v>
+        <v>151</v>
       </c>
       <c r="D134" t="s">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="E134" t="s">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c r="F134" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>100</v>
-      </c>
-      <c r="B135" t="s">
-        <v>104</v>
-      </c>
-      <c r="C135" t="s">
-        <v>17</v>
-      </c>
-      <c r="D135" t="s">
-        <v>105</v>
-      </c>
-      <c r="E135" t="s">
-        <v>16</v>
-      </c>
-      <c r="F135" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>100</v>
-      </c>
-      <c r="B136" t="s">
-        <v>104</v>
-      </c>
-      <c r="C136" t="s">
-        <v>20</v>
-      </c>
-      <c r="D136" t="s">
-        <v>33</v>
-      </c>
-      <c r="E136" t="s">
-        <v>16</v>
-      </c>
-      <c r="F136" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>100</v>
-      </c>
-      <c r="B137" t="s">
-        <v>151</v>
-      </c>
-      <c r="C137" t="s">
-        <v>152</v>
-      </c>
-      <c r="D137" t="s">
-        <v>65</v>
-      </c>
-      <c r="E137" t="s">
-        <v>74</v>
-      </c>
-      <c r="F137" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>100</v>
-      </c>
-      <c r="B138" t="s">
-        <v>151</v>
-      </c>
-      <c r="C138" t="s">
-        <v>153</v>
-      </c>
-      <c r="D138" t="s">
-        <v>154</v>
-      </c>
-      <c r="E138" t="s">
-        <v>155</v>
-      </c>
-      <c r="F138" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3874,7 +3774,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3886,186 +3786,186 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" t="s">
         <v>127</v>
       </c>
-      <c r="B5" t="s">
-        <v>129</v>
-      </c>
       <c r="C5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" t="s">
         <v>120</v>
-      </c>
-      <c r="D5" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" t="s">
         <v>132</v>
-      </c>
-      <c r="B7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B14" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
